--- a/tame_output/ON/bt/strategyON_20240808.xlsx
+++ b/tame_output/ON/bt/strategyON_20240808.xlsx
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.4%</t>
+          <t>125.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-631.1%</t>
+          <t>-630.6%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-181.4%</t>
+          <t>-181.2%</t>
         </is>
       </c>
     </row>
@@ -48678,10 +48678,10 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.694954097106327</v>
+        <v>-4.690737687042696</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.948094615136932</v>
+        <v>1.949781179162385</v>
       </c>
       <c r="F2049" t="n">
         <v>0.4749241796036319</v>

--- a/tame_output/ON/bt/strategyON_20240808.xlsx
+++ b/tame_output/ON/bt/strategyON_20240808.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-630.6%</t>
+          <t>-633.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-181.2%</t>
+          <t>-200.1%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.9%</t>
+          <t>-154.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-52.8%</t>
         </is>
       </c>
     </row>
@@ -45363,19 +45363,19 @@
         <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>2.971988151156609</v>
       </c>
       <c r="D1905" t="n">
         <v>-6.895633554317592</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3926166545551468</v>
+        <v>0.2133783051158238</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4677072284042083</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.870602163553407</v>
+        <v>2.691363814114084</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>2.974803211844245</v>
       </c>
       <c r="D1906" t="n">
         <v>-6.73989522175785</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4577270482666802</v>
+        <v>0.2784886988273572</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.3119688958444667</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.966860223776889</v>
+        <v>2.787621874337566</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>2.987709553067904</v>
       </c>
       <c r="D1907" t="n">
         <v>-6.490895423074269</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5702333089637714</v>
+        <v>0.3909949595244484</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.06296909716088606</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.129166444210696</v>
+        <v>2.949928094771373</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>2.859733623468685</v>
       </c>
       <c r="D1908" t="n">
         <v>-6.596485412847374</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4000213834553108</v>
+        <v>0.2207830340159873</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.1685590869339904</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937836520747615</v>
+        <v>2.758598171308291</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>2.908277965345771</v>
       </c>
       <c r="D1909" t="n">
         <v>-6.615220314965971</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4410717644849584</v>
+        <v>0.261833415045635</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.1741550965941217</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.983023256828622</v>
+        <v>2.803784907389299</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.788399042657604</v>
       </c>
       <c r="D1910" t="n">
         <v>-6.467280273558371</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3803688583598306</v>
+        <v>0.2011305089205071</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.1538341806855641</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.875336883685589</v>
+        <v>2.696098534246266</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.779685056404126</v>
       </c>
       <c r="D1911" t="n">
         <v>-6.414310751304383</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3928426810079477</v>
+        <v>0.2136043315686242</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.1008646584315753</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.898404610784504</v>
+        <v>2.719166261345181</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.772724444309032</v>
       </c>
       <c r="D1912" t="n">
         <v>-6.248522555344092</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4521973472969711</v>
+        <v>0.2729589978576477</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.1008646584315753</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.891443998689411</v>
+        <v>2.712205649250087</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.787186798690175</v>
       </c>
       <c r="D1913" t="n">
         <v>-6.215159348865323</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4800049842696215</v>
+        <v>0.300766634830298</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.1008646584315753</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.905906353070554</v>
+        <v>2.726668003631231</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.781718919149371</v>
       </c>
       <c r="D1914" t="n">
         <v>-6.106900211742802</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5178407595778252</v>
+        <v>0.3386024101385017</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.1008646584315753</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.900438473529749</v>
+        <v>2.721200124090426</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.779217013159947</v>
       </c>
       <c r="D1915" t="n">
         <v>-5.983609076925671</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5646553075152547</v>
+        <v>0.3854169580759312</v>
       </c>
       <c r="F1915" t="n">
         <v>0.02242647638555523</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.971911248430605</v>
+        <v>2.792672898991281</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.786917991397273</v>
       </c>
       <c r="D1916" t="n">
         <v>-5.962459878022227</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5808159653139571</v>
+        <v>0.4015776158746336</v>
       </c>
       <c r="F1916" t="n">
         <v>0.04357567528899858</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.992301746009995</v>
+        <v>2.813063396570672</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.782698699744323</v>
       </c>
       <c r="D1917" t="n">
         <v>-5.718694436038783</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6741028504543856</v>
+        <v>0.4948645010150621</v>
       </c>
       <c r="F1917" t="n">
         <v>0.04357567528899858</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.988082454357046</v>
+        <v>2.808844104917723</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.784823013664339</v>
       </c>
       <c r="D1918" t="n">
         <v>-5.616931615761488</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7169322924853194</v>
+        <v>0.5376939430459959</v>
       </c>
       <c r="F1918" t="n">
         <v>0.05679474368142728</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.998138209312519</v>
+        <v>2.818899859873196</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.777565088648041</v>
       </c>
       <c r="D1919" t="n">
         <v>-5.367081221812414</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8096145250486515</v>
+        <v>0.630376175609328</v>
       </c>
       <c r="F1919" t="n">
         <v>0.05679474368142728</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.990880284296221</v>
+        <v>2.811641934856898</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.78116421216869</v>
       </c>
       <c r="D1920" t="n">
         <v>-5.191189129344981</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8835704855562736</v>
+        <v>0.7043321361169501</v>
       </c>
       <c r="F1920" t="n">
         <v>0.05679474368142728</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.99447940781687</v>
+        <v>2.815241058377547</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.794491718223244</v>
       </c>
       <c r="D1921" t="n">
         <v>-5.019742666322517</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9654765768198126</v>
+        <v>0.7862382273804891</v>
       </c>
       <c r="F1921" t="n">
         <v>0.2282412067038904</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.110674791684902</v>
+        <v>2.931436442245579</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.793512195839541</v>
       </c>
       <c r="D1922" t="n">
         <v>-4.945453100584178</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9942128807314452</v>
+        <v>0.8149745312921217</v>
       </c>
       <c r="F1922" t="n">
         <v>0.3025307724422297</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.154269008744202</v>
+        <v>2.975030659304879</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.798206996893858</v>
       </c>
       <c r="D1923" t="n">
         <v>-4.881817358350244</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.024361978679336</v>
+        <v>0.8451236292400126</v>
       </c>
       <c r="F1923" t="n">
         <v>0.3661665146761642</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.197145255138881</v>
+        <v>3.017906905699557</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.779401255677654</v>
       </c>
       <c r="D1924" t="n">
         <v>-4.770390599024323</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.0501269411935</v>
+        <v>0.8708885917541764</v>
       </c>
       <c r="F1924" t="n">
         <v>0.3661665146761642</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.178339513922676</v>
+        <v>2.999101164483353</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.781144332302531</v>
       </c>
       <c r="D1925" t="n">
         <v>-4.780893222089612</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.047668968592262</v>
+        <v>0.8684306191529383</v>
       </c>
       <c r="F1925" t="n">
         <v>0.3556638916108754</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.17378101670838</v>
+        <v>2.994542667269056</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.785073646137351</v>
       </c>
       <c r="D1926" t="n">
         <v>-4.708650653918418</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.08049530969556</v>
+        <v>0.9012569602562364</v>
       </c>
       <c r="F1926" t="n">
         <v>0.3556638916108754</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.1777103305432</v>
+        <v>2.998471981103877</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.785752230054691</v>
       </c>
       <c r="D1927" t="n">
         <v>-4.690936967040552</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.088259368364046</v>
+        <v>0.9090210189247223</v>
       </c>
       <c r="F1927" t="n">
         <v>0.3588452205077922</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.18029771179869</v>
+        <v>3.001059362359367</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.782750301274685</v>
       </c>
       <c r="D1928" t="n">
         <v>-4.582132081560825</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.12877939377593</v>
+        <v>0.9495410443366068</v>
       </c>
       <c r="F1928" t="n">
         <v>0.3588452205077922</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.177295783018684</v>
+        <v>2.99805743357936</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.784329338285299</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.362111283523815</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.218366750001349</v>
+        <v>1.039128400562025</v>
       </c>
       <c r="F1929" t="n">
         <v>0.5000650655757723</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.263606727070086</v>
+        <v>3.084368377630763</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.800223521087122</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.229243594460537</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.287408008428483</v>
+        <v>1.108169658989159</v>
       </c>
       <c r="F1930" t="n">
         <v>0.5000650655757723</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.279500909871909</v>
+        <v>3.100262560432586</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.801369365527424</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.109070511096038</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.336623086214584</v>
+        <v>1.157384736775261</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6202381489402713</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.352750604330911</v>
+        <v>3.173512254891587</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.811457468088864</v>
       </c>
       <c r="D1932" t="n">
         <v>-3.973817149766061</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.400812533308015</v>
+        <v>1.221574183868692</v>
       </c>
       <c r="F1932" t="n">
         <v>0.7554915102702484</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.443990723690337</v>
+        <v>3.264752374251013</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.79749495949029</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.033691977123754</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.362900093766364</v>
+        <v>1.18366174432704</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6956166829125563</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.394103318677147</v>
+        <v>3.214864969237824</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>2.812784128724498</v>
       </c>
       <c r="D1934" t="n">
         <v>-3.913871746212916</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.426117355364907</v>
+        <v>1.246879005925584</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6956166829125563</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.409392487911356</v>
+        <v>3.230154138472032</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>2.72042832804694</v>
       </c>
       <c r="D1935" t="n">
         <v>-3.916341452674722</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.332773672102626</v>
+        <v>1.153535322663303</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6931469764507501</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.315554863356714</v>
+        <v>3.13631651391739</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>2.639690189532241</v>
       </c>
       <c r="D1936" t="n">
         <v>-3.984711638998732</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.224687459058324</v>
+        <v>1.045449109619001</v>
       </c>
       <c r="F1936" t="n">
         <v>0.702422675486965</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.240382144263744</v>
+        <v>3.06114379482442</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>2.630126898164133</v>
       </c>
       <c r="D1937" t="n">
         <v>-3.998499691845779</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.209608946551397</v>
+        <v>1.030370597112073</v>
       </c>
       <c r="F1937" t="n">
         <v>0.702422675486965</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.230818852895635</v>
+        <v>3.051580503456312</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.946396084295658</v>
+        <v>2.767157734856335</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.054019767738368</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.324431752886563</v>
+        <v>1.14519340344724</v>
       </c>
       <c r="F1938" t="n">
         <v>0.702422675486965</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.367849689587838</v>
+        <v>3.188611340148514</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.950963316287446</v>
+        <v>2.771724966848123</v>
       </c>
       <c r="D1939" t="n">
         <v>-3.878545507945899</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.399188688795339</v>
+        <v>1.219950339356015</v>
       </c>
       <c r="F1939" t="n">
         <v>0.702422675486965</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.372416921579625</v>
+        <v>3.193178572140302</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.926705345048653</v>
+        <v>2.74746699560933</v>
       </c>
       <c r="D1940" t="n">
         <v>-3.989481760587148</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.330556216500046</v>
+        <v>1.151317867060723</v>
       </c>
       <c r="F1940" t="n">
         <v>0.702422675486965</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.348158950340832</v>
+        <v>3.168920600901509</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.855243658450103</v>
+        <v>2.67600530901078</v>
       </c>
       <c r="D1941" t="n">
         <v>-3.955818215114866</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.272559948090409</v>
+        <v>1.093321598651085</v>
       </c>
       <c r="F1941" t="n">
         <v>0.7360862209592469</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.296895391025652</v>
+        <v>3.117657041586328</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.865416044882235</v>
+        <v>2.686177695442912</v>
       </c>
       <c r="D1942" t="n">
         <v>-3.895965595911143</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.30667338220403</v>
+        <v>1.127435032764707</v>
       </c>
       <c r="F1942" t="n">
         <v>0.7360862209592469</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.307067777457784</v>
+        <v>3.12782942801846</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.860362315456096</v>
+        <v>2.681123966016772</v>
       </c>
       <c r="D1943" t="n">
         <v>-3.809722132884765</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.336117037988442</v>
+        <v>1.156878688549118</v>
       </c>
       <c r="F1943" t="n">
         <v>0.7360862209592469</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.302014048031644</v>
+        <v>3.122775698592321</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.852138090900621</v>
+        <v>2.672899741461298</v>
       </c>
       <c r="D1944" t="n">
         <v>-3.855028952283745</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.309770085673375</v>
+        <v>1.130531736234052</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6952760579500161</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.269303725670631</v>
+        <v>3.090065376231308</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.852689963933723</v>
+        <v>2.673451614494399</v>
       </c>
       <c r="D1945" t="n">
         <v>-3.884062056986047</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.298708716825556</v>
+        <v>1.119470367386233</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6952760579500161</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.269855598703733</v>
+        <v>3.09061724926441</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.781962655825089</v>
+        <v>2.602724306385765</v>
       </c>
       <c r="D1946" t="n">
         <v>-3.791251575535187</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.265105601297265</v>
+        <v>1.085867251857942</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7880865394008755</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.254814579465614</v>
+        <v>3.07557623002629</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.783836131749689</v>
+        <v>2.604597782310366</v>
       </c>
       <c r="D1947" t="n">
         <v>-3.835641044864615</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.249223289490095</v>
+        <v>1.069984940050772</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7436970700714478</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.230054373792558</v>
+        <v>3.050816024353235</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.778911840261412</v>
+        <v>2.599673490822089</v>
       </c>
       <c r="D1948" t="n">
         <v>-3.952182649969958</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.197682355959681</v>
+        <v>1.018444006520358</v>
       </c>
       <c r="F1948" t="n">
         <v>0.6271554649661051</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.155205119241076</v>
+        <v>2.975966769801752</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.78440313609208</v>
+        <v>2.605164786652756</v>
       </c>
       <c r="D1949" t="n">
         <v>-3.839805648787285</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.248124452263417</v>
+        <v>1.068886102824094</v>
       </c>
       <c r="F1949" t="n">
         <v>0.6271554649661051</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.160696415071743</v>
+        <v>2.981458065632419</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.795900337860619</v>
+        <v>2.616661988421295</v>
       </c>
       <c r="D1950" t="n">
         <v>-3.867586046688638</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.248509494871415</v>
+        <v>1.069271145432092</v>
       </c>
       <c r="F1950" t="n">
         <v>0.599375067064752</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.15552537809947</v>
+        <v>2.976287028660146</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.634256057861272</v>
+        <v>2.455017708421948</v>
       </c>
       <c r="D1951" t="n">
         <v>-3.985966719418777</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.039512945780013</v>
+        <v>0.8602745963406897</v>
       </c>
       <c r="F1951" t="n">
         <v>0.5321572149137758</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.953550386809538</v>
+        <v>2.774312037370214</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.754405718580478</v>
+        <v>2.575167369141154</v>
       </c>
       <c r="D1952" t="n">
         <v>-4.094580797862108</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.116216975121886</v>
+        <v>0.936978625682563</v>
       </c>
       <c r="F1952" t="n">
         <v>0.5321572149137758</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.073700047528743</v>
+        <v>2.89446169808942</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.768918744682801</v>
+        <v>2.589680395243477</v>
       </c>
       <c r="D1953" t="n">
         <v>-4.059171759613965</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.144893616523467</v>
+        <v>0.9656552670841432</v>
       </c>
       <c r="F1953" t="n">
         <v>0.5321572149137758</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.088213073631066</v>
+        <v>2.908974724191743</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.766338186025169</v>
+        <v>2.587099836585846</v>
       </c>
       <c r="D1954" t="n">
         <v>-4.020788097055814</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.157666522889096</v>
+        <v>0.9784281734497724</v>
       </c>
       <c r="F1954" t="n">
         <v>0.5705408774719269</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.108662712508325</v>
+        <v>2.929424363069002</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.763067214870471</v>
+        <v>2.583828865431148</v>
       </c>
       <c r="D1955" t="n">
         <v>-3.843671767020648</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.225242083748464</v>
+        <v>1.046003734309141</v>
       </c>
       <c r="F1955" t="n">
         <v>0.5705408774719269</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.105391741353627</v>
+        <v>2.926153391914304</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.763750606632384</v>
+        <v>2.584512257193061</v>
       </c>
       <c r="D1956" t="n">
         <v>-3.888764011854193</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.207888577576959</v>
+        <v>1.028650228137636</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5086448343025372</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.068937507213907</v>
+        <v>2.889699157774583</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.757537581938799</v>
+        <v>2.578299232499475</v>
       </c>
       <c r="D1957" t="n">
         <v>-3.709388590615426</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.27342572137888</v>
+        <v>1.094187371939557</v>
       </c>
       <c r="F1957" t="n">
         <v>0.6654215924732558</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.156790537422753</v>
+        <v>2.977552187983429</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.738345037270388</v>
+        <v>2.559106687831065</v>
       </c>
       <c r="D1958" t="n">
         <v>-3.754402804136032</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.236227491302228</v>
+        <v>1.056989141862904</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6350726971586512</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.119388655565579</v>
+        <v>2.940150306126256</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.744036599609334</v>
+        <v>2.564798250170011</v>
       </c>
       <c r="D1959" t="n">
         <v>-4.021407314408467</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.135117249532199</v>
+        <v>0.9558789000928758</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4407096591157026</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.008462395078756</v>
+        <v>2.829224045639433</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.743240521505836</v>
+        <v>2.564002172066512</v>
       </c>
       <c r="D1960" t="n">
         <v>-4.12260509584564</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.093842058853832</v>
+        <v>0.9146037094145081</v>
       </c>
       <c r="F1960" t="n">
         <v>0.3723008455703835</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.966621028848066</v>
+        <v>2.787382679408742</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.740840483060152</v>
+        <v>2.561602133620829</v>
       </c>
       <c r="D1961" t="n">
         <v>-4.116094129231327</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.094046407053873</v>
+        <v>0.9148080576145499</v>
       </c>
       <c r="F1961" t="n">
         <v>0.3723008455703835</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.964220990402382</v>
+        <v>2.784982640963059</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.737365202268397</v>
+        <v>2.558126852829074</v>
       </c>
       <c r="D1962" t="n">
         <v>-4.09705600152403</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.098186377345037</v>
+        <v>0.9189480279057136</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3141172342391889</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.925835542811911</v>
+        <v>2.746597193372587</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.856659603902588</v>
+        <v>2.677421254463264</v>
       </c>
       <c r="D1963" t="n">
         <v>-4.128182632674648</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.20503012651898</v>
+        <v>1.025791777079657</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3141172342391889</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.045129944446101</v>
+        <v>2.865891595006778</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.857492932888721</v>
+        <v>2.678254583449398</v>
       </c>
       <c r="D1964" t="n">
         <v>-4.142049394008566</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.200316750971547</v>
+        <v>1.021078401532223</v>
       </c>
       <c r="F1964" t="n">
         <v>0.276259317505366</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.023248523391941</v>
+        <v>2.844010173952618</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.863501463285647</v>
+        <v>2.684263113846324</v>
       </c>
       <c r="D1965" t="n">
         <v>-4.097245222468636</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.224246949984444</v>
+        <v>1.045008600545121</v>
       </c>
       <c r="F1965" t="n">
         <v>0.276259317505366</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.029257053788867</v>
+        <v>2.850018704349544</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.761451684562847</v>
+        <v>2.582213335123523</v>
       </c>
       <c r="D1966" t="n">
         <v>-3.949502252233634</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.181294359355645</v>
+        <v>1.002056009916321</v>
       </c>
       <c r="F1966" t="n">
         <v>0.4440666747402491</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.027891689406996</v>
+        <v>2.848653339967673</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.764245306094328</v>
+        <v>2.585006956655004</v>
       </c>
       <c r="D1967" t="n">
         <v>-4.033323473508332</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.150559492377247</v>
+        <v>0.9713211429379232</v>
       </c>
       <c r="F1967" t="n">
         <v>0.4440666747402491</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.030685310938477</v>
+        <v>2.851446961499154</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.764907654485986</v>
+        <v>2.585669305046662</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.027170767455548</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.153682923190019</v>
+        <v>0.9744445737506953</v>
       </c>
       <c r="F1968" t="n">
         <v>0.4502193807930334</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.035039282961806</v>
+        <v>2.855800933522483</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.763988131226096</v>
+        <v>2.584749781786773</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.04398006560605</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.146039680669928</v>
+        <v>0.9668013312306047</v>
       </c>
       <c r="F1969" t="n">
         <v>0.4334100826425318</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.024034180811615</v>
+        <v>2.844795831372292</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.830323685022917</v>
+        <v>2.651085335583593</v>
       </c>
       <c r="D1970" t="n">
         <v>-3.981682066829928</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.237294433977198</v>
+        <v>1.058056084537874</v>
       </c>
       <c r="F1970" t="n">
         <v>0.4334100826425318</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.090369734608436</v>
+        <v>2.911131385169113</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.632615686737044</v>
+        <v>2.453377337297721</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.77989186916477</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.120302514757388</v>
+        <v>0.9410641653180645</v>
       </c>
       <c r="F1971" t="n">
         <v>0.6314282748116862</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.011472651624056</v>
+        <v>2.832234302184732</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.702905919059219</v>
+        <v>2.523667569619896</v>
       </c>
       <c r="D1972" t="n">
         <v>-3.830778581850965</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.170238062005085</v>
+        <v>0.9909997125657619</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5805415621254917</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.051230856334515</v>
+        <v>2.871992506895191</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.717533655175263</v>
+        <v>2.538295305735939</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.744167839201157</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.219510095181052</v>
+        <v>1.040271745741729</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6591672933306499</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.113034031173653</v>
+        <v>2.93379568173433</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.716069635999935</v>
+        <v>2.536831286560611</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.804377137206442</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.19396235680361</v>
+        <v>1.014724007364286</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5989579953253654</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.075444433195154</v>
+        <v>2.896206083755831</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.714561254039863</v>
+        <v>2.53532290460054</v>
       </c>
       <c r="D1975" t="n">
         <v>-3.727955090774515</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.223022793416309</v>
+        <v>1.043784443976986</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5989579953253654</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.073936051235083</v>
+        <v>2.894697701795759</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.714424121475299</v>
+        <v>2.535185772035976</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.683581959135946</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.240634913507173</v>
+        <v>1.061396564067849</v>
       </c>
       <c r="F1976" t="n">
         <v>0.643331126963934</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.10042279765366</v>
+        <v>2.921184448214337</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.70881791561389</v>
+        <v>2.529579566174566</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.706062309994831</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.226036567302209</v>
+        <v>1.046798217862886</v>
       </c>
       <c r="F1977" t="n">
         <v>0.643331126963934</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.094816591792251</v>
+        <v>2.915578242352927</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.715199672641694</v>
+        <v>2.535961323202371</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.658406579433776</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.251480616554436</v>
+        <v>1.072242267115113</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6909868575249897</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.129791787156689</v>
+        <v>2.950553437717365</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.720092046016419</v>
+        <v>2.540853696577096</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.557888420935021</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.296580253328663</v>
+        <v>1.117341903889339</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7915050160237442</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.194995055630666</v>
+        <v>3.015756706191342</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.706846718492292</v>
+        <v>2.527608369052968</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.61855501133741</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.259068289643579</v>
+        <v>1.079829940204256</v>
       </c>
       <c r="F1980" t="n">
         <v>0.7098066993052106</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.132730738075418</v>
+        <v>2.953492388636095</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.71094442110292</v>
+        <v>2.531706071663597</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.573716609729012</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.281101352897567</v>
+        <v>1.101863003458244</v>
       </c>
       <c r="F1981" t="n">
         <v>0.71435013225008</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.139554500452968</v>
+        <v>2.960316151013645</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.715105360733998</v>
+        <v>2.535867011294675</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.59321506597102</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.277462910031842</v>
+        <v>1.098224560592518</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6662654909701757</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.114864655316104</v>
+        <v>2.93562630587678</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.720984963261835</v>
+        <v>2.541746613822512</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.54901222888512</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.301023647394039</v>
+        <v>1.121785297954716</v>
       </c>
       <c r="F1983" t="n">
         <v>0.7104683280560762</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.147265960095481</v>
+        <v>2.968027610656158</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.719394963731083</v>
+        <v>2.540156614291759</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.585991256548563</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.284642036797909</v>
+        <v>1.105403687358586</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7474422298474067</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.167860301639527</v>
+        <v>2.988621952200204</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.770642728914122</v>
+        <v>2.591404379474799</v>
       </c>
       <c r="D1985" t="n">
         <v>-3.427699839009291</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.399206368996658</v>
+        <v>1.219968019557335</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7474422298474067</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.219108066822567</v>
+        <v>3.039869717383243</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.769083433508376</v>
+        <v>2.589845084069052</v>
       </c>
       <c r="D1986" t="n">
         <v>-3.220057835374815</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.480703875044702</v>
+        <v>1.301465525605378</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9550842334818829</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.342133973597505</v>
+        <v>3.162895624158182</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.764031661746646</v>
+        <v>2.584793312307322</v>
       </c>
       <c r="D1987" t="n">
         <v>-3.169025742652287</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.496064940371983</v>
+        <v>1.31682659093266</v>
       </c>
       <c r="F1987" t="n">
         <v>1.006116326204411</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.367701457469293</v>
+        <v>3.188463108029969</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.781219065839351</v>
+        <v>2.601980716400027</v>
       </c>
       <c r="D1988" t="n">
         <v>-3.103801561525081</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.53934201691557</v>
+        <v>1.360103667476247</v>
       </c>
       <c r="F1988" t="n">
         <v>1.071340507331616</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.42402337023832</v>
+        <v>3.244785020798997</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.777180038138631</v>
+        <v>2.597941688699307</v>
       </c>
       <c r="D1989" t="n">
         <v>-3.066374541453948</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.550273797243304</v>
+        <v>1.37103544780398</v>
       </c>
       <c r="F1989" t="n">
         <v>1.076592045360798</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.42313526535511</v>
+        <v>3.243896915915786</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.778436830469871</v>
+        <v>2.599198481030548</v>
       </c>
       <c r="D1990" t="n">
         <v>-3.086486197488656</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.543485927160661</v>
+        <v>1.364247577721337</v>
       </c>
       <c r="F1990" t="n">
         <v>1.087619390358217</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.431008464684802</v>
+        <v>3.251770115245479</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.938994601491082</v>
+        <v>2.759756252051758</v>
       </c>
       <c r="D1991" t="n">
         <v>-3.032741383061451</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.725541623952753</v>
+        <v>1.54630327451343</v>
       </c>
       <c r="F1991" t="n">
         <v>1.097682699798679</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.59760422137029</v>
+        <v>3.418365871930966</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.059107510708899</v>
+        <v>2.879869161269576</v>
       </c>
       <c r="D1992" t="n">
         <v>-2.957959122036439</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.875567437580576</v>
+        <v>1.696329088141252</v>
       </c>
       <c r="F1992" t="n">
         <v>1.172464960823692</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.762586487203115</v>
+        <v>3.583348137763791</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.050815486722758</v>
+        <v>2.871577137283435</v>
       </c>
       <c r="D1993" t="n">
         <v>-2.931875037772631</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.877709047299958</v>
+        <v>1.698470697860635</v>
       </c>
       <c r="F1993" t="n">
         <v>1.172464960823692</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.754294463216973</v>
+        <v>3.57505611377765</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.049008682306538</v>
+        <v>2.869770332867214</v>
       </c>
       <c r="D1994" t="n">
         <v>-2.84399712466351</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.911053408127386</v>
+        <v>1.731815058688062</v>
       </c>
       <c r="F1994" t="n">
         <v>1.288390603247043</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.822043044254764</v>
+        <v>3.64280469481544</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.066563088033329</v>
+        <v>2.887324738594006</v>
       </c>
       <c r="D1995" t="n">
         <v>-2.835104663270227</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.93216479841149</v>
+        <v>1.752926448972167</v>
       </c>
       <c r="F1995" t="n">
         <v>1.288390603247043</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.839597449981555</v>
+        <v>3.660359100542232</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.058418135437913</v>
+        <v>2.879179785998589</v>
       </c>
       <c r="D1996" t="n">
         <v>-3.003580780240104</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.856629399028123</v>
+        <v>1.6773910495888</v>
       </c>
       <c r="F1996" t="n">
         <v>1.260442767530462</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.814683795956191</v>
+        <v>3.635445446516867</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.039687832625775</v>
+        <v>2.860449483186451</v>
       </c>
       <c r="D1997" t="n">
         <v>-2.305781251378521</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.117018907760619</v>
+        <v>1.937780558321295</v>
       </c>
       <c r="F1997" t="n">
         <v>1.190094708160052</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.753744657521806</v>
+        <v>3.574506308082483</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.030351855122679</v>
+        <v>2.851113505683356</v>
       </c>
       <c r="D1998" t="n">
         <v>-2.283060147695369</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.116771371730784</v>
+        <v>1.93753302229146</v>
       </c>
       <c r="F1998" t="n">
         <v>1.190094708160052</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.744408680018711</v>
+        <v>3.565170330579387</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.189257980973848</v>
+        <v>3.010019631534525</v>
       </c>
       <c r="D1999" t="n">
         <v>-2.412261960989411</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.223996772264336</v>
+        <v>2.044758422825013</v>
       </c>
       <c r="F1999" t="n">
         <v>1.060892894866009</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.825793717893454</v>
+        <v>3.646555368454131</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.226335803467495</v>
+        <v>3.047097454028171</v>
       </c>
       <c r="D2000" t="n">
         <v>-2.567042967767667</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.19916219204668</v>
+        <v>2.019923842607357</v>
       </c>
       <c r="F2000" t="n">
         <v>1.027525220811533</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.842850935954415</v>
+        <v>3.663612586515092</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.22301115945704</v>
+        <v>3.043772810017717</v>
       </c>
       <c r="D2001" t="n">
         <v>-2.559988277552493</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.198659424122295</v>
+        <v>2.019421074682971</v>
       </c>
       <c r="F2001" t="n">
         <v>1.034579911026707</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.843759106073064</v>
+        <v>3.664520756633741</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.233017313101782</v>
+        <v>3.053778963662458</v>
       </c>
       <c r="D2002" t="n">
         <v>-2.533037053226005</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.219446067497632</v>
+        <v>2.040207718058308</v>
       </c>
       <c r="F2002" t="n">
         <v>1.049460257054426</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.862693467334438</v>
+        <v>3.683455117895114</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.417120445246741</v>
+        <v>3.237882095807418</v>
       </c>
       <c r="D2003" t="n">
         <v>-2.668990061282321</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.349167996420065</v>
+        <v>2.169929646980742</v>
       </c>
       <c r="F2003" t="n">
         <v>1.049460257054426</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.046796599479397</v>
+        <v>3.867558250040074</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.409237140149735</v>
+        <v>3.229998790710411</v>
       </c>
       <c r="D2004" t="n">
         <v>-2.691398179087193</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.332321444201109</v>
+        <v>2.153083094761786</v>
       </c>
       <c r="F2004" t="n">
         <v>1.049460257054426</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.03891329438239</v>
+        <v>3.859674944943067</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.411291139699372</v>
+        <v>3.232052790260048</v>
       </c>
       <c r="D2005" t="n">
         <v>-2.719622414664794</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.323085749519707</v>
+        <v>2.143847400080383</v>
       </c>
       <c r="F2005" t="n">
         <v>1.067437009505735</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.051753345402813</v>
+        <v>3.87251499596349</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.467544857421219</v>
+        <v>3.288306507981896</v>
       </c>
       <c r="D2006" t="n">
         <v>-2.729063340553324</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.375563096886141</v>
+        <v>2.196324747446818</v>
       </c>
       <c r="F2006" t="n">
         <v>1.189864127049126</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.181463333650695</v>
+        <v>4.002224984211372</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.47043595196652</v>
+        <v>3.291197602527197</v>
       </c>
       <c r="D2007" t="n">
         <v>-2.781336947888965</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.357544748497186</v>
+        <v>2.178306399057862</v>
       </c>
       <c r="F2007" t="n">
         <v>1.137590519713485</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.152990263794611</v>
+        <v>3.973751914355288</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.468547764860295</v>
+        <v>3.289309415420972</v>
       </c>
       <c r="D2008" t="n">
         <v>-2.857666925489871</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.325124570350598</v>
+        <v>2.145886220911275</v>
       </c>
       <c r="F2008" t="n">
         <v>1.137590519713485</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.151102076688386</v>
+        <v>3.971863727249063</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.463367994463157</v>
+        <v>3.284129645023834</v>
       </c>
       <c r="D2009" t="n">
         <v>-3.059920645814224</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.23904331182372</v>
+        <v>2.059804962384396</v>
       </c>
       <c r="F2009" t="n">
         <v>0.9353367993891315</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.024570074096637</v>
+        <v>3.845331724657313</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.46180200467331</v>
+        <v>3.282563655233986</v>
       </c>
       <c r="D2010" t="n">
         <v>-3.221489071341479</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.17284995182297</v>
+        <v>1.993611602383647</v>
       </c>
       <c r="F2010" t="n">
         <v>0.8085538755912521</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.946934330028061</v>
+        <v>3.767695980588738</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.474875411539228</v>
+        <v>3.295637062099905</v>
       </c>
       <c r="D2011" t="n">
         <v>-3.353790363439033</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.133002841849867</v>
+        <v>1.953764492410544</v>
       </c>
       <c r="F2011" t="n">
         <v>0.8085538755912521</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.96000773689398</v>
+        <v>3.780769387454657</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.466880608322168</v>
+        <v>3.287642258882845</v>
       </c>
       <c r="D2012" t="n">
         <v>-3.539658674278263</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.050660714297115</v>
+        <v>1.871422364857792</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6499882822713045</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.856873577684951</v>
+        <v>3.677635228245628</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.46540464944917</v>
+        <v>3.286166300009847</v>
       </c>
       <c r="D2013" t="n">
         <v>-3.567559461387736</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.038024440580328</v>
+        <v>1.858786091141005</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6153913581283696</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.834639464326192</v>
+        <v>3.655401114886869</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.462169093426369</v>
+        <v>3.282930743987046</v>
       </c>
       <c r="D2014" t="n">
         <v>-3.69008556409063</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.985778443476369</v>
+        <v>1.806540094037046</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4928652554254758</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.757888246681655</v>
+        <v>3.578649897242332</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.528875053016873</v>
+        <v>3.349636703577549</v>
       </c>
       <c r="D2015" t="n">
         <v>-3.920600060276218</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.960278604592638</v>
+        <v>1.781040255153314</v>
       </c>
       <c r="F2015" t="n">
         <v>0.262350759239887</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.686285508560805</v>
+        <v>3.507047159121482</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.66918677201872</v>
+        <v>3.489948422579396</v>
       </c>
       <c r="D2016" t="n">
         <v>-4.177320878271042</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.997901996396555</v>
+        <v>1.818663646957232</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1539361850960722</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.761548483076364</v>
+        <v>3.58231013363704</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.73816704116436</v>
+        <v>3.558928691725036</v>
       </c>
       <c r="D2017" t="n">
         <v>-4.331307296047182</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.005287698431739</v>
+        <v>1.826049348992415</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1539361850960722</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.830528752222004</v>
+        <v>3.65129040278268</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.724218243284481</v>
+        <v>3.544979893845157</v>
       </c>
       <c r="D2018" t="n">
         <v>-4.280785392219516</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.011547662082926</v>
+        <v>1.832309312643603</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1539361850960722</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.816579954342124</v>
+        <v>3.637341604902801</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.736088732339895</v>
+        <v>3.556850382900571</v>
       </c>
       <c r="D2019" t="n">
         <v>-4.533260546227241</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.92242808953525</v>
+        <v>1.743189740095927</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1539361850960722</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.828450443397538</v>
+        <v>3.649212093958215</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.737299266858838</v>
+        <v>3.558060917419515</v>
       </c>
       <c r="D2020" t="n">
         <v>-4.826156302706653</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.806480321462429</v>
+        <v>1.627241972023106</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1539361850960722</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.829660977916482</v>
+        <v>3.650422628477159</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74142100908616</v>
+        <v>3.562182659646836</v>
       </c>
       <c r="D2021" t="n">
         <v>-4.983700374436094</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.747584434997974</v>
+        <v>1.56834608555865</v>
       </c>
       <c r="F2021" t="n">
         <v>0.08703437995579771</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.793641637059638</v>
+        <v>3.614403287620315</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.736498861822349</v>
+        <v>3.557260512383026</v>
       </c>
       <c r="D2022" t="n">
         <v>-5.261664770019368</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.631476529500854</v>
+        <v>1.45223818006153</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.00258535432968654</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.734947649224537</v>
+        <v>3.555709299785214</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.898702918521393</v>
+        <v>3.71946456908207</v>
       </c>
       <c r="D2023" t="n">
         <v>-5.378632462658259</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.746893509144342</v>
+        <v>1.567655159705018</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.00258535432968654</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.897151705923582</v>
+        <v>3.717913356484258</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.893549556485207</v>
+        <v>3.714311207045884</v>
       </c>
       <c r="D2024" t="n">
         <v>-5.463350404879212</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.707852970219775</v>
+        <v>1.528614620780451</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.08770138325773291</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.840928726530568</v>
+        <v>3.661690377091245</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.903778974053699</v>
+        <v>3.724540624614375</v>
       </c>
       <c r="D2025" t="n">
         <v>-5.545285223148095</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.685308460480712</v>
+        <v>1.506070111041389</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.0976361288448131</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.845197296746811</v>
+        <v>3.665958947307487</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.912704612509601</v>
+        <v>3.733466263070278</v>
       </c>
       <c r="D2026" t="n">
         <v>-5.647261345396503</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.653443650037252</v>
+        <v>1.474205300597928</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.1996122510932207</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.792937261853669</v>
+        <v>3.613698912414345</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.904857499753776</v>
+        <v>3.725619150314453</v>
       </c>
       <c r="D2027" t="n">
         <v>-5.537255061919281</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.689599050672316</v>
+        <v>1.510360701232992</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.1764076791759455</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.799012892248209</v>
+        <v>3.619774542808886</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.909107510475751</v>
+        <v>3.729869161036427</v>
       </c>
       <c r="D2028" t="n">
         <v>-5.394195486178356</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.75107289169066</v>
+        <v>1.571834542251337</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.1683942525859662</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.808070958924171</v>
+        <v>3.628832609484848</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.737130043918963</v>
       </c>
       <c r="D2029" t="n">
         <v>-5.092748760706518</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.878912464761931</v>
+        <v>1.699674115322608</v>
       </c>
       <c r="F2029" t="n">
         <v>0.1330524728858711</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.99619987708981</v>
+        <v>3.816961527650486</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.738101221671674</v>
       </c>
       <c r="D2030" t="n">
         <v>-5.117339004941702</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.870047544820568</v>
+        <v>1.690809195381245</v>
       </c>
       <c r="F2030" t="n">
         <v>0.1330524728858711</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.997171054842521</v>
+        <v>3.817932705403197</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.738944126051429</v>
       </c>
       <c r="D2031" t="n">
         <v>-5.066300628935182</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.891305799602931</v>
+        <v>1.712067450163608</v>
       </c>
       <c r="F2031" t="n">
         <v>0.1330524728858711</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.998013959222275</v>
+        <v>3.818775609782952</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.757982224925575</v>
       </c>
       <c r="D2032" t="n">
         <v>-5.025161334068551</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.926799616423729</v>
+        <v>1.747561266984406</v>
       </c>
       <c r="F2032" t="n">
         <v>0.1741917677525019</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.0417356350164</v>
+        <v>3.862497285577076</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.574166221049509</v>
       </c>
       <c r="D2033" t="n">
         <v>-4.914555193988949</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.787226068579505</v>
+        <v>1.607987719140182</v>
       </c>
       <c r="F2033" t="n">
         <v>0.2847979078321039</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.924283315188095</v>
+        <v>3.745044965748772</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.577668265123473</v>
       </c>
       <c r="D2034" t="n">
         <v>-5.045135928519792</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.738495818841131</v>
+        <v>1.559257469401809</v>
       </c>
       <c r="F2034" t="n">
         <v>0.1542171733012614</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.849436918543553</v>
+        <v>3.67019856910423</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.562095084199556</v>
       </c>
       <c r="D2035" t="n">
         <v>-4.88063959432883</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.788721171593599</v>
+        <v>1.609482822154276</v>
       </c>
       <c r="F2035" t="n">
         <v>0.1542171733012614</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.833863737619636</v>
+        <v>3.654625388180313</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.561282794635986</v>
       </c>
       <c r="D2036" t="n">
         <v>-4.908009527013262</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.776960908956255</v>
+        <v>1.597722559516933</v>
       </c>
       <c r="F2036" t="n">
         <v>0.1542171733012614</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.833051448056065</v>
+        <v>3.653813098616743</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.571151573761058</v>
       </c>
       <c r="D2037" t="n">
         <v>-4.918394721903152</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.782675610125372</v>
+        <v>1.60343726068605</v>
       </c>
       <c r="F2037" t="n">
         <v>0.1438319784113721</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.836689110247204</v>
+        <v>3.657450760807882</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.641988579537483</v>
       </c>
       <c r="D2038" t="n">
         <v>-4.936982880625377</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.846077352412907</v>
+        <v>1.666839002973585</v>
       </c>
       <c r="F2038" t="n">
         <v>0.1252438196891467</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.896373220790294</v>
+        <v>3.717134871350972</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.638857590355782</v>
       </c>
       <c r="D2039" t="n">
         <v>-4.937281427321413</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.842826944552791</v>
+        <v>1.663588595113469</v>
       </c>
       <c r="F2039" t="n">
         <v>0.1252438196891467</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.893242231608593</v>
+        <v>3.71400388216927</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.643388485295173</v>
       </c>
       <c r="D2040" t="n">
         <v>-4.836458293630985</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.887687092968354</v>
+        <v>1.708448743529031</v>
       </c>
       <c r="F2040" t="n">
         <v>0.1377080351735006</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.905251655838597</v>
+        <v>3.726013306399274</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.643517738773717</v>
       </c>
       <c r="D2041" t="n">
         <v>-4.645676932878578</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.96412889074786</v>
+        <v>1.784890541308537</v>
       </c>
       <c r="F2041" t="n">
         <v>0.3284893959259079</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.019849725768585</v>
+        <v>3.840611376329262</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.623354584511313</v>
       </c>
       <c r="D2042" t="n">
         <v>-4.627160078836758</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.951372478102185</v>
+        <v>1.772134128662862</v>
       </c>
       <c r="F2042" t="n">
         <v>0.3414195253511161</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.007444649161306</v>
+        <v>3.828206299721983</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.658321521123372</v>
       </c>
       <c r="D2043" t="n">
         <v>-4.601966894335439</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.99641668851477</v>
+        <v>1.817178339075448</v>
       </c>
       <c r="F2043" t="n">
         <v>0.3666127098524345</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.057527496474155</v>
+        <v>3.878289147034832</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.652008089024809</v>
       </c>
       <c r="D2044" t="n">
         <v>-4.589912767422477</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.994924907181393</v>
+        <v>1.815686557742071</v>
       </c>
       <c r="F2044" t="n">
         <v>0.3786668367653973</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.05844654052337</v>
+        <v>3.879208191084048</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.653888719208945</v>
       </c>
       <c r="D2045" t="n">
         <v>-4.596536014112835</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.994156238689386</v>
+        <v>1.814917889250063</v>
       </c>
       <c r="F2045" t="n">
         <v>0.372043590075039</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.056353222693291</v>
+        <v>3.877114873253969</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.666739745086828</v>
       </c>
       <c r="D2046" t="n">
         <v>-4.493655424584242</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.048159500378706</v>
+        <v>1.868921150939383</v>
       </c>
       <c r="F2046" t="n">
         <v>0.4749241796036319</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.13093260228833</v>
+        <v>3.951694252849007</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.686942415260422</v>
       </c>
       <c r="D2047" t="n">
         <v>-4.517097463764329</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.058985354880265</v>
+        <v>1.879747005440942</v>
       </c>
       <c r="F2047" t="n">
         <v>0.4749241796036319</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.151135272461924</v>
+        <v>3.971896923022602</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.686942415260422</v>
       </c>
       <c r="D2048" t="n">
         <v>-4.53516997205594</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.05175635156362</v>
+        <v>1.872518002124298</v>
       </c>
       <c r="F2048" t="n">
         <v>0.4749241796036319</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.151135272461924</v>
+        <v>3.971896923022602</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.88902175309763</v>
+        <v>3.846386257095995</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.647194328853888</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.690737687042696</v>
+        <v>-4.714906277451456</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.949781179162385</v>
+        <v>1.760875393559558</v>
       </c>
       <c r="F2049" t="n">
         <v>0.4749241796036319</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.11138718605539</v>
+        <v>3.932148836616068</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240808.xlsx
+++ b/tame_output/ON/bt/strategyON_20240808.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>126.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>435.0%</t>
+          <t>433.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-633.1%</t>
+          <t>-647.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,42 +1155,42 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-200.1%</t>
+          <t>-205.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-1422.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.0%</t>
+          <t>-149.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-176.5%</t>
+          <t>-182.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-52.8%</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045691</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279811</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386091</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.367370539998558</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706666</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537423</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.272760131382188</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006528</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330517</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>2.971988151156609</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.895633554317592</v>
+        <v>-6.950154596319519</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2133783051158238</v>
+        <v>0.1915698883150529</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4677072284042083</v>
+        <v>-0.5222282704061352</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.691363814114084</v>
+        <v>2.658651188912928</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>2.974803211844245</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.73989522175785</v>
+        <v>-6.794416263759777</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2784886988273572</v>
+        <v>0.2566802820265868</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3119688958444667</v>
+        <v>-0.3664899378463936</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.787621874337566</v>
+        <v>2.754909249136409</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>2.987709553067904</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.490895423074269</v>
+        <v>-6.545416465076196</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3909949595244484</v>
+        <v>0.3691865427236776</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06296909716088606</v>
+        <v>-0.1174901391628129</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.949928094771373</v>
+        <v>2.917215469570217</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.859733623468685</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.596485412847374</v>
+        <v>-6.6510064548493</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2207830340159873</v>
+        <v>0.1989746172152169</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1685590869339904</v>
+        <v>-0.2230801289359173</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.758598171308291</v>
+        <v>2.725885546107135</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.908277965345771</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.615220314965971</v>
+        <v>-6.669741356967897</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.261833415045635</v>
+        <v>0.2400249982448646</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1741550965941217</v>
+        <v>-0.2286761385960486</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.803784907389299</v>
+        <v>2.771072282188142</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.788399042657604</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.467280273558371</v>
+        <v>-6.521801315560298</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2011305089205071</v>
+        <v>0.1793220921197367</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1538341806855641</v>
+        <v>-0.208355222687491</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.696098534246266</v>
+        <v>2.663385909045109</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.779685056404126</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.414310751304383</v>
+        <v>-6.468831793306309</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2136043315686242</v>
+        <v>0.1917959147678538</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1553857004335021</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.719166261345181</v>
+        <v>2.686453636144024</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.772724444309032</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.248522555344092</v>
+        <v>-6.303043597346019</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2729589978576477</v>
+        <v>0.2511505810568768</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1553857004335021</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.712205649250087</v>
+        <v>2.679493024048931</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.787186798690175</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.215159348865323</v>
+        <v>-6.26968039086725</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.300766634830298</v>
+        <v>0.2789582180295276</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1553857004335021</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.726668003631231</v>
+        <v>2.693955378430074</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.781718919149371</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.106900211742802</v>
+        <v>-6.161421253744728</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3386024101385017</v>
+        <v>0.3167939933377313</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1553857004335021</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.721200124090426</v>
+        <v>2.688487498889269</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.779217013159947</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.983609076925671</v>
+        <v>-6.038130118927597</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3854169580759312</v>
+        <v>0.3636085412751604</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.02242647638555523</v>
+        <v>-0.03209456561637164</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.792672898991281</v>
+        <v>2.759960273790125</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.786917991397273</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.962459878022227</v>
+        <v>-6.016980920024154</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4015776158746336</v>
+        <v>0.3797691990738628</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.01094536671292828</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.813063396570672</v>
+        <v>2.780350771369516</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.782698699744323</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.718694436038783</v>
+        <v>-5.77321547804071</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4948645010150621</v>
+        <v>0.4730560842142912</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.01094536671292828</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.808844104917723</v>
+        <v>2.776131479716566</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.784823013664339</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.616931615761488</v>
+        <v>-5.671452657763415</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5376939430459959</v>
+        <v>0.5158855262452255</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.05679474368142728</v>
+        <v>0.002273701679500417</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.818899859873196</v>
+        <v>2.78618723467204</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.777565088648041</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.367081221812414</v>
+        <v>-5.42160226381434</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.630376175609328</v>
+        <v>0.6085677588085572</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.05679474368142728</v>
+        <v>0.002273701679500417</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.811641934856898</v>
+        <v>2.778929309655742</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.78116421216869</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.191189129344981</v>
+        <v>-5.245710171346907</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7043321361169501</v>
+        <v>0.6825237193161793</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.05679474368142728</v>
+        <v>0.002273701679500417</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.815241058377547</v>
+        <v>2.782528433176391</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.794491718223244</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.019742666322517</v>
+        <v>-5.074263708324444</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7862382273804891</v>
+        <v>0.7644298105797183</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2282412067038904</v>
+        <v>0.1737201647019636</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.931436442245579</v>
+        <v>2.898723817044422</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.793512195839541</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.945453100584178</v>
+        <v>-4.999974142586105</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8149745312921217</v>
+        <v>0.7931661144913509</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3025307724422297</v>
+        <v>0.2480097304403028</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.975030659304879</v>
+        <v>2.942318034103723</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.798206996893858</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.881817358350244</v>
+        <v>-4.93633840035217</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8451236292400126</v>
+        <v>0.823315212439242</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.3116454726742374</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.017906905699557</v>
+        <v>2.985194280498401</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.779401255677654</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.770390599024323</v>
+        <v>-4.82491164102625</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8708885917541764</v>
+        <v>0.8490801749534058</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.3116454726742374</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.999101164483353</v>
+        <v>2.966388539282196</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.781144332302531</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.780893222089612</v>
+        <v>-4.835414264091539</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8684306191529383</v>
+        <v>0.8466222023521675</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.3011428496089485</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.994542667269056</v>
+        <v>2.9618300420679</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.785073646137351</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.708650653918418</v>
+        <v>-4.763171695920344</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9012569602562364</v>
+        <v>0.8794485434554655</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.3011428496089485</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.998471981103877</v>
+        <v>2.965759355902721</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.785752230054691</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.690936967040552</v>
+        <v>-4.745458009042479</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9090210189247223</v>
+        <v>0.8872126021239517</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.3043241785058653</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.001059362359367</v>
+        <v>2.968346737158211</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.782750301274685</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.582132081560825</v>
+        <v>-4.636653123562752</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9495410443366068</v>
+        <v>0.927732627535836</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.3043241785058653</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.99805743357936</v>
+        <v>2.965344808378204</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.784329338285299</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.362111283523815</v>
+        <v>-4.416632325525741</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.039128400562025</v>
+        <v>1.017319983761254</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.4455440235738455</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.084368377630763</v>
+        <v>3.051655752429606</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.800223521087122</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.229243594460537</v>
+        <v>-4.283764636462464</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.108169658989159</v>
+        <v>1.086361242188389</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.4455440235738455</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.100262560432586</v>
+        <v>3.06754993523143</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.801369365527424</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.109070511096038</v>
+        <v>-4.163591553097965</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.157384736775261</v>
+        <v>1.13557631997449</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6202381489402713</v>
+        <v>0.5657171069383444</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.173512254891587</v>
+        <v>3.140799629690431</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.811457468088864</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.973817149766061</v>
+        <v>-4.028338191767988</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.221574183868692</v>
+        <v>1.199765767067921</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7554915102702484</v>
+        <v>0.7009704682683215</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.264752374251013</v>
+        <v>3.232039749049857</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.79749495949029</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.033691977123754</v>
+        <v>-4.08821301912568</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.18366174432704</v>
+        <v>1.16185332752627</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.6410956409106294</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.214864969237824</v>
+        <v>3.182152344036668</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.812784128724498</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.913871746212916</v>
+        <v>-3.968392788214843</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.246879005925584</v>
+        <v>1.225070589124813</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.6410956409106294</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.230154138472032</v>
+        <v>3.197441513270876</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.72042832804694</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.916341452674722</v>
+        <v>-3.970862494676649</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.153535322663303</v>
+        <v>1.131726905862532</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6931469764507501</v>
+        <v>0.6386259344488232</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.13631651391739</v>
+        <v>3.103603888716234</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003597</v>
       </c>
       <c r="C1936" t="n">
         <v>2.639690189532241</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.984711638998732</v>
+        <v>-4.039232681000659</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.045449109619001</v>
+        <v>1.02364069281823</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6479016334850382</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.06114379482442</v>
+        <v>3.028431169623265</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.630126898164133</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.998499691845779</v>
+        <v>-4.053020733847705</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.030370597112073</v>
+        <v>1.008562180311303</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6479016334850382</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.051580503456312</v>
+        <v>3.018867878255156</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.767157734856335</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.054019767738368</v>
+        <v>-4.108540809740295</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.14519340344724</v>
+        <v>1.123384986646469</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6479016334850382</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.188611340148514</v>
+        <v>3.155898714947358</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.771724966848123</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.878545507945899</v>
+        <v>-3.933066549947826</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.219950339356015</v>
+        <v>1.198141922555245</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6479016334850382</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.193178572140302</v>
+        <v>3.160465946939146</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.74746699560933</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.989481760587148</v>
+        <v>-4.044002802589074</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.151317867060723</v>
+        <v>1.129509450259952</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6479016334850382</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.168920600901509</v>
+        <v>3.136207975700353</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.67600530901078</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.955818215114866</v>
+        <v>-4.010339257116792</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.093321598651085</v>
+        <v>1.071513181850315</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6815651789573201</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.117657041586328</v>
+        <v>3.084944416385172</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.686177695442912</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.895965595911143</v>
+        <v>-3.950486637913069</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.127435032764707</v>
+        <v>1.105626615963937</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6815651789573201</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.12782942801846</v>
+        <v>3.095116802817304</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.681123966016772</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.809722132884765</v>
+        <v>-3.864243174886691</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.156878688549118</v>
+        <v>1.135070271748348</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6815651789573201</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.122775698592321</v>
+        <v>3.090063073391164</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.672899741461298</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.855028952283745</v>
+        <v>-3.909549994285671</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.130531736234052</v>
+        <v>1.108723319433282</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.6407550159480893</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.090065376231308</v>
+        <v>3.057352751030152</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.673451614494399</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.884062056986047</v>
+        <v>-3.938583098987972</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.119470367386233</v>
+        <v>1.097661950585462</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.6407550159480893</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.09061724926441</v>
+        <v>3.057904624063253</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.602724306385765</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.791251575535187</v>
+        <v>-3.845772617537113</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.085867251857942</v>
+        <v>1.064058835057172</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7880865394008755</v>
+        <v>0.7335654973989486</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.07557623002629</v>
+        <v>3.042863604825135</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.604597782310366</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.835641044864615</v>
+        <v>-3.890162086866541</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.069984940050772</v>
+        <v>1.048176523250002</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7436970700714478</v>
+        <v>0.6891760280695209</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.050816024353235</v>
+        <v>3.018103399152078</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472735</v>
       </c>
       <c r="C1948" t="n">
         <v>2.599673490822089</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.952182649969958</v>
+        <v>-4.006703691971884</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.018444006520358</v>
+        <v>0.9966355897195873</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.5726344229641782</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.975966769801752</v>
+        <v>2.943254144600596</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.605164786652756</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.839805648787285</v>
+        <v>-3.894326690789212</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.068886102824094</v>
+        <v>1.047077686023324</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.5726344229641782</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.981458065632419</v>
+        <v>2.948745440431263</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.616661988421295</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.867586046688638</v>
+        <v>-3.922107088690565</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.069271145432092</v>
+        <v>1.047462728631321</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.599375067064752</v>
+        <v>0.5448540250628251</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.976287028660146</v>
+        <v>2.943574403458991</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.455017708421948</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.985966719418777</v>
+        <v>-4.040487761420703</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8602745963406897</v>
+        <v>0.8384661795399195</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.4776361729118489</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.774312037370214</v>
+        <v>2.741599412169058</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.575167369141154</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.094580797862108</v>
+        <v>-4.149101839864034</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.936978625682563</v>
+        <v>0.9151702088817928</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.4776361729118489</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.89446169808942</v>
+        <v>2.861749072888264</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.589680395243477</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.059171759613965</v>
+        <v>-4.113692801615891</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9656552670841432</v>
+        <v>0.9438468502833728</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.4776361729118489</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.908974724191743</v>
+        <v>2.876262098990586</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.587099836585846</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.020788097055814</v>
+        <v>-4.07530913905774</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9784281734497724</v>
+        <v>0.956619756649002</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.5160198354700001</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.929424363069002</v>
+        <v>2.896711737867846</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.583828865431148</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.843671767020648</v>
+        <v>-3.898192809022574</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.046003734309141</v>
+        <v>1.02419531750837</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.5160198354700001</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.926153391914304</v>
+        <v>2.893440766713148</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.584512257193061</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.888764011854193</v>
+        <v>-3.94328505385612</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.028650228137636</v>
+        <v>1.006841811336865</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5086448343025372</v>
+        <v>0.4541237923006103</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.889699157774583</v>
+        <v>2.856986532573427</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.578299232499475</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.709388590615426</v>
+        <v>-3.763909632617352</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.094187371939557</v>
+        <v>1.072378955138787</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6654215924732558</v>
+        <v>0.610900550471329</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.977552187983429</v>
+        <v>2.944839562782273</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.559106687831065</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.754402804136032</v>
+        <v>-3.808923846137958</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.056989141862904</v>
+        <v>1.035180725062134</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6350726971586512</v>
+        <v>0.5805516551567244</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.940150306126256</v>
+        <v>2.9074376809251</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.564798250170011</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.021407314408467</v>
+        <v>-4.075928356410394</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9558789000928758</v>
+        <v>0.9340704832921054</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4407096591157026</v>
+        <v>0.3861886171137758</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.829224045639433</v>
+        <v>2.796511420438276</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.564002172066512</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.12260509584564</v>
+        <v>-4.177126137847567</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9146037094145081</v>
+        <v>0.8927952926137377</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.3177798035684566</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.787382679408742</v>
+        <v>2.754670054207586</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.561602133620829</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.116094129231327</v>
+        <v>-4.170615171233254</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9148080576145499</v>
+        <v>0.8929996408137795</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.3177798035684566</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.784982640963059</v>
+        <v>2.752270015761903</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.558126852829074</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.09705600152403</v>
+        <v>-4.151577043525957</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9189480279057136</v>
+        <v>0.8971396111049434</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.259596192237262</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.746597193372587</v>
+        <v>2.713884568171431</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677421254463264</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.128182632674648</v>
+        <v>-4.182703674676575</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.025791777079657</v>
+        <v>1.003983360278886</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.259596192237262</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.865891595006778</v>
+        <v>2.833178969805622</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678254583449398</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.142049394008566</v>
+        <v>-4.196570436010493</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.021078401532223</v>
+        <v>0.9992699847314528</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.276259317505366</v>
+        <v>0.2217382755034391</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.844010173952618</v>
+        <v>2.811297548751461</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789117</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684263113846324</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.097245222468636</v>
+        <v>-4.151766264470563</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.045008600545121</v>
+        <v>1.023200183744351</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.276259317505366</v>
+        <v>0.2217382755034391</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.850018704349544</v>
+        <v>2.817306079148387</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519904</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582213335123523</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.949502252233634</v>
+        <v>-4.00402329423556</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.002056009916321</v>
+        <v>0.980247593115551</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.3895456327383223</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.848653339967673</v>
+        <v>2.815940714766517</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181166</v>
       </c>
       <c r="C1967" t="n">
         <v>2.585006956655004</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.033323473508332</v>
+        <v>-4.087844515510259</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9713211429379232</v>
+        <v>0.9495127261371528</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.3895456327383223</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.851446961499154</v>
+        <v>2.818734336297998</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585669305046662</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.027170767455548</v>
+        <v>-4.081691809457475</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9744445737506953</v>
+        <v>0.9526361569499249</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4502193807930334</v>
+        <v>0.3956983387911066</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.855800933522483</v>
+        <v>2.823088308321327</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890607</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584749781786773</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.04398006560605</v>
+        <v>-4.098501107607976</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9668013312306047</v>
+        <v>0.9449929144298344</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.3788890406406049</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.844795831372292</v>
+        <v>2.812083206171136</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>2.651085335583593</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.981682066829928</v>
+        <v>-4.036203108831854</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.058056084537874</v>
+        <v>1.036247667737104</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.3788890406406049</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.911131385169113</v>
+        <v>2.878418759967957</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453377337297721</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.77989186916477</v>
+        <v>-3.834412911166696</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9410641653180645</v>
+        <v>0.9192557485172945</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6314282748116862</v>
+        <v>0.5769072328097593</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.832234302184732</v>
+        <v>2.799521676983576</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.523667569619896</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.830778581850965</v>
+        <v>-3.885299623852891</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9909997125657619</v>
+        <v>0.9691912957649917</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5805415621254917</v>
+        <v>0.5260205201235648</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.871992506895191</v>
+        <v>2.839279881694035</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538295305735939</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.744167839201157</v>
+        <v>-3.798688881203084</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.040271745741729</v>
+        <v>1.018463328940958</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6591672933306499</v>
+        <v>0.6046462513287231</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.93379568173433</v>
+        <v>2.901083056533174</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536831286560611</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.804377137206442</v>
+        <v>-3.858898179208368</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.014724007364286</v>
+        <v>0.9929155905635163</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.5444369533234386</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.896206083755831</v>
+        <v>2.863493458554674</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.53532290460054</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.727955090774515</v>
+        <v>-3.782476132776441</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.043784443976986</v>
+        <v>1.021976027176215</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.5444369533234386</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.894697701795759</v>
+        <v>2.861985076594603</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.535185772035976</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.683581959135946</v>
+        <v>-3.738103001137873</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.061396564067849</v>
+        <v>1.039588147267079</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.643331126963934</v>
+        <v>0.5888100849620072</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.921184448214337</v>
+        <v>2.88847182301318</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529579566174566</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.706062309994831</v>
+        <v>-3.760583351996758</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.046798217862886</v>
+        <v>1.024989801062116</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.643331126963934</v>
+        <v>0.5888100849620072</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.915578242352927</v>
+        <v>2.882865617151771</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535961323202371</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.658406579433776</v>
+        <v>-3.712927621435702</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.072242267115113</v>
+        <v>1.050433850314343</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6909868575249897</v>
+        <v>0.6364658155230628</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.950553437717365</v>
+        <v>2.917840812516209</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569611</v>
       </c>
       <c r="C1979" t="n">
         <v>2.540853696577096</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.557888420935021</v>
+        <v>-3.612409462936947</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.117341903889339</v>
+        <v>1.095533487088569</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7915050160237442</v>
+        <v>0.7369839740218174</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.015756706191342</v>
+        <v>2.983044080990187</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557288</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527608369052968</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.61855501133741</v>
+        <v>-3.673076053339336</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.079829940204256</v>
+        <v>1.058021523403486</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7098066993052106</v>
+        <v>0.6552856573032837</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.953492388636095</v>
+        <v>2.920779763434938</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531706071663597</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.573716609729012</v>
+        <v>-3.628237651730938</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.101863003458244</v>
+        <v>1.080054586657474</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.71435013225008</v>
+        <v>0.6598290902481532</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.960316151013645</v>
+        <v>2.927603525812489</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535867011294675</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.59321506597102</v>
+        <v>-3.647736107972946</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.098224560592518</v>
+        <v>1.076416143791749</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6662654909701757</v>
+        <v>0.6117444489682489</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.93562630587678</v>
+        <v>2.902913680675624</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541746613822512</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.54901222888512</v>
+        <v>-3.603533270887046</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.121785297954716</v>
+        <v>1.099976881153946</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7104683280560762</v>
+        <v>0.6559472860541493</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.968027610656158</v>
+        <v>2.935314985455002</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265639</v>
       </c>
       <c r="C1984" t="n">
         <v>2.540156614291759</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.585991256548563</v>
+        <v>-3.640512298550489</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.105403687358586</v>
+        <v>1.083595270557816</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7474422298474067</v>
+        <v>0.6929211878454798</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.988621952200204</v>
+        <v>2.955909326999048</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591404379474799</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.427699839009291</v>
+        <v>-3.482220881011217</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.219968019557335</v>
+        <v>1.198159602756565</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7474422298474067</v>
+        <v>0.6929211878454798</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.039869717383243</v>
+        <v>3.007157092182087</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321016</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589845084069052</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.220057835374815</v>
+        <v>-3.274578877376741</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.301465525605378</v>
+        <v>1.279657108804608</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9550842334818829</v>
+        <v>0.900563191479956</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.162895624158182</v>
+        <v>3.130182998957026</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475132</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584793312307322</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.169025742652287</v>
+        <v>-3.223546784654213</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.31682659093266</v>
+        <v>1.29501817413189</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.006116326204411</v>
+        <v>0.951595284202484</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.188463108029969</v>
+        <v>3.155750482828813</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404847</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601980716400027</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.103801561525081</v>
+        <v>-3.158322603527007</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.360103667476247</v>
+        <v>1.338295250675477</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.071340507331616</v>
+        <v>1.01681946532969</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.244785020798997</v>
+        <v>3.212072395597841</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882551</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597941688699307</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.066374541453948</v>
+        <v>-3.120895583455873</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.37103544780398</v>
+        <v>1.34922703100321</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.076592045360798</v>
+        <v>1.022071003358871</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.243896915915786</v>
+        <v>3.21118429071463</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.599198481030548</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.086486197488656</v>
+        <v>-3.141007239490582</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.364247577721337</v>
+        <v>1.342439160920567</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.087619390358217</v>
+        <v>1.033098348356291</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.251770115245479</v>
+        <v>3.219057490044322</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.82866144563628</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759756252051758</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.032741383061451</v>
+        <v>-3.087262425063377</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.54630327451343</v>
+        <v>1.52449485771266</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.097682699798679</v>
+        <v>1.043161657796753</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.418365871930966</v>
+        <v>3.38565324672981</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957619</v>
       </c>
       <c r="C1992" t="n">
         <v>2.879869161269576</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.957959122036439</v>
+        <v>-3.012480164038364</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.696329088141252</v>
+        <v>1.674520671340482</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.172464960823692</v>
+        <v>1.117943918821765</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.583348137763791</v>
+        <v>3.550635512562635</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998749</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871577137283435</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.931875037772631</v>
+        <v>-2.986396079774556</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.698470697860635</v>
+        <v>1.676662281059865</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.172464960823692</v>
+        <v>1.117943918821765</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.57505611377765</v>
+        <v>3.542343488576494</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896922</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869770332867214</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.84399712466351</v>
+        <v>-2.898518166665436</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.731815058688062</v>
+        <v>1.710006641887292</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.288390603247043</v>
+        <v>1.233869561245116</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.64280469481544</v>
+        <v>3.610092069614284</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959851</v>
       </c>
       <c r="C1995" t="n">
         <v>2.887324738594006</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.835104663270227</v>
+        <v>-2.889625705272152</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.752926448972167</v>
+        <v>1.731118032171397</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.288390603247043</v>
+        <v>1.233869561245116</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.660359100542232</v>
+        <v>3.627646475341076</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945359</v>
       </c>
       <c r="C1996" t="n">
         <v>2.879179785998589</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.003580780240104</v>
+        <v>-3.05810182224203</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.6773910495888</v>
+        <v>1.65558263278803</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.260442767530462</v>
+        <v>1.205921725528536</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.635445446516867</v>
+        <v>3.602732821315711</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782701</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860449483186451</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.305781251378521</v>
+        <v>-2.360302293380447</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.937780558321295</v>
+        <v>1.915972141520525</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.190094708160052</v>
+        <v>1.135573666158125</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.574506308082483</v>
+        <v>3.541793682881327</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.78467134563263</v>
       </c>
       <c r="C1998" t="n">
         <v>2.851113505683356</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.283060147695369</v>
+        <v>-2.337581189697294</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.93753302229146</v>
+        <v>1.91572460549069</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.190094708160052</v>
+        <v>1.135573666158125</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.565170330579387</v>
+        <v>3.532457705378231</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777666</v>
       </c>
       <c r="C1999" t="n">
         <v>3.010019631534525</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.412261960989411</v>
+        <v>-2.466783002991337</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.044758422825013</v>
+        <v>2.022950006024243</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.060892894866009</v>
+        <v>1.006371852864083</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.646555368454131</v>
+        <v>3.613842743252975</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644406</v>
       </c>
       <c r="C2000" t="n">
         <v>3.047097454028171</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.567042967767667</v>
+        <v>-2.621564009769592</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.019923842607357</v>
+        <v>1.998115425806587</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.027525220811533</v>
+        <v>0.9730041788096067</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.663612586515092</v>
+        <v>3.630899961313935</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799956</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043772810017717</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.559988277552493</v>
+        <v>-2.614509319554419</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.019421074682971</v>
+        <v>1.997612657882201</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.034579911026707</v>
+        <v>0.9800588690247805</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.664520756633741</v>
+        <v>3.631808131432585</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331109</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053778963662458</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.533037053226005</v>
+        <v>-2.587558095227931</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.040207718058308</v>
+        <v>2.018399301257539</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.049460257054426</v>
+        <v>0.9949392150524996</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.683455117895114</v>
+        <v>3.650742492693958</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784101</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237882095807418</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.668990061282321</v>
+        <v>-2.723511103284247</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.169929646980742</v>
+        <v>2.148121230179972</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.049460257054426</v>
+        <v>0.9949392150524996</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.867558250040074</v>
+        <v>3.834845624838918</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714419</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229998790710411</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.691398179087193</v>
+        <v>-2.745919221089119</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.153083094761786</v>
+        <v>2.131274677961016</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.049460257054426</v>
+        <v>0.9949392150524996</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.859674944943067</v>
+        <v>3.826962319741911</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155026</v>
       </c>
       <c r="C2005" t="n">
         <v>3.232052790260048</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.719622414664794</v>
+        <v>-2.77414345666672</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.143847400080383</v>
+        <v>2.122038983279613</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.067437009505735</v>
+        <v>1.012915967503808</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.87251499596349</v>
+        <v>3.839802370762333</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161971</v>
       </c>
       <c r="C2006" t="n">
         <v>3.288306507981896</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.729063340553324</v>
+        <v>-2.78358438255525</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.196324747446818</v>
+        <v>2.174516330646048</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.189864127049126</v>
+        <v>1.1353430850472</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.002224984211372</v>
+        <v>3.969512359010215</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321628</v>
       </c>
       <c r="C2007" t="n">
         <v>3.291197602527197</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.781336947888965</v>
+        <v>-2.835857989890891</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.178306399057862</v>
+        <v>2.156497982257092</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.137590519713485</v>
+        <v>1.083069477711558</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.973751914355288</v>
+        <v>3.941039289154132</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347697</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289309415420972</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.857666925489871</v>
+        <v>-2.912187967491797</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.145886220911275</v>
+        <v>2.124077804110505</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.137590519713485</v>
+        <v>1.083069477711558</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.971863727249063</v>
+        <v>3.939151102047907</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887741</v>
       </c>
       <c r="C2009" t="n">
         <v>3.284129645023834</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.059920645814224</v>
+        <v>-3.11444168781615</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.059804962384396</v>
+        <v>2.037996545583626</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9353367993891315</v>
+        <v>0.8808157573872049</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.845331724657313</v>
+        <v>3.812619099456157</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.71289761234306</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282563655233986</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.221489071341479</v>
+        <v>-3.276010113343405</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.993611602383647</v>
+        <v>1.971803185582877</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8085538755912521</v>
+        <v>0.7540328335893255</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.767695980588738</v>
+        <v>3.734983355387582</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389343</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295637062099905</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.353790363439033</v>
+        <v>-3.408311405440958</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.953764492410544</v>
+        <v>1.931956075609774</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8085538755912521</v>
+        <v>0.7540328335893255</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.780769387454657</v>
+        <v>3.7480567622535</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378385</v>
       </c>
       <c r="C2012" t="n">
         <v>3.287642258882845</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.539658674278263</v>
+        <v>-3.594179716280189</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.871422364857792</v>
+        <v>1.849613948057022</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6499882822713045</v>
+        <v>0.5954672402693778</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.677635228245628</v>
+        <v>3.644922603044472</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006968</v>
       </c>
       <c r="C2013" t="n">
         <v>3.286166300009847</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.567559461387736</v>
+        <v>-3.622080503389661</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.858786091141005</v>
+        <v>1.836977674340235</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6153913581283696</v>
+        <v>0.560870316126443</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.655401114886869</v>
+        <v>3.622688489685713</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.68489577878738</v>
       </c>
       <c r="C2014" t="n">
         <v>3.282930743987046</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.69008556409063</v>
+        <v>-3.744606606092555</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.806540094037046</v>
+        <v>1.784731677236276</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4928652554254758</v>
+        <v>0.4383442134235491</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.578649897242332</v>
+        <v>3.545937272041175</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585931</v>
       </c>
       <c r="C2015" t="n">
         <v>3.349636703577549</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.920600060276218</v>
+        <v>-3.975121102278144</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.781040255153314</v>
+        <v>1.759231838352544</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.262350759239887</v>
+        <v>0.2078297172379604</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.507047159121482</v>
+        <v>3.474334533920326</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814658</v>
       </c>
       <c r="C2016" t="n">
         <v>3.489948422579396</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.177320878271042</v>
+        <v>-4.231841920272967</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.818663646957232</v>
+        <v>1.796855230156462</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1539361850960722</v>
+        <v>0.09941514309414556</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.58231013363704</v>
+        <v>3.549597508435884</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237089</v>
       </c>
       <c r="C2017" t="n">
         <v>3.558928691725036</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.331307296047182</v>
+        <v>-4.385828338049108</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.826049348992415</v>
+        <v>1.804240932191645</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1539361850960722</v>
+        <v>0.09941514309414556</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.65129040278268</v>
+        <v>3.618577777581524</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423381</v>
       </c>
       <c r="C2018" t="n">
         <v>3.544979893845157</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.280785392219516</v>
+        <v>-4.335306434221442</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.832309312643603</v>
+        <v>1.810500895842833</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1539361850960722</v>
+        <v>0.09941514309414556</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.637341604902801</v>
+        <v>3.604628979701645</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609746</v>
       </c>
       <c r="C2019" t="n">
         <v>3.556850382900571</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.533260546227241</v>
+        <v>-4.587781588229166</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.743189740095927</v>
+        <v>1.721381323295157</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1539361850960722</v>
+        <v>0.09941514309414556</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.649212093958215</v>
+        <v>3.616499468757059</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973151</v>
       </c>
       <c r="C2020" t="n">
         <v>3.558060917419515</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.826156302706653</v>
+        <v>-4.880677344708579</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.627241972023106</v>
+        <v>1.605433555222336</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1539361850960722</v>
+        <v>0.09941514309414556</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.650422628477159</v>
+        <v>3.617710003276002</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251939</v>
       </c>
       <c r="C2021" t="n">
         <v>3.562182659646836</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.983700374436094</v>
+        <v>-5.03822141643802</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.56834608555865</v>
+        <v>1.54653766875788</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08703437995579771</v>
+        <v>0.03251333795387107</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.614403287620315</v>
+        <v>3.581690662419159</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916196</v>
       </c>
       <c r="C2022" t="n">
         <v>3.557260512383026</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.261664770019368</v>
+        <v>-5.316185812021294</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.45223818006153</v>
+        <v>1.430429763260761</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.00258535432968654</v>
+        <v>-0.05710639633161319</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.555709299785214</v>
+        <v>3.522996674584058</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830322</v>
       </c>
       <c r="C2023" t="n">
         <v>3.71946456908207</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.378632462658259</v>
+        <v>-5.433153504660185</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.567655159705018</v>
+        <v>1.545846742904248</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.00258535432968654</v>
+        <v>-0.05710639633161319</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.717913356484258</v>
+        <v>3.685200731283102</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071545</v>
       </c>
       <c r="C2024" t="n">
         <v>3.714311207045884</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.463350404879212</v>
+        <v>-5.517871446881138</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.528614620780451</v>
+        <v>1.506806203979681</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.08770138325773291</v>
+        <v>-0.1422224252596596</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.661690377091245</v>
+        <v>3.628977751890088</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.724540624614375</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.545285223148095</v>
+        <v>-5.599806265150021</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.506070111041389</v>
+        <v>1.484261694240619</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.0976361288448131</v>
+        <v>-0.1521571708467397</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.665958947307487</v>
+        <v>3.633246322106332</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332685</v>
       </c>
       <c r="C2026" t="n">
         <v>3.733466263070278</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.647261345396503</v>
+        <v>-5.701782387398429</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.474205300597928</v>
+        <v>1.452396883797158</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1996122510932207</v>
+        <v>-0.2541332930951473</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.613698912414345</v>
+        <v>3.580986287213189</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231802</v>
       </c>
       <c r="C2027" t="n">
         <v>3.725619150314453</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.537255061919281</v>
+        <v>-5.591776103921207</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.510360701232992</v>
+        <v>1.488552284432223</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1764076791759455</v>
+        <v>-0.2309287211778721</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.619774542808886</v>
+        <v>3.58706191760773</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818515</v>
       </c>
       <c r="C2028" t="n">
         <v>3.729869161036427</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.394195486178356</v>
+        <v>-5.448716528180282</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.571834542251337</v>
+        <v>1.550026125450567</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1683942525859662</v>
+        <v>-0.2229152945878928</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.628832609484848</v>
+        <v>3.596119984283692</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
         <v>3.737130043918963</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.092748760706518</v>
+        <v>-5.147269802708444</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.699674115322608</v>
+        <v>1.677865698521838</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1330524728858711</v>
+        <v>0.07853143088394443</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.816961527650486</v>
+        <v>3.78424890244933</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
         <v>3.738101221671674</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.117339004941702</v>
+        <v>-5.171860046943628</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.690809195381245</v>
+        <v>1.669000778580475</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1330524728858711</v>
+        <v>0.07853143088394443</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.817932705403197</v>
+        <v>3.785220080202041</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474154</v>
       </c>
       <c r="C2031" t="n">
         <v>3.738944126051429</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.066300628935182</v>
+        <v>-5.120821670937108</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.712067450163608</v>
+        <v>1.690259033362838</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1330524728858711</v>
+        <v>0.07853143088394443</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.818775609782952</v>
+        <v>3.786062984581796</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969537</v>
       </c>
       <c r="C2032" t="n">
         <v>3.757982224925575</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.025161334068551</v>
+        <v>-5.079682376070477</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.747561266984406</v>
+        <v>1.725752850183636</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1741917677525019</v>
+        <v>0.1196707257505752</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.862497285577076</v>
+        <v>3.82978466037592</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700473</v>
       </c>
       <c r="C2033" t="n">
         <v>3.574166221049509</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.914555193988949</v>
+        <v>-4.969076235990875</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.607987719140182</v>
+        <v>1.586179302339412</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2847979078321039</v>
+        <v>0.2302768658301773</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.745044965748772</v>
+        <v>3.712332340547616</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077635</v>
       </c>
       <c r="C2034" t="n">
         <v>3.577668265123473</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.045135928519792</v>
+        <v>-5.099656970521718</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.559257469401809</v>
+        <v>1.537449052601039</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1542171733012614</v>
+        <v>0.09969613129933474</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.67019856910423</v>
+        <v>3.637485943903075</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.562095084199556</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.88063959432883</v>
+        <v>-4.935160636330756</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.609482822154276</v>
+        <v>1.587674405353506</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.1542171733012614</v>
+        <v>0.09969613129933474</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.654625388180313</v>
+        <v>3.621912762979157</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077622</v>
       </c>
       <c r="C2036" t="n">
         <v>3.561282794635986</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.908009527013262</v>
+        <v>-4.962530569015188</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.597722559516933</v>
+        <v>1.575914142716163</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.1542171733012614</v>
+        <v>0.09969613129933474</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.653813098616743</v>
+        <v>3.621100473415587</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
         <v>3.571151573761058</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.918394721903152</v>
+        <v>-4.972915763905077</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.60343726068605</v>
+        <v>1.58162884388528</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1438319784113721</v>
+        <v>0.08931093640944543</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.657450760807882</v>
+        <v>3.624738135606726</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735281</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.641988579537483</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.936982880625377</v>
+        <v>-4.991503922627302</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.666839002973585</v>
+        <v>1.645030586172815</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1252438196891467</v>
+        <v>0.07072277768722007</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.717134871350972</v>
+        <v>3.684422246149816</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496548</v>
       </c>
       <c r="C2039" t="n">
         <v>3.638857590355782</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.937281427321413</v>
+        <v>-4.991802469323338</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.663588595113469</v>
+        <v>1.641780178312699</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1252438196891467</v>
+        <v>0.07072277768722007</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.71400388216927</v>
+        <v>3.681291256968114</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108852</v>
       </c>
       <c r="C2040" t="n">
         <v>3.643388485295173</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.836458293630985</v>
+        <v>-4.890979335632911</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.708448743529031</v>
+        <v>1.686640326728261</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.1377080351735006</v>
+        <v>0.08318699317157391</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.726013306399274</v>
+        <v>3.693300681198118</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121461</v>
       </c>
       <c r="C2041" t="n">
         <v>3.643517738773717</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.645676932878578</v>
+        <v>-4.700197974880504</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.784890541308537</v>
+        <v>1.763082124507767</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3284893959259079</v>
+        <v>0.2739683539239813</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.840611376329262</v>
+        <v>3.807898751128106</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.623354584511313</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.627160078836758</v>
+        <v>-4.681681120838683</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.772134128662862</v>
+        <v>1.750325711862092</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.3414195253511161</v>
+        <v>0.2868984833491895</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.828206299721983</v>
+        <v>3.795493674520827</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
         <v>3.658321521123372</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.601966894335439</v>
+        <v>-4.656487936337365</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.817178339075448</v>
+        <v>1.795369922274678</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.3666127098524345</v>
+        <v>0.3120916678505078</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.878289147034832</v>
+        <v>3.845576521833677</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
         <v>3.652008089024809</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.589912767422477</v>
+        <v>-4.644433809424402</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.815686557742071</v>
+        <v>1.793878140941301</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.3786668367653973</v>
+        <v>0.3241457947634707</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.879208191084048</v>
+        <v>3.846495565882892</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
         <v>3.653888719208945</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.596536014112835</v>
+        <v>-4.651057056114761</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.814917889250063</v>
+        <v>1.793109472449293</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.372043590075039</v>
+        <v>0.3175225480731123</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.877114873253969</v>
+        <v>3.844402248052813</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.666739745086828</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.493655424584242</v>
+        <v>-4.548176466586168</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.868921150939383</v>
+        <v>1.847112734138613</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.4204031376017052</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.951694252849007</v>
+        <v>3.918981627647851</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760309</v>
       </c>
       <c r="C2047" t="n">
         <v>3.686942415260422</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.517097463764329</v>
+        <v>-4.571618505766255</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.879747005440942</v>
+        <v>1.857938588640172</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.4204031376017052</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.971896923022602</v>
+        <v>3.939184297821445</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781699</v>
       </c>
       <c r="C2048" t="n">
         <v>3.686942415260422</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.53516997205594</v>
+        <v>-4.589691014057866</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.872518002124298</v>
+        <v>1.850709585323528</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.4204031376017052</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.971896923022602</v>
+        <v>3.939184297821445</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.846386257095995</v>
+        <v>3.577300447431507</v>
       </c>
       <c r="C2049" t="n">
         <v>3.647194328853888</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.714906277451456</v>
+        <v>-4.855574261846256</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.760875393559558</v>
+        <v>1.704608199801638</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.4204031376017052</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.932148836616068</v>
+        <v>3.899436211414912</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240808.xlsx
+++ b/tame_output/ON/bt/strategyON_20240808.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>56.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>69.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.0%</t>
+          <t>125.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>433.7%</t>
+          <t>435.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-647.1%</t>
+          <t>-633.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-205.8%</t>
+          <t>-200.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-1422.2%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.4%</t>
+          <t>-154.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-182.0%</t>
+          <t>-176.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>-65.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2049"/>
+  <dimension ref="A1:G2050"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045691</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279811</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511402</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386091</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998558</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706666</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296833</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537423</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382188</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006528</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330517</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>2.971988151156609</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.950154596319519</v>
+        <v>-6.895633554317592</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.1915698883150529</v>
+        <v>0.2133783051158238</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5222282704061352</v>
+        <v>-0.4677072284042083</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.658651188912928</v>
+        <v>2.691363814114084</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>2.974803211844245</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.794416263759777</v>
+        <v>-6.73989522175785</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2566802820265868</v>
+        <v>0.2784886988273572</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3664899378463936</v>
+        <v>-0.3119688958444667</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.754909249136409</v>
+        <v>2.787621874337566</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>2.987709553067904</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.545416465076196</v>
+        <v>-6.490895423074269</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3691865427236776</v>
+        <v>0.3909949595244484</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1174901391628129</v>
+        <v>-0.06296909716088606</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.917215469570217</v>
+        <v>2.949928094771373</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.859733623468685</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.6510064548493</v>
+        <v>-6.596485412847374</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1989746172152169</v>
+        <v>0.2207830340159873</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2230801289359173</v>
+        <v>-0.1685590869339904</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.725885546107135</v>
+        <v>2.758598171308291</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.908277965345771</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.669741356967897</v>
+        <v>-6.615220314965971</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2400249982448646</v>
+        <v>0.261833415045635</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2286761385960486</v>
+        <v>-0.1741550965941217</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.771072282188142</v>
+        <v>2.803784907389299</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.788399042657604</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.521801315560298</v>
+        <v>-6.467280273558371</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1793220921197367</v>
+        <v>0.2011305089205071</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.208355222687491</v>
+        <v>-0.1538341806855641</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.663385909045109</v>
+        <v>2.696098534246266</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.779685056404126</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.468831793306309</v>
+        <v>-6.414310751304383</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1917959147678538</v>
+        <v>0.2136043315686242</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1553857004335021</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.686453636144024</v>
+        <v>2.719166261345181</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.772724444309032</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.303043597346019</v>
+        <v>-6.248522555344092</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2511505810568768</v>
+        <v>0.2729589978576477</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1553857004335021</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.679493024048931</v>
+        <v>2.712205649250087</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.787186798690175</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.26968039086725</v>
+        <v>-6.215159348865323</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2789582180295276</v>
+        <v>0.300766634830298</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1553857004335021</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.693955378430074</v>
+        <v>2.726668003631231</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.781718919149371</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.161421253744728</v>
+        <v>-6.106900211742802</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3167939933377313</v>
+        <v>0.3386024101385017</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1553857004335021</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.688487498889269</v>
+        <v>2.721200124090426</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.779217013159947</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.038130118927597</v>
+        <v>-5.983609076925671</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3636085412751604</v>
+        <v>0.3854169580759312</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.03209456561637164</v>
+        <v>0.02242647638555523</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.759960273790125</v>
+        <v>2.792672898991281</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.786917991397273</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.016980920024154</v>
+        <v>-5.962459878022227</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3797691990738628</v>
+        <v>0.4015776158746336</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.01094536671292828</v>
+        <v>0.04357567528899858</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.780350771369516</v>
+        <v>2.813063396570672</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.782698699744323</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.77321547804071</v>
+        <v>-5.718694436038783</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4730560842142912</v>
+        <v>0.4948645010150621</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.01094536671292828</v>
+        <v>0.04357567528899858</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.776131479716566</v>
+        <v>2.808844104917723</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.784823013664339</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.671452657763415</v>
+        <v>-5.616931615761488</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5158855262452255</v>
+        <v>0.5376939430459959</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.002273701679500417</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.78618723467204</v>
+        <v>2.818899859873196</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.777565088648041</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.42160226381434</v>
+        <v>-5.367081221812414</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6085677588085572</v>
+        <v>0.630376175609328</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.002273701679500417</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.778929309655742</v>
+        <v>2.811641934856898</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.78116421216869</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.245710171346907</v>
+        <v>-5.191189129344981</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6825237193161793</v>
+        <v>0.7043321361169501</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.002273701679500417</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.782528433176391</v>
+        <v>2.815241058377547</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.794491718223244</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.074263708324444</v>
+        <v>-5.019742666322517</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7644298105797183</v>
+        <v>0.7862382273804891</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1737201647019636</v>
+        <v>0.2282412067038904</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.898723817044422</v>
+        <v>2.931436442245579</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.793512195839541</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.999974142586105</v>
+        <v>-4.945453100584178</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7931661144913509</v>
+        <v>0.8149745312921217</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2480097304403028</v>
+        <v>0.3025307724422297</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.942318034103723</v>
+        <v>2.975030659304879</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.798206996893858</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.93633840035217</v>
+        <v>-4.881817358350244</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.823315212439242</v>
+        <v>0.8451236292400126</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3116454726742374</v>
+        <v>0.3661665146761642</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.985194280498401</v>
+        <v>3.017906905699557</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.779401255677654</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.82491164102625</v>
+        <v>-4.770390599024323</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8490801749534058</v>
+        <v>0.8708885917541764</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3116454726742374</v>
+        <v>0.3661665146761642</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.966388539282196</v>
+        <v>2.999101164483353</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.781144332302531</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.835414264091539</v>
+        <v>-4.780893222089612</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8466222023521675</v>
+        <v>0.8684306191529383</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3011428496089485</v>
+        <v>0.3556638916108754</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.9618300420679</v>
+        <v>2.994542667269056</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.785073646137351</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.763171695920344</v>
+        <v>-4.708650653918418</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8794485434554655</v>
+        <v>0.9012569602562364</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3011428496089485</v>
+        <v>0.3556638916108754</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.965759355902721</v>
+        <v>2.998471981103877</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.785752230054691</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.745458009042479</v>
+        <v>-4.690936967040552</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8872126021239517</v>
+        <v>0.9090210189247223</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3043241785058653</v>
+        <v>0.3588452205077922</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.968346737158211</v>
+        <v>3.001059362359367</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.782750301274685</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.636653123562752</v>
+        <v>-4.582132081560825</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.927732627535836</v>
+        <v>0.9495410443366068</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3043241785058653</v>
+        <v>0.3588452205077922</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.965344808378204</v>
+        <v>2.99805743357936</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.784329338285299</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.416632325525741</v>
+        <v>-4.362111283523815</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.017319983761254</v>
+        <v>1.039128400562025</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4455440235738455</v>
+        <v>0.5000650655757723</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.051655752429606</v>
+        <v>3.084368377630763</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.800223521087122</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.283764636462464</v>
+        <v>-4.229243594460537</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.086361242188389</v>
+        <v>1.108169658989159</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4455440235738455</v>
+        <v>0.5000650655757723</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.06754993523143</v>
+        <v>3.100262560432586</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.801369365527424</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.163591553097965</v>
+        <v>-4.109070511096038</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.13557631997449</v>
+        <v>1.157384736775261</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5657171069383444</v>
+        <v>0.6202381489402713</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.140799629690431</v>
+        <v>3.173512254891587</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.811457468088864</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.028338191767988</v>
+        <v>-3.973817149766061</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.199765767067921</v>
+        <v>1.221574183868692</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7009704682683215</v>
+        <v>0.7554915102702484</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.232039749049857</v>
+        <v>3.264752374251013</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.79749495949029</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.08821301912568</v>
+        <v>-4.033691977123754</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.16185332752627</v>
+        <v>1.18366174432704</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6410956409106294</v>
+        <v>0.6956166829125563</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.182152344036668</v>
+        <v>3.214864969237824</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.812784128724498</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.968392788214843</v>
+        <v>-3.913871746212916</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.225070589124813</v>
+        <v>1.246879005925584</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6410956409106294</v>
+        <v>0.6956166829125563</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.197441513270876</v>
+        <v>3.230154138472032</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.72042832804694</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.970862494676649</v>
+        <v>-3.916341452674722</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.131726905862532</v>
+        <v>1.153535322663303</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6386259344488232</v>
+        <v>0.6931469764507501</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.103603888716234</v>
+        <v>3.13631651391739</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.639690189532241</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.039232681000659</v>
+        <v>-3.984711638998732</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.02364069281823</v>
+        <v>1.045449109619001</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6479016334850382</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.028431169623265</v>
+        <v>3.06114379482442</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.630126898164133</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.053020733847705</v>
+        <v>-3.998499691845779</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.008562180311303</v>
+        <v>1.030370597112073</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6479016334850382</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.018867878255156</v>
+        <v>3.051580503456312</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.767157734856335</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.108540809740295</v>
+        <v>-4.054019767738368</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.123384986646469</v>
+        <v>1.14519340344724</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6479016334850382</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.155898714947358</v>
+        <v>3.188611340148514</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.771724966848123</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.933066549947826</v>
+        <v>-3.878545507945899</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.198141922555245</v>
+        <v>1.219950339356015</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6479016334850382</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.160465946939146</v>
+        <v>3.193178572140302</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.74746699560933</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.044002802589074</v>
+        <v>-3.989481760587148</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.129509450259952</v>
+        <v>1.151317867060723</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6479016334850382</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.136207975700353</v>
+        <v>3.168920600901509</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.67600530901078</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.010339257116792</v>
+        <v>-3.955818215114866</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.071513181850315</v>
+        <v>1.093321598651085</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6815651789573201</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.084944416385172</v>
+        <v>3.117657041586328</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.686177695442912</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.950486637913069</v>
+        <v>-3.895965595911143</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.105626615963937</v>
+        <v>1.127435032764707</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6815651789573201</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.095116802817304</v>
+        <v>3.12782942801846</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.681123966016772</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.864243174886691</v>
+        <v>-3.809722132884765</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.135070271748348</v>
+        <v>1.156878688549118</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6815651789573201</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.090063073391164</v>
+        <v>3.122775698592321</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.672899741461298</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.909549994285671</v>
+        <v>-3.855028952283745</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.108723319433282</v>
+        <v>1.130531736234052</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6407550159480893</v>
+        <v>0.6952760579500161</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.057352751030152</v>
+        <v>3.090065376231308</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.673451614494399</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.938583098987972</v>
+        <v>-3.884062056986047</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.097661950585462</v>
+        <v>1.119470367386233</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6407550159480893</v>
+        <v>0.6952760579500161</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.057904624063253</v>
+        <v>3.09061724926441</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.602724306385765</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.845772617537113</v>
+        <v>-3.791251575535187</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.064058835057172</v>
+        <v>1.085867251857942</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7335654973989486</v>
+        <v>0.7880865394008755</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.042863604825135</v>
+        <v>3.07557623002629</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.604597782310366</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.890162086866541</v>
+        <v>-3.835641044864615</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.048176523250002</v>
+        <v>1.069984940050772</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6891760280695209</v>
+        <v>0.7436970700714478</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.018103399152078</v>
+        <v>3.050816024353235</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472735</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.599673490822089</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.006703691971884</v>
+        <v>-3.952182649969958</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9966355897195873</v>
+        <v>1.018444006520358</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5726344229641782</v>
+        <v>0.6271554649661051</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.943254144600596</v>
+        <v>2.975966769801752</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.605164786652756</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.894326690789212</v>
+        <v>-3.839805648787285</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.047077686023324</v>
+        <v>1.068886102824094</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5726344229641782</v>
+        <v>0.6271554649661051</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.948745440431263</v>
+        <v>2.981458065632419</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498861</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.616661988421295</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.922107088690565</v>
+        <v>-3.867586046688638</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.047462728631321</v>
+        <v>1.069271145432092</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5448540250628251</v>
+        <v>0.599375067064752</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.943574403458991</v>
+        <v>2.976287028660146</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.455017708421948</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.040487761420703</v>
+        <v>-3.985966719418777</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8384661795399195</v>
+        <v>0.8602745963406897</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4776361729118489</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.741599412169058</v>
+        <v>2.774312037370214</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729265</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.575167369141154</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.149101839864034</v>
+        <v>-4.094580797862108</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9151702088817928</v>
+        <v>0.936978625682563</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4776361729118489</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.861749072888264</v>
+        <v>2.89446169808942</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.589680395243477</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.113692801615891</v>
+        <v>-4.059171759613965</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9438468502833728</v>
+        <v>0.9656552670841432</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4776361729118489</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.876262098990586</v>
+        <v>2.908974724191743</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.587099836585846</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.07530913905774</v>
+        <v>-4.020788097055814</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.956619756649002</v>
+        <v>0.9784281734497724</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5160198354700001</v>
+        <v>0.5705408774719269</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.896711737867846</v>
+        <v>2.929424363069002</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.583828865431148</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.898192809022574</v>
+        <v>-3.843671767020648</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.02419531750837</v>
+        <v>1.046003734309141</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5160198354700001</v>
+        <v>0.5705408774719269</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.893440766713148</v>
+        <v>2.926153391914304</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.584512257193061</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.94328505385612</v>
+        <v>-3.888764011854193</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.006841811336865</v>
+        <v>1.028650228137636</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4541237923006103</v>
+        <v>0.5086448343025372</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.856986532573427</v>
+        <v>2.889699157774583</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.578299232499475</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.763909632617352</v>
+        <v>-3.709388590615426</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.072378955138787</v>
+        <v>1.094187371939557</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.610900550471329</v>
+        <v>0.6654215924732558</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.944839562782273</v>
+        <v>2.977552187983429</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.559106687831065</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.808923846137958</v>
+        <v>-3.754402804136032</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.035180725062134</v>
+        <v>1.056989141862904</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5805516551567244</v>
+        <v>0.6350726971586512</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.9074376809251</v>
+        <v>2.940150306126256</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.564798250170011</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.075928356410394</v>
+        <v>-4.021407314408467</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9340704832921054</v>
+        <v>0.9558789000928758</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3861886171137758</v>
+        <v>0.4407096591157026</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.796511420438276</v>
+        <v>2.829224045639433</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.564002172066512</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.177126137847567</v>
+        <v>-4.12260509584564</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8927952926137377</v>
+        <v>0.9146037094145081</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3177798035684566</v>
+        <v>0.3723008455703835</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.754670054207586</v>
+        <v>2.787382679408742</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815452</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.561602133620829</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.170615171233254</v>
+        <v>-4.116094129231327</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8929996408137795</v>
+        <v>0.9148080576145499</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3177798035684566</v>
+        <v>0.3723008455703835</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.752270015761903</v>
+        <v>2.784982640963059</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.558126852829074</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.151577043525957</v>
+        <v>-4.09705600152403</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8971396111049434</v>
+        <v>0.9189480279057136</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.259596192237262</v>
+        <v>0.3141172342391889</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.713884568171431</v>
+        <v>2.746597193372587</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677421254463264</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.182703674676575</v>
+        <v>-4.128182632674648</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.003983360278886</v>
+        <v>1.025791777079657</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.259596192237262</v>
+        <v>0.3141172342391889</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.833178969805622</v>
+        <v>2.865891595006778</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678254583449398</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.196570436010493</v>
+        <v>-4.142049394008566</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9992699847314528</v>
+        <v>1.021078401532223</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2217382755034391</v>
+        <v>0.276259317505366</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.811297548751461</v>
+        <v>2.844010173952618</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789117</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684263113846324</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.151766264470563</v>
+        <v>-4.097245222468636</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.023200183744351</v>
+        <v>1.045008600545121</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2217382755034391</v>
+        <v>0.276259317505366</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.817306079148387</v>
+        <v>2.850018704349544</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519904</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582213335123523</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.00402329423556</v>
+        <v>-3.949502252233634</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.980247593115551</v>
+        <v>1.002056009916321</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3895456327383223</v>
+        <v>0.4440666747402491</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.815940714766517</v>
+        <v>2.848653339967673</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181166</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.585006956655004</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.087844515510259</v>
+        <v>-4.033323473508332</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9495127261371528</v>
+        <v>0.9713211429379232</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3895456327383223</v>
+        <v>0.4440666747402491</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.818734336297998</v>
+        <v>2.851446961499154</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585669305046662</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.081691809457475</v>
+        <v>-4.027170767455548</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9526361569499249</v>
+        <v>0.9744445737506953</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3956983387911066</v>
+        <v>0.4502193807930334</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.823088308321327</v>
+        <v>2.855800933522483</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890607</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584749781786773</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.098501107607976</v>
+        <v>-4.04398006560605</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9449929144298344</v>
+        <v>0.9668013312306047</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3788890406406049</v>
+        <v>0.4334100826425318</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.812083206171136</v>
+        <v>2.844795831372292</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.651085335583593</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.036203108831854</v>
+        <v>-3.981682066829928</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.036247667737104</v>
+        <v>1.058056084537874</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3788890406406049</v>
+        <v>0.4334100826425318</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.878418759967957</v>
+        <v>2.911131385169113</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453377337297721</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.834412911166696</v>
+        <v>-3.77989186916477</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9192557485172945</v>
+        <v>0.9410641653180645</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5769072328097593</v>
+        <v>0.6314282748116862</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.799521676983576</v>
+        <v>2.832234302184732</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.523667569619896</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.885299623852891</v>
+        <v>-3.830778581850965</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9691912957649917</v>
+        <v>0.9909997125657619</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5260205201235648</v>
+        <v>0.5805415621254917</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.839279881694035</v>
+        <v>2.871992506895191</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538295305735939</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.798688881203084</v>
+        <v>-3.744167839201157</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.018463328940958</v>
+        <v>1.040271745741729</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6046462513287231</v>
+        <v>0.6591672933306499</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.901083056533174</v>
+        <v>2.93379568173433</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536831286560611</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.858898179208368</v>
+        <v>-3.804377137206442</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9929155905635163</v>
+        <v>1.014724007364286</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5444369533234386</v>
+        <v>0.5989579953253654</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.863493458554674</v>
+        <v>2.896206083755831</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.53532290460054</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.782476132776441</v>
+        <v>-3.727955090774515</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.021976027176215</v>
+        <v>1.043784443976986</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5444369533234386</v>
+        <v>0.5989579953253654</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.861985076594603</v>
+        <v>2.894697701795759</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.535185772035976</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.738103001137873</v>
+        <v>-3.683581959135946</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.039588147267079</v>
+        <v>1.061396564067849</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5888100849620072</v>
+        <v>0.643331126963934</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.88847182301318</v>
+        <v>2.921184448214337</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529579566174566</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.760583351996758</v>
+        <v>-3.706062309994831</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.024989801062116</v>
+        <v>1.046798217862886</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5888100849620072</v>
+        <v>0.643331126963934</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.882865617151771</v>
+        <v>2.915578242352927</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535961323202371</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.712927621435702</v>
+        <v>-3.658406579433776</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.050433850314343</v>
+        <v>1.072242267115113</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6364658155230628</v>
+        <v>0.6909868575249897</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.917840812516209</v>
+        <v>2.950553437717365</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569611</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.540853696577096</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.612409462936947</v>
+        <v>-3.557888420935021</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.095533487088569</v>
+        <v>1.117341903889339</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7369839740218174</v>
+        <v>0.7915050160237442</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.983044080990187</v>
+        <v>3.015756706191342</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557288</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527608369052968</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.673076053339336</v>
+        <v>-3.61855501133741</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.058021523403486</v>
+        <v>1.079829940204256</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6552856573032837</v>
+        <v>0.7098066993052106</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.920779763434938</v>
+        <v>2.953492388636095</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531706071663597</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.628237651730938</v>
+        <v>-3.573716609729012</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.080054586657474</v>
+        <v>1.101863003458244</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6598290902481532</v>
+        <v>0.71435013225008</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.927603525812489</v>
+        <v>2.960316151013645</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535867011294675</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.647736107972946</v>
+        <v>-3.59321506597102</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.076416143791749</v>
+        <v>1.098224560592518</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6117444489682489</v>
+        <v>0.6662654909701757</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.902913680675624</v>
+        <v>2.93562630587678</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405954</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541746613822512</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.603533270887046</v>
+        <v>-3.54901222888512</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.099976881153946</v>
+        <v>1.121785297954716</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6559472860541493</v>
+        <v>0.7104683280560762</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.935314985455002</v>
+        <v>2.968027610656158</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265639</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.540156614291759</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.640512298550489</v>
+        <v>-3.585991256548563</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.083595270557816</v>
+        <v>1.105403687358586</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6929211878454798</v>
+        <v>0.7474422298474067</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.955909326999048</v>
+        <v>2.988621952200204</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591404379474799</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.482220881011217</v>
+        <v>-3.427699839009291</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.198159602756565</v>
+        <v>1.219968019557335</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6929211878454798</v>
+        <v>0.7474422298474067</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.007157092182087</v>
+        <v>3.039869717383243</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321016</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589845084069052</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.274578877376741</v>
+        <v>-3.220057835374815</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.279657108804608</v>
+        <v>1.301465525605378</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.900563191479956</v>
+        <v>0.9550842334818829</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.130182998957026</v>
+        <v>3.162895624158182</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475132</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584793312307322</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.223546784654213</v>
+        <v>-3.169025742652287</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.29501817413189</v>
+        <v>1.31682659093266</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.951595284202484</v>
+        <v>1.006116326204411</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.155750482828813</v>
+        <v>3.188463108029969</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404847</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601980716400027</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.158322603527007</v>
+        <v>-3.103801561525081</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.338295250675477</v>
+        <v>1.360103667476247</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.01681946532969</v>
+        <v>1.071340507331616</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.212072395597841</v>
+        <v>3.244785020798997</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882551</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597941688699307</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.120895583455873</v>
+        <v>-3.066374541453948</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.34922703100321</v>
+        <v>1.37103544780398</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.022071003358871</v>
+        <v>1.076592045360798</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.21118429071463</v>
+        <v>3.243896915915786</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.599198481030548</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.141007239490582</v>
+        <v>-3.086486197488656</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.342439160920567</v>
+        <v>1.364247577721337</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.033098348356291</v>
+        <v>1.087619390358217</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.219057490044322</v>
+        <v>3.251770115245479</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563628</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759756252051758</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.087262425063377</v>
+        <v>-3.032741383061451</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.52449485771266</v>
+        <v>1.54630327451343</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.043161657796753</v>
+        <v>1.097682699798679</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.38565324672981</v>
+        <v>3.418365871930966</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957619</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>2.879869161269576</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.012480164038364</v>
+        <v>-2.957959122036439</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.674520671340482</v>
+        <v>1.696329088141252</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.117943918821765</v>
+        <v>1.172464960823692</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.550635512562635</v>
+        <v>3.583348137763791</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998749</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871577137283435</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.986396079774556</v>
+        <v>-2.931875037772631</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.676662281059865</v>
+        <v>1.698470697860635</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.117943918821765</v>
+        <v>1.172464960823692</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.542343488576494</v>
+        <v>3.57505611377765</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896922</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869770332867214</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.898518166665436</v>
+        <v>-2.84399712466351</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.710006641887292</v>
+        <v>1.731815058688062</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.233869561245116</v>
+        <v>1.288390603247043</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.610092069614284</v>
+        <v>3.64280469481544</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959851</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.887324738594006</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.889625705272152</v>
+        <v>-2.835104663270227</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.731118032171397</v>
+        <v>1.752926448972167</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.233869561245116</v>
+        <v>1.288390603247043</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.627646475341076</v>
+        <v>3.660359100542232</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945359</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.879179785998589</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.05810182224203</v>
+        <v>-3.003580780240104</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.65558263278803</v>
+        <v>1.6773910495888</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.205921725528536</v>
+        <v>1.260442767530462</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.602732821315711</v>
+        <v>3.635445446516867</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782701</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860449483186451</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.360302293380447</v>
+        <v>-2.305781251378521</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.915972141520525</v>
+        <v>1.937780558321295</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.135573666158125</v>
+        <v>1.190094708160052</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.541793682881327</v>
+        <v>3.574506308082483</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563263</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.851113505683356</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.337581189697294</v>
+        <v>-2.283060147695369</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.91572460549069</v>
+        <v>1.93753302229146</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.135573666158125</v>
+        <v>1.190094708160052</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.532457705378231</v>
+        <v>3.565170330579387</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777666</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.010019631534525</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.466783002991337</v>
+        <v>-2.412261960989411</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.022950006024243</v>
+        <v>2.044758422825013</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.006371852864083</v>
+        <v>1.060892894866009</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.613842743252975</v>
+        <v>3.646555368454131</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644406</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.047097454028171</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.621564009769592</v>
+        <v>-2.567042967767667</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.998115425806587</v>
+        <v>2.019923842607357</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9730041788096067</v>
+        <v>1.027525220811533</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.630899961313935</v>
+        <v>3.663612586515092</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799956</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043772810017717</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.614509319554419</v>
+        <v>-2.559988277552493</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.997612657882201</v>
+        <v>2.019421074682971</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9800588690247805</v>
+        <v>1.034579911026707</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.631808131432585</v>
+        <v>3.664520756633741</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331109</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053778963662458</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.587558095227931</v>
+        <v>-2.533037053226005</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.018399301257539</v>
+        <v>2.040207718058308</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9949392150524996</v>
+        <v>1.049460257054426</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.650742492693958</v>
+        <v>3.683455117895114</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784101</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237882095807418</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.723511103284247</v>
+        <v>-2.668990061282321</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.148121230179972</v>
+        <v>2.169929646980742</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9949392150524996</v>
+        <v>1.049460257054426</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.834845624838918</v>
+        <v>3.867558250040074</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714419</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229998790710411</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.745919221089119</v>
+        <v>-2.691398179087193</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.131274677961016</v>
+        <v>2.153083094761786</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9949392150524996</v>
+        <v>1.049460257054426</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.826962319741911</v>
+        <v>3.859674944943067</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155026</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.232052790260048</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.77414345666672</v>
+        <v>-2.719622414664794</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.122038983279613</v>
+        <v>2.143847400080383</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.012915967503808</v>
+        <v>1.067437009505735</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.839802370762333</v>
+        <v>3.87251499596349</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.288306507981896</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.78358438255525</v>
+        <v>-2.729063340553324</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.174516330646048</v>
+        <v>2.196324747446818</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.1353430850472</v>
+        <v>1.189864127049126</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.969512359010215</v>
+        <v>4.002224984211372</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.291197602527197</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.835857989890891</v>
+        <v>-2.781336947888965</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.156497982257092</v>
+        <v>2.178306399057862</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.083069477711558</v>
+        <v>1.137590519713485</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.941039289154132</v>
+        <v>3.973751914355288</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347697</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289309415420972</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.912187967491797</v>
+        <v>-2.857666925489871</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.124077804110505</v>
+        <v>2.145886220911275</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.083069477711558</v>
+        <v>1.137590519713485</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.939151102047907</v>
+        <v>3.971863727249063</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887741</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.284129645023834</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.11444168781615</v>
+        <v>-3.059920645814224</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.037996545583626</v>
+        <v>2.059804962384396</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8808157573872049</v>
+        <v>0.9353367993891315</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.812619099456157</v>
+        <v>3.845331724657313</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.71289761234306</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282563655233986</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.276010113343405</v>
+        <v>-3.221489071341479</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.971803185582877</v>
+        <v>1.993611602383647</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7540328335893255</v>
+        <v>0.8085538755912521</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.734983355387582</v>
+        <v>3.767695980588738</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389343</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295637062099905</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.408311405440958</v>
+        <v>-3.353790363439033</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.931956075609774</v>
+        <v>1.953764492410544</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7540328335893255</v>
+        <v>0.8085538755912521</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.7480567622535</v>
+        <v>3.780769387454657</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378385</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.287642258882845</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.594179716280189</v>
+        <v>-3.539658674278263</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.849613948057022</v>
+        <v>1.871422364857792</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5954672402693778</v>
+        <v>0.6499882822713045</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.644922603044472</v>
+        <v>3.677635228245628</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006968</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.286166300009847</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.622080503389661</v>
+        <v>-3.567559461387736</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.836977674340235</v>
+        <v>1.858786091141005</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.560870316126443</v>
+        <v>0.6153913581283696</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.622688489685713</v>
+        <v>3.655401114886869</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878738</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.282930743987046</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.744606606092555</v>
+        <v>-3.69008556409063</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.784731677236276</v>
+        <v>1.806540094037046</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4383442134235491</v>
+        <v>0.4928652554254758</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.545937272041175</v>
+        <v>3.578649897242332</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585931</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.349636703577549</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.975121102278144</v>
+        <v>-3.920600060276218</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.759231838352544</v>
+        <v>1.781040255153314</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2078297172379604</v>
+        <v>0.262350759239887</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.474334533920326</v>
+        <v>3.507047159121482</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814658</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.489948422579396</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.231841920272967</v>
+        <v>-4.177320878271042</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.796855230156462</v>
+        <v>1.818663646957232</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.09941514309414556</v>
+        <v>0.1539361850960722</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.549597508435884</v>
+        <v>3.58231013363704</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237089</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.558928691725036</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.385828338049108</v>
+        <v>-4.331307296047182</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.804240932191645</v>
+        <v>1.826049348992415</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.09941514309414556</v>
+        <v>0.1539361850960722</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.618577777581524</v>
+        <v>3.65129040278268</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423381</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.544979893845157</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.335306434221442</v>
+        <v>-4.280785392219516</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.810500895842833</v>
+        <v>1.832309312643603</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.09941514309414556</v>
+        <v>0.1539361850960722</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.604628979701645</v>
+        <v>3.637341604902801</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609746</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.556850382900571</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.587781588229166</v>
+        <v>-4.533260546227241</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.721381323295157</v>
+        <v>1.743189740095927</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.09941514309414556</v>
+        <v>0.1539361850960722</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.616499468757059</v>
+        <v>3.649212093958215</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973151</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.558060917419515</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.880677344708579</v>
+        <v>-4.826156302706653</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.605433555222336</v>
+        <v>1.627241972023106</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.09941514309414556</v>
+        <v>0.1539361850960722</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.617710003276002</v>
+        <v>3.650422628477159</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251939</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.562182659646836</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.03822141643802</v>
+        <v>-4.983700374436094</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.54653766875788</v>
+        <v>1.56834608555865</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.03251333795387107</v>
+        <v>0.08703437995579771</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.581690662419159</v>
+        <v>3.614403287620315</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916196</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.557260512383026</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.316185812021294</v>
+        <v>-5.261664770019368</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.430429763260761</v>
+        <v>1.45223818006153</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.05710639633161319</v>
+        <v>-0.00258535432968654</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.522996674584058</v>
+        <v>3.555709299785214</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830322</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.71946456908207</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.433153504660185</v>
+        <v>-5.378632462658259</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.545846742904248</v>
+        <v>1.567655159705018</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.05710639633161319</v>
+        <v>-0.00258535432968654</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.685200731283102</v>
+        <v>3.717913356484258</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071545</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.714311207045884</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.517871446881138</v>
+        <v>-5.463350404879212</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.506806203979681</v>
+        <v>1.528614620780451</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1422224252596596</v>
+        <v>-0.08770138325773291</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.628977751890088</v>
+        <v>3.661690377091245</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.724540624614375</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.599806265150021</v>
+        <v>-5.545285223148095</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.484261694240619</v>
+        <v>1.506070111041389</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1521571708467397</v>
+        <v>-0.0976361288448131</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.633246322106332</v>
+        <v>3.665958947307487</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332685</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.733466263070278</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.701782387398429</v>
+        <v>-5.647261345396503</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.452396883797158</v>
+        <v>1.474205300597928</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2541332930951473</v>
+        <v>-0.1996122510932207</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.580986287213189</v>
+        <v>3.613698912414345</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231802</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.725619150314453</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.591776103921207</v>
+        <v>-5.537255061919281</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.488552284432223</v>
+        <v>1.510360701232992</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2309287211778721</v>
+        <v>-0.1764076791759455</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.58706191760773</v>
+        <v>3.619774542808886</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818515</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.729869161036427</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.448716528180282</v>
+        <v>-5.394195486178356</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.550026125450567</v>
+        <v>1.571834542251337</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2229152945878928</v>
+        <v>-0.1683942525859662</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.596119984283692</v>
+        <v>3.628832609484848</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051782</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.737130043918963</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.147269802708444</v>
+        <v>-5.092748760706518</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.677865698521838</v>
+        <v>1.699674115322608</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.07853143088394443</v>
+        <v>0.1330524728858711</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.78424890244933</v>
+        <v>3.816961527650486</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.738101221671674</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.171860046943628</v>
+        <v>-5.117339004941702</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.669000778580475</v>
+        <v>1.690809195381245</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.07853143088394443</v>
+        <v>0.1330524728858711</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.785220080202041</v>
+        <v>3.817932705403197</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474154</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.738944126051429</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.120821670937108</v>
+        <v>-5.066300628935182</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.690259033362838</v>
+        <v>1.712067450163608</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.07853143088394443</v>
+        <v>0.1330524728858711</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.786062984581796</v>
+        <v>3.818775609782952</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969537</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.757982224925575</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.079682376070477</v>
+        <v>-5.025161334068551</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.725752850183636</v>
+        <v>1.747561266984406</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1196707257505752</v>
+        <v>0.1741917677525019</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.82978466037592</v>
+        <v>3.862497285577076</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700473</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.574166221049509</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.969076235990875</v>
+        <v>-4.914555193988949</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.586179302339412</v>
+        <v>1.607987719140182</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2302768658301773</v>
+        <v>0.2847979078321039</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.712332340547616</v>
+        <v>3.745044965748772</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077635</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.577668265123473</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.099656970521718</v>
+        <v>-5.045135928519792</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.537449052601039</v>
+        <v>1.559257469401809</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.09969613129933474</v>
+        <v>0.1542171733012614</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.637485943903075</v>
+        <v>3.67019856910423</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.562095084199556</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.935160636330756</v>
+        <v>-4.88063959432883</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.587674405353506</v>
+        <v>1.609482822154276</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.09969613129933474</v>
+        <v>0.1542171733012614</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.621912762979157</v>
+        <v>3.654625388180313</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077622</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.561282794635986</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.962530569015188</v>
+        <v>-4.908009527013262</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.575914142716163</v>
+        <v>1.597722559516933</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.09969613129933474</v>
+        <v>0.1542171733012614</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.621100473415587</v>
+        <v>3.653813098616743</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147903</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.571151573761058</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.972915763905077</v>
+        <v>-4.918394721903152</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.58162884388528</v>
+        <v>1.60343726068605</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.08931093640944543</v>
+        <v>0.1438319784113721</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.624738135606726</v>
+        <v>3.657450760807882</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
         <v>3.641988579537483</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.991503922627302</v>
+        <v>-4.936982880625377</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.645030586172815</v>
+        <v>1.666839002973585</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.07072277768722007</v>
+        <v>0.1252438196891467</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.684422246149816</v>
+        <v>3.717134871350972</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496548</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.638857590355782</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.991802469323338</v>
+        <v>-4.937281427321413</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.641780178312699</v>
+        <v>1.663588595113469</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.07072277768722007</v>
+        <v>0.1252438196891467</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.681291256968114</v>
+        <v>3.71400388216927</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108852</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.643388485295173</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.890979335632911</v>
+        <v>-4.836458293630985</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.686640326728261</v>
+        <v>1.708448743529031</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.08318699317157391</v>
+        <v>0.1377080351735006</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.693300681198118</v>
+        <v>3.726013306399274</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121461</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.643517738773717</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.700197974880504</v>
+        <v>-4.645676932878578</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.763082124507767</v>
+        <v>1.784890541308537</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.2739683539239813</v>
+        <v>0.3284893959259079</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.807898751128106</v>
+        <v>3.840611376329262</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.623354584511313</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.681681120838683</v>
+        <v>-4.627160078836758</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.750325711862092</v>
+        <v>1.772134128662862</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.2868984833491895</v>
+        <v>0.3414195253511161</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.795493674520827</v>
+        <v>3.828206299721983</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912979</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.658321521123372</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.656487936337365</v>
+        <v>-4.601966894335439</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.795369922274678</v>
+        <v>1.817178339075448</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.3120916678505078</v>
+        <v>0.3666127098524345</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.845576521833677</v>
+        <v>3.878289147034832</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539888</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.652008089024809</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.644433809424402</v>
+        <v>-4.589912767422477</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.793878140941301</v>
+        <v>1.815686557742071</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.3241457947634707</v>
+        <v>0.3786668367653973</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.846495565882892</v>
+        <v>3.879208191084048</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811003</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.653888719208945</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.651057056114761</v>
+        <v>-4.596536014112835</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.793109472449293</v>
+        <v>1.814917889250063</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.3175225480731123</v>
+        <v>0.372043590075039</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.844402248052813</v>
+        <v>3.877114873253969</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.666739745086828</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.548176466586168</v>
+        <v>-4.493655424584242</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.847112734138613</v>
+        <v>1.868921150939383</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4204031376017052</v>
+        <v>0.4749241796036319</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.918981627647851</v>
+        <v>3.951694252849007</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760309</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.686942415260422</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.571618505766255</v>
+        <v>-4.517097463764329</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.857938588640172</v>
+        <v>1.879747005440942</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4204031376017052</v>
+        <v>0.4749241796036319</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.939184297821445</v>
+        <v>3.971896923022602</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781699</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.686942415260422</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.589691014057866</v>
+        <v>-4.53516997205594</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.850709585323528</v>
+        <v>1.872518002124298</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4204031376017052</v>
+        <v>0.4749241796036319</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.939184297821445</v>
+        <v>3.971896923022602</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,45 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.577300447431507</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.647194328853888</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.855574261846256</v>
+        <v>-4.714906277451456</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.704608199801638</v>
+        <v>1.760875393559558</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4204031376017052</v>
+        <v>0.4749241796036319</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.899436211414912</v>
+        <v>3.932148836616068</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" s="2" t="n">
+        <v>45512</v>
+      </c>
+      <c r="B2050" t="n">
+        <v>3.845806060592298</v>
+      </c>
+      <c r="C2050" t="n">
+        <v>3.813673360061921</v>
+      </c>
+      <c r="D2050" t="n">
+        <v>-4.714906277451456</v>
+      </c>
+      <c r="E2050" t="n">
+        <v>1.760875393559558</v>
+      </c>
+      <c r="F2050" t="n">
+        <v>0.4749241796036319</v>
+      </c>
+      <c r="G2050" t="n">
+        <v>3.806737157048289</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240808.xlsx
+++ b/tame_output/ON/bt/strategyON_20240808.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,46 +815,46 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>110.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.4%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>435.0%</t>
+          <t>432.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-633.1%</t>
+          <t>-656.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-200.1%</t>
+          <t>-191.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.0%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-176.5%</t>
+          <t>-199.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-65.4%</t>
+          <t>-79.3%</t>
         </is>
       </c>
     </row>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.673916174092536</v>
+        <v>-8.846438384567879</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3097485457176585</v>
+        <v>-0.3787574299077954</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.335116651231713</v>
+        <v>-1.507638861707055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.359104357494076</v>
+        <v>2.255591031208871</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.84904059147908</v>
+        <v>-9.021562801954422</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3652430919247589</v>
+        <v>-0.4342519761148962</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.510241068618257</v>
+        <v>-1.682763279093599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.268584927809667</v>
+        <v>2.165071601524462</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.083492685493569</v>
+        <v>-9.256014895968912</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.466243094432151</v>
+        <v>-0.5352519786222878</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.510241068618257</v>
+        <v>-1.682763279093599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.261365762908071</v>
+        <v>2.157852436622866</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.187867416520016</v>
+        <v>-9.360389626995358</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5146651776167057</v>
+        <v>-0.5836740618068426</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.614615799644703</v>
+        <v>-1.787138010120045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.192068733518227</v>
+        <v>2.088555407233022</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.240653572120342</v>
+        <v>-9.413175782595685</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5346638500182799</v>
+        <v>-0.6036727342084172</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.7102912862271</v>
+        <v>-1.882813496702442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.135779231407345</v>
+        <v>2.032265905122141</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.366690365488632</v>
+        <v>-9.539212575963974</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5823848387364809</v>
+        <v>-0.6513937229266182</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.8575618738927</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.153623933722305</v>
+        <v>2.0501106074371</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.309618593592701</v>
+        <v>-9.482140804068043</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5555657942917076</v>
+        <v>-0.6245746784818449</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.8575618738927</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.157614269408707</v>
+        <v>2.054100943123501</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.451290435316821</v>
+        <v>-9.623812645792164</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6137097578800974</v>
+        <v>-0.6827186420702347</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.8575618738927</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.156139042509965</v>
+        <v>2.052625716224759</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.401699590891987</v>
+        <v>-9.574221801367329</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5788200099452916</v>
+        <v>-0.6478288941354289</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.635448818992524</v>
+        <v>-1.807971029467866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.200946959329737</v>
+        <v>2.097433633044532</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.25278125642013</v>
+        <v>-9.425303466895473</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5323038098032318</v>
+        <v>-0.6013126939933691</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.604199228257351</v>
+        <v>-1.776721438732693</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.206645580124158</v>
+        <v>2.103132253838953</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.026936103700718</v>
+        <v>-9.199458314176061</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4323866756792585</v>
+        <v>-0.5013955598693958</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.562272552670187</v>
+        <v>-1.734794763145529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.241380658512665</v>
+        <v>2.13786733222746</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.902357447363126</v>
+        <v>-9.074879657838469</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3814160685881629</v>
+        <v>-0.4504249527783002</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.562272552670187</v>
+        <v>-1.734794763145529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.242519803068724</v>
+        <v>2.139006476783519</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.955252735407413</v>
+        <v>-9.127774945882756</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.39994040964377</v>
+        <v>-0.4689492938339068</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.557317206581741</v>
+        <v>-1.729839417057083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.248126784883899</v>
+        <v>2.144613458598694</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.883119560119532</v>
+        <v>-9.055641770594875</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3653534352899808</v>
+        <v>-0.4343623194801181</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.557317206581741</v>
+        <v>-1.729839417057083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.253860489122536</v>
+        <v>2.15034716283733</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.811753167509885</v>
+        <v>-8.984275377985227</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3465441406399874</v>
+        <v>-0.4155530248301242</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.658473024447435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.286943062294459</v>
+        <v>2.183429736009254</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.71829413352466</v>
+        <v>-8.890816344000003</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3190440083588051</v>
+        <v>-0.3880528925489419</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.658473024447435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.277059580981552</v>
+        <v>2.173546254696347</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.707640951971229</v>
+        <v>-8.880163162446571</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3166172962368061</v>
+        <v>-0.3856261804269434</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.658473024447435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.275225020482178</v>
+        <v>2.171711694196973</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.609733913294738</v>
+        <v>-8.782256123770081</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2777547957396709</v>
+        <v>-0.3467636799298077</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.417965064111537</v>
+        <v>-1.590487274586879</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.315716155425051</v>
+        <v>2.212202829139846</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.58578037231878</v>
+        <v>-8.758302582794123</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2675048732037939</v>
+        <v>-0.3365137573939312</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.394011523135579</v>
+        <v>-1.566533733610921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.330756786156119</v>
+        <v>2.227243459870914</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.321720433995983</v>
+        <v>-8.494242644471326</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1751412140364272</v>
+        <v>-0.2441500982265645</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.129951584812783</v>
+        <v>-1.302473795288125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.475932432988045</v>
+        <v>2.372419106702839</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.614640810491145</v>
+        <v>-7.787163020966488</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1049036017052072</v>
+        <v>0.0358947175150699</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.129951584812783</v>
+        <v>-1.302473795288125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.473145399327744</v>
+        <v>2.369632073042538</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.574456512124955</v>
+        <v>-7.746978722600297</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1213209449395247</v>
+        <v>0.05231206074938743</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.089767286446592</v>
+        <v>-1.262289496921934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.4975996022353</v>
+        <v>2.394086275950094</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.411056641185592</v>
+        <v>-7.583578851660935</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1860477145360266</v>
+        <v>0.1170388303458894</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9263674155072295</v>
+        <v>-1.098889625982571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.595006346019674</v>
+        <v>2.491493019734469</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.177575418955993</v>
+        <v>-7.350097629431336</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2873646322657182</v>
+        <v>0.2183557480755813</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6928861932776309</v>
+        <v>-0.8654084037529728</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.743019508195286</v>
+        <v>2.639506181910081</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.027909027948478</v>
+        <v>-7.200431238423821</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3443389783557653</v>
+        <v>0.275330094165628</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.599982702035095</v>
+        <v>-0.7725049125104368</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.795869392627848</v>
+        <v>2.692356066342643</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>2.971988151156609</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.895633554317592</v>
+        <v>-7.125209880691897</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2133783051158238</v>
+        <v>0.3007861240054246</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4677072284042083</v>
+        <v>-0.6972835547785128</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.691363814114084</v>
+        <v>2.732856367728824</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>2.974803211844245</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.73989522175785</v>
+        <v>-6.969471548132155</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2784886988273572</v>
+        <v>0.3658965177169584</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3119688958444667</v>
+        <v>-0.5415452222187712</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.787621874337566</v>
+        <v>2.829114427952306</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>2.987709553067904</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.490895423074269</v>
+        <v>-6.720471749448574</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3909949595244484</v>
+        <v>0.4784027784140492</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06296909716088606</v>
+        <v>-0.2925454235351905</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.949928094771373</v>
+        <v>2.991420648386113</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.859733623468685</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.596485412847374</v>
+        <v>-6.826061739221679</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2207830340159873</v>
+        <v>0.308190852905589</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1685590869339904</v>
+        <v>-0.3981354133082949</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.758598171308291</v>
+        <v>2.800090724923032</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.908277965345771</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.615220314965971</v>
+        <v>-6.844796641340276</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.261833415045635</v>
+        <v>0.3492412339352367</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1741550965941217</v>
+        <v>-0.4037314229684262</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.803784907389299</v>
+        <v>2.845277461004039</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.788399042657604</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.467280273558371</v>
+        <v>-6.696856599932676</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2011305089205071</v>
+        <v>0.2885383278101088</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1538341806855641</v>
+        <v>-0.3834105070598686</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.696098534246266</v>
+        <v>2.737591087861006</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.779685056404126</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.414310751304383</v>
+        <v>-6.643887077678688</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2136043315686242</v>
+        <v>0.3010121504582259</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.3304409848058797</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.719166261345181</v>
+        <v>2.760658814959922</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.772724444309032</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.248522555344092</v>
+        <v>-6.478098881718397</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2729589978576477</v>
+        <v>0.3603668167472489</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.3304409848058797</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.712205649250087</v>
+        <v>2.753698202864828</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.787186798690175</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.215159348865323</v>
+        <v>-6.444735675239628</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.300766634830298</v>
+        <v>0.3881744537198997</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.3304409848058797</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.726668003631231</v>
+        <v>2.768160557245972</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.781718919149371</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.106900211742802</v>
+        <v>-6.336476538117107</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3386024101385017</v>
+        <v>0.4260102290281034</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.3304409848058797</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.721200124090426</v>
+        <v>2.762692677705167</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.779217013159947</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.983609076925671</v>
+        <v>-6.213185403299976</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3854169580759312</v>
+        <v>0.4728247769655325</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.02242647638555523</v>
+        <v>-0.2071498499887492</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.792672898991281</v>
+        <v>2.834165452606022</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.786917991397273</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.962459878022227</v>
+        <v>-6.192036204396532</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4015776158746336</v>
+        <v>0.4889854347642348</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.1860006510853059</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.813063396570672</v>
+        <v>2.854555950185413</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.782698699744323</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.718694436038783</v>
+        <v>-5.948270762413088</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4948645010150621</v>
+        <v>0.5822723199046633</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.1860006510853059</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.808844104917723</v>
+        <v>2.850336658532464</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.784823013664339</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.616931615761488</v>
+        <v>-5.846507942135793</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5376939430459959</v>
+        <v>0.6251017619355976</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.1727815826928772</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.818899859873196</v>
+        <v>2.860392413487937</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.777565088648041</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.367081221812414</v>
+        <v>-5.596657548186719</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.630376175609328</v>
+        <v>0.7177839944989293</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.1727815826928772</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.811641934856898</v>
+        <v>2.853134488471639</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.78116421216869</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.191189129344981</v>
+        <v>-5.420765455719286</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7043321361169501</v>
+        <v>0.7917399550065514</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.1727815826928772</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.815241058377547</v>
+        <v>2.856733611992288</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.794491718223244</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.019742666322517</v>
+        <v>-5.249318992696822</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7862382273804891</v>
+        <v>0.8736460462700903</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2282412067038904</v>
+        <v>-0.001335119670414053</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.931436442245579</v>
+        <v>2.972928995860319</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.793512195839541</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.945453100584178</v>
+        <v>-5.175029426958483</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8149745312921217</v>
+        <v>0.902382350181723</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3025307724422297</v>
+        <v>0.07295444606792523</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.975030659304879</v>
+        <v>3.01652321291962</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.798206996893858</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.881817358350244</v>
+        <v>-5.111393684724549</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8451236292400126</v>
+        <v>0.9325314481296143</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.1365901883018598</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.017906905699557</v>
+        <v>3.059399459314298</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.779401255677654</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.770390599024323</v>
+        <v>-4.999966925398629</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8708885917541764</v>
+        <v>0.9582964106437779</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.1365901883018598</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.999101164483353</v>
+        <v>3.040593718098093</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.781144332302531</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.780893222089612</v>
+        <v>-5.010469548463917</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8684306191529383</v>
+        <v>0.9558384380425395</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.1260875652365709</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.994542667269056</v>
+        <v>3.036035220883798</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.785073646137351</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.708650653918418</v>
+        <v>-4.938226980292723</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9012569602562364</v>
+        <v>0.9886647791458376</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.1260875652365709</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.998471981103877</v>
+        <v>3.039964534718618</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.785752230054691</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.690936967040552</v>
+        <v>-4.920513293414857</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9090210189247223</v>
+        <v>0.9964288378143238</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.1292688941334877</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.001059362359367</v>
+        <v>3.042551915974108</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.782750301274685</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.582132081560825</v>
+        <v>-4.81170840793513</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9495410443366068</v>
+        <v>1.036948863226208</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.1292688941334877</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.99805743357936</v>
+        <v>3.039549987194101</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.784329338285299</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.362111283523815</v>
+        <v>-4.59168760989812</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.039128400562025</v>
+        <v>1.126536219451626</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.2704887392014679</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.084368377630763</v>
+        <v>3.125860931245503</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.800223521087122</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.229243594460537</v>
+        <v>-4.458819920834842</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.108169658989159</v>
+        <v>1.195577477878761</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.2704887392014679</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.100262560432586</v>
+        <v>3.141755114047327</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.801369365527424</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.109070511096038</v>
+        <v>-4.338646837470344</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.157384736775261</v>
+        <v>1.244792555664862</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6202381489402713</v>
+        <v>0.3906618225659669</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.173512254891587</v>
+        <v>3.215004808506328</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.811457468088864</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.973817149766061</v>
+        <v>-4.203393476140366</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.221574183868692</v>
+        <v>1.308982002758293</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7554915102702484</v>
+        <v>0.5259151838959439</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.264752374251013</v>
+        <v>3.306244927865754</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.79749495949029</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.033691977123754</v>
+        <v>-4.263268303498059</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.18366174432704</v>
+        <v>1.271069563216642</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.4660403565382518</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.214864969237824</v>
+        <v>3.256357522852565</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.812784128724498</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.913871746212916</v>
+        <v>-4.143448072587222</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.246879005925584</v>
+        <v>1.334286824815185</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.4660403565382518</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.230154138472032</v>
+        <v>3.271646692086773</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.72042832804694</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.916341452674722</v>
+        <v>-4.145917779049028</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.153535322663303</v>
+        <v>1.240943141552904</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6931469764507501</v>
+        <v>0.4635706500764457</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.13631651391739</v>
+        <v>3.177809067532131</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.639690189532241</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.984711638998732</v>
+        <v>-4.214287965373038</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.045449109619001</v>
+        <v>1.132856928508602</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.702422675486965</v>
+        <v>0.4728463491126606</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.06114379482442</v>
+        <v>3.102636348439161</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.630126898164133</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.998499691845779</v>
+        <v>-4.228076018220085</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.030370597112073</v>
+        <v>1.117778416001674</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.702422675486965</v>
+        <v>0.4728463491126606</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.051580503456312</v>
+        <v>3.093073057071053</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.767157734856335</v>
+        <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.054019767738368</v>
+        <v>-4.283596094112674</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.14519340344724</v>
+        <v>1.232601222336841</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.702422675486965</v>
+        <v>0.4728463491126606</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.188611340148514</v>
+        <v>3.230103893763255</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.771724966848123</v>
+        <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.878545507945899</v>
+        <v>-4.108121834320205</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.219950339356015</v>
+        <v>1.307358158245616</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.702422675486965</v>
+        <v>0.4728463491126606</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.193178572140302</v>
+        <v>3.234671125755043</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.74746699560933</v>
+        <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.989481760587148</v>
+        <v>-4.219058086961454</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.151317867060723</v>
+        <v>1.238725685950324</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.702422675486965</v>
+        <v>0.4728463491126606</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.168920600901509</v>
+        <v>3.21041315451625</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.67600530901078</v>
+        <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.955818215114866</v>
+        <v>-4.185394541489171</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.093321598651085</v>
+        <v>1.180729417540687</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.5065098945849424</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.117657041586328</v>
+        <v>3.159149595201069</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.686177695442912</v>
+        <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.895965595911143</v>
+        <v>-4.125541922285448</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.127435032764707</v>
+        <v>1.214842851654308</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.5065098945849424</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.12782942801846</v>
+        <v>3.169321981633201</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.681123966016772</v>
+        <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.809722132884765</v>
+        <v>-4.03929845925907</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.156878688549118</v>
+        <v>1.24428650743872</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.5065098945849424</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.122775698592321</v>
+        <v>3.164268252207061</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.672899741461298</v>
+        <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.855028952283745</v>
+        <v>-4.08460527865805</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.130531736234052</v>
+        <v>1.217939555123653</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.4656997315757117</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.090065376231308</v>
+        <v>3.131557929846049</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.673451614494399</v>
+        <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.884062056986047</v>
+        <v>-4.113638383360351</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.119470367386233</v>
+        <v>1.206878186275834</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.4656997315757117</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.09061724926441</v>
+        <v>3.13210980287915</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.602724306385765</v>
+        <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.791251575535187</v>
+        <v>-4.020827901909492</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.085867251857942</v>
+        <v>1.173275070747544</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7880865394008755</v>
+        <v>0.558510213026571</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.07557623002629</v>
+        <v>3.117068783641031</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.604597782310366</v>
+        <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.835641044864615</v>
+        <v>-4.065217371238919</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.069984940050772</v>
+        <v>1.157392758940374</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7436970700714478</v>
+        <v>0.5141207436971433</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.050816024353235</v>
+        <v>3.092308577967976</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.599673490822089</v>
+        <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.952182649969958</v>
+        <v>-4.181758976344262</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.018444006520358</v>
+        <v>1.10585182540996</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.3975791385918006</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.975966769801752</v>
+        <v>3.017459323416493</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.605164786652756</v>
+        <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.839805648787285</v>
+        <v>-4.069381975161589</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.068886102824094</v>
+        <v>1.156293921713696</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.3975791385918006</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.981458065632419</v>
+        <v>3.02295061924716</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.616661988421295</v>
+        <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.867586046688638</v>
+        <v>-4.097162373062941</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.069271145432092</v>
+        <v>1.156678964321694</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.599375067064752</v>
+        <v>0.3697987406904475</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.976287028660146</v>
+        <v>3.017779582274887</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.455017708421948</v>
+        <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.985966719418777</v>
+        <v>-4.21554304579308</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8602745963406897</v>
+        <v>0.9476824152302921</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.3025808885394713</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.774312037370214</v>
+        <v>2.815804590984955</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.575167369141154</v>
+        <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.094580797862108</v>
+        <v>-4.324157124236411</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.936978625682563</v>
+        <v>1.024386444572165</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.3025808885394713</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.89446169808942</v>
+        <v>2.935954251704161</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.589680395243477</v>
+        <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.059171759613965</v>
+        <v>-4.288748085988268</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9656552670841432</v>
+        <v>1.053063085973745</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.3025808885394713</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.908974724191743</v>
+        <v>2.950467277806484</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.587099836585846</v>
+        <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.020788097055814</v>
+        <v>-4.250364423430117</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9784281734497724</v>
+        <v>1.065835992339375</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.3409645510976225</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.929424363069002</v>
+        <v>2.970916916683743</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.583828865431148</v>
+        <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.843671767020648</v>
+        <v>-4.073248093394951</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.046003734309141</v>
+        <v>1.133411553198743</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.3409645510976225</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.926153391914304</v>
+        <v>2.967645945529045</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.584512257193061</v>
+        <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.888764011854193</v>
+        <v>-4.118340338228497</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.028650228137636</v>
+        <v>1.116058047027238</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5086448343025372</v>
+        <v>0.2790685079282327</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.889699157774583</v>
+        <v>2.931191711389324</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.578299232499475</v>
+        <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.709388590615426</v>
+        <v>-3.938964916989729</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.094187371939557</v>
+        <v>1.181595190829159</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6654215924732558</v>
+        <v>0.4358452660989514</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.977552187983429</v>
+        <v>3.01904474159817</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.559106687831065</v>
+        <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.754402804136032</v>
+        <v>-3.983979130510335</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.056989141862904</v>
+        <v>1.144396960752506</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6350726971586512</v>
+        <v>0.4054963707843467</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.940150306126256</v>
+        <v>2.981642859740997</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.564798250170011</v>
+        <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.021407314408467</v>
+        <v>-4.250983640782771</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9558789000928758</v>
+        <v>1.043286718982478</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4407096591157026</v>
+        <v>0.2111333327413982</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.829224045639433</v>
+        <v>2.870716599254173</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.564002172066512</v>
+        <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.12260509584564</v>
+        <v>-4.352181422219943</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9146037094145081</v>
+        <v>1.00201152830411</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.142724519196079</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.787382679408742</v>
+        <v>2.828875233023483</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.561602133620829</v>
+        <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.116094129231327</v>
+        <v>-4.345670455605631</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9148080576145499</v>
+        <v>1.002215876504152</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.142724519196079</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.784982640963059</v>
+        <v>2.8264751945778</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.558126852829074</v>
+        <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.09705600152403</v>
+        <v>-4.326632327898333</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9189480279057136</v>
+        <v>1.006355846795316</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.08454090786488444</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.746597193372587</v>
+        <v>2.788089746987328</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.677421254463264</v>
+        <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.128182632674648</v>
+        <v>-4.357758959048952</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.025791777079657</v>
+        <v>1.113199595969259</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.08454090786488444</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.865891595006778</v>
+        <v>2.907384148621519</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.678254583449398</v>
+        <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.142049394008566</v>
+        <v>-4.37162572038287</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.021078401532223</v>
+        <v>1.108486220421825</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.276259317505366</v>
+        <v>0.0466829911310615</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.844010173952618</v>
+        <v>2.885502727567358</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.684263113846324</v>
+        <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.097245222468636</v>
+        <v>-4.32682154884294</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.045008600545121</v>
+        <v>1.132416419434723</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.276259317505366</v>
+        <v>0.0466829911310615</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.850018704349544</v>
+        <v>2.891511257964284</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.582213335123523</v>
+        <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.949502252233634</v>
+        <v>-4.179078578607937</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.002056009916321</v>
+        <v>1.089463828805924</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.2144903483659447</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.848653339967673</v>
+        <v>2.890145893582413</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.585006956655004</v>
+        <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.033323473508332</v>
+        <v>-4.262899799882636</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9713211429379232</v>
+        <v>1.058728961827525</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.2144903483659447</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.851446961499154</v>
+        <v>2.892939515113894</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.585669305046662</v>
+        <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.027170767455548</v>
+        <v>-4.256747093829851</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9744445737506953</v>
+        <v>1.061852392640297</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4502193807930334</v>
+        <v>0.2206430544187289</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.855800933522483</v>
+        <v>2.897293487137223</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.584749781786773</v>
+        <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.04398006560605</v>
+        <v>-4.273556391980353</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9668013312306047</v>
+        <v>1.054209150120207</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.2038337562682273</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.844795831372292</v>
+        <v>2.886288384987033</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.651085335583593</v>
+        <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.981682066829928</v>
+        <v>-4.211258393204231</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.058056084537874</v>
+        <v>1.145463903427477</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.2038337562682273</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.911131385169113</v>
+        <v>2.952623938783854</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.453377337297721</v>
+        <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.77989186916477</v>
+        <v>-4.009468195539073</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9410641653180645</v>
+        <v>1.028471984207667</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6314282748116862</v>
+        <v>0.4018519484373817</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.832234302184732</v>
+        <v>2.873726855799474</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.523667569619896</v>
+        <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.830778581850965</v>
+        <v>-4.060354908225268</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9909997125657619</v>
+        <v>1.078407531455364</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5805415621254917</v>
+        <v>0.3509652357511872</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.871992506895191</v>
+        <v>2.913485060509932</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.538295305735939</v>
+        <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.744167839201157</v>
+        <v>-3.97374416557546</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.040271745741729</v>
+        <v>1.127679564631331</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6591672933306499</v>
+        <v>0.4295909669563454</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.93379568173433</v>
+        <v>2.97528823534907</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.536831286560611</v>
+        <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.804377137206442</v>
+        <v>-4.033953463580745</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.014724007364286</v>
+        <v>1.102131826253889</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.3693816689510609</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.896206083755831</v>
+        <v>2.937698637370572</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.53532290460054</v>
+        <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.727955090774515</v>
+        <v>-3.957531417148818</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.043784443976986</v>
+        <v>1.131192262866588</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.3693816689510609</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.894697701795759</v>
+        <v>2.9361902554105</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.535185772035976</v>
+        <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.683581959135946</v>
+        <v>-3.913158285510249</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.061396564067849</v>
+        <v>1.148804382957452</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.643331126963934</v>
+        <v>0.4137548005896295</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.921184448214337</v>
+        <v>2.962677001829077</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.529579566174566</v>
+        <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.706062309994831</v>
+        <v>-3.935638636369134</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.046798217862886</v>
+        <v>1.134206036752488</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.643331126963934</v>
+        <v>0.4137548005896295</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.915578242352927</v>
+        <v>2.957070795967668</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.535961323202371</v>
+        <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.658406579433776</v>
+        <v>-3.887982905808078</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.072242267115113</v>
+        <v>1.159650086004715</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6909868575249897</v>
+        <v>0.4614105311506851</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.950553437717365</v>
+        <v>2.992045991332106</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.540853696577096</v>
+        <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.557888420935021</v>
+        <v>-3.787464747309324</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.117341903889339</v>
+        <v>1.204749722778942</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7915050160237442</v>
+        <v>0.5619286896494398</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.015756706191342</v>
+        <v>3.057249259806083</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.527608369052968</v>
+        <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.61855501133741</v>
+        <v>-3.848131337711713</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.079829940204256</v>
+        <v>1.167237759093859</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7098066993052106</v>
+        <v>0.4802303729309061</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.953492388636095</v>
+        <v>2.994984942250835</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.531706071663597</v>
+        <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.573716609729012</v>
+        <v>-3.803292936103315</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.101863003458244</v>
+        <v>1.189270822347846</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.71435013225008</v>
+        <v>0.4847738058757756</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.960316151013645</v>
+        <v>3.001808704628386</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.535867011294675</v>
+        <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.59321506597102</v>
+        <v>-3.822791392345323</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.098224560592518</v>
+        <v>1.185632379482121</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6662654909701757</v>
+        <v>0.4366891645958713</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.93562630587678</v>
+        <v>2.977118859491521</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.541746613822512</v>
+        <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.54901222888512</v>
+        <v>-3.778588555259422</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.121785297954716</v>
+        <v>1.209193116844318</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7104683280560762</v>
+        <v>0.4808920016817717</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.968027610656158</v>
+        <v>3.009520164270898</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.540156614291759</v>
+        <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.585991256548563</v>
+        <v>-3.815567582922866</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.105403687358586</v>
+        <v>1.192811506248189</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7474422298474067</v>
+        <v>0.5178659034731022</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.988621952200204</v>
+        <v>3.030114505814944</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.591404379474799</v>
+        <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.427699839009291</v>
+        <v>-3.657276165383593</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.219968019557335</v>
+        <v>1.307375838446937</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7474422298474067</v>
+        <v>0.5178659034731022</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.039869717383243</v>
+        <v>3.081362270997984</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.589845084069052</v>
+        <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.220057835374815</v>
+        <v>-3.449634161749117</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.301465525605378</v>
+        <v>1.388873344494981</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9550842334818829</v>
+        <v>0.7255079071075784</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.162895624158182</v>
+        <v>3.204388177772923</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.584793312307322</v>
+        <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.169025742652287</v>
+        <v>-3.398602069026589</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.31682659093266</v>
+        <v>1.404234409822262</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.006116326204411</v>
+        <v>0.7765399998301064</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.188463108029969</v>
+        <v>3.22995566164471</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.601980716400027</v>
+        <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.103801561525081</v>
+        <v>-3.333377887899384</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.360103667476247</v>
+        <v>1.447511486365849</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.071340507331616</v>
+        <v>0.841764180957312</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.244785020798997</v>
+        <v>3.286277574413738</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.597941688699307</v>
+        <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.066374541453948</v>
+        <v>-3.29595086782825</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.37103544780398</v>
+        <v>1.458443266693583</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.076592045360798</v>
+        <v>0.8470157189864936</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.243896915915786</v>
+        <v>3.285389469530527</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.599198481030548</v>
+        <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.086486197488656</v>
+        <v>-3.316062523862958</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.364247577721337</v>
+        <v>1.45165539661094</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.087619390358217</v>
+        <v>0.8580430639839128</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.251770115245479</v>
+        <v>3.293262668860219</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.759756252051758</v>
+        <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.032741383061451</v>
+        <v>-3.262317709435754</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.54630327451343</v>
+        <v>1.633711093403033</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.097682699798679</v>
+        <v>0.8681063734243748</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.418365871930966</v>
+        <v>3.459858425545707</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.879869161269576</v>
+        <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.957959122036439</v>
+        <v>-3.187535448410741</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.696329088141252</v>
+        <v>1.783736907030855</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.172464960823692</v>
+        <v>0.9428886344493874</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.583348137763791</v>
+        <v>3.624840691378532</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.871577137283435</v>
+        <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.931875037772631</v>
+        <v>-3.161451364146933</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.698470697860635</v>
+        <v>1.785878516750237</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.172464960823692</v>
+        <v>0.9428886344493874</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.57505611377765</v>
+        <v>3.616548667392391</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.869770332867214</v>
+        <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.84399712466351</v>
+        <v>-3.073573451037813</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.731815058688062</v>
+        <v>1.819222877577665</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.288390603247043</v>
+        <v>1.058814276872738</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.64280469481544</v>
+        <v>3.684297248430181</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.887324738594006</v>
+        <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.835104663270227</v>
+        <v>-3.064680989644529</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.752926448972167</v>
+        <v>1.840334267861769</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.288390603247043</v>
+        <v>1.058814276872738</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.660359100542232</v>
+        <v>3.701851654156972</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.879179785998589</v>
+        <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.003580780240104</v>
+        <v>-3.233157106614407</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.6773910495888</v>
+        <v>1.764798868478402</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.260442767530462</v>
+        <v>1.030866441156158</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.635445446516867</v>
+        <v>3.676938000131608</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782704</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.860449483186451</v>
+        <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.305781251378521</v>
+        <v>-2.535357577752824</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.937780558321295</v>
+        <v>2.025188377210897</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.190094708160052</v>
+        <v>0.960518381785747</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.574506308082483</v>
+        <v>3.615998861697223</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.851113505683356</v>
+        <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.283060147695369</v>
+        <v>-2.512636474069671</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.93753302229146</v>
+        <v>2.024940841181063</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.190094708160052</v>
+        <v>0.960518381785747</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.565170330579387</v>
+        <v>3.606662884194128</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.010019631534525</v>
+        <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.412261960989411</v>
+        <v>-2.641838287363714</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.044758422825013</v>
+        <v>2.132166241714615</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.060892894866009</v>
+        <v>0.8313165684917048</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.646555368454131</v>
+        <v>3.688047922068872</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.047097454028171</v>
+        <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.567042967767667</v>
+        <v>-2.796619294141969</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.019923842607357</v>
+        <v>2.107331661496959</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.027525220811533</v>
+        <v>0.7979488944372286</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.663612586515092</v>
+        <v>3.705105140129832</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.043772810017717</v>
+        <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.559988277552493</v>
+        <v>-2.789564603926796</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.019421074682971</v>
+        <v>2.106828893572574</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.034579911026707</v>
+        <v>0.8050035846524024</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.664520756633741</v>
+        <v>3.706013310248482</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.053778963662458</v>
+        <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.533037053226005</v>
+        <v>-2.762613379600308</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.040207718058308</v>
+        <v>2.127615536947911</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.049460257054426</v>
+        <v>0.8198839306801216</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.683455117895114</v>
+        <v>3.724947671509855</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784104</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.237882095807418</v>
+        <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.668990061282321</v>
+        <v>-2.898566387656624</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.169929646980742</v>
+        <v>2.257337465870344</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.049460257054426</v>
+        <v>0.8198839306801216</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.867558250040074</v>
+        <v>3.909050803654814</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.229998790710411</v>
+        <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.691398179087193</v>
+        <v>-2.920974505461496</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.153083094761786</v>
+        <v>2.240490913651388</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.049460257054426</v>
+        <v>0.8198839306801216</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.859674944943067</v>
+        <v>3.901167498557808</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.232052790260048</v>
+        <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.719622414664794</v>
+        <v>-2.949198741039096</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.143847400080383</v>
+        <v>2.231255218969985</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.067437009505735</v>
+        <v>0.8378606831314301</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.87251499596349</v>
+        <v>3.91400754957823</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.288306507981896</v>
+        <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.729063340553324</v>
+        <v>-2.958639666927626</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.196324747446818</v>
+        <v>2.283732566336421</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.189864127049126</v>
+        <v>0.9602878006748216</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.002224984211372</v>
+        <v>4.043717537826113</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.291197602527197</v>
+        <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.781336947888965</v>
+        <v>-3.010913274263268</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.178306399057862</v>
+        <v>2.265714217947465</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.137590519713485</v>
+        <v>0.9080141933391803</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.973751914355288</v>
+        <v>4.015244467970028</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.289309415420972</v>
+        <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.857666925489871</v>
+        <v>-3.087243251864173</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.145886220911275</v>
+        <v>2.233294039800878</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.137590519713485</v>
+        <v>0.9080141933391803</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.971863727249063</v>
+        <v>4.013356280863803</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.284129645023834</v>
+        <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.059920645814224</v>
+        <v>-3.289496972188527</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.059804962384396</v>
+        <v>2.147212781273999</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9353367993891315</v>
+        <v>0.7057604730148268</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.845331724657313</v>
+        <v>3.886824278272054</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.282563655233986</v>
+        <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.221489071341479</v>
+        <v>-3.451065397715782</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.993611602383647</v>
+        <v>2.081019421273249</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8085538755912521</v>
+        <v>0.5789775492169474</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.767695980588738</v>
+        <v>3.809188534203479</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.295637062099905</v>
+        <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.353790363439033</v>
+        <v>-3.583366689813335</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.953764492410544</v>
+        <v>2.041172311300146</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8085538755912521</v>
+        <v>0.5789775492169474</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.780769387454657</v>
+        <v>3.822261941069397</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.287642258882845</v>
+        <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.539658674278263</v>
+        <v>-3.769235000652565</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.871422364857792</v>
+        <v>1.958830183747394</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6499882822713045</v>
+        <v>0.4204119558969998</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.677635228245628</v>
+        <v>3.719127781860368</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.286166300009847</v>
+        <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.567559461387736</v>
+        <v>-3.797135787762038</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.858786091141005</v>
+        <v>1.946193910030607</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6153913581283696</v>
+        <v>0.385815031754065</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.655401114886869</v>
+        <v>3.69689366850161</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787381</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.282930743987046</v>
+        <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.69008556409063</v>
+        <v>-3.919661890464932</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.806540094037046</v>
+        <v>1.893947912926648</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4928652554254758</v>
+        <v>0.2632889290511711</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.578649897242332</v>
+        <v>3.620142450857072</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.349636703577549</v>
+        <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.920600060276218</v>
+        <v>-4.150176386650521</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.781040255153314</v>
+        <v>1.868448074042917</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.262350759239887</v>
+        <v>0.03277443286558235</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.507047159121482</v>
+        <v>3.548539712736222</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.64075008781466</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.489948422579396</v>
+        <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.177320878271042</v>
+        <v>-4.406897204645345</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.818663646957232</v>
+        <v>1.906071465846834</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1539361850960722</v>
+        <v>-0.07564014127823249</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.58231013363704</v>
+        <v>3.623802687251781</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.66828900423709</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.558928691725036</v>
+        <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.331307296047182</v>
+        <v>-4.560883622421485</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.826049348992415</v>
+        <v>1.913457167882018</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1539361850960722</v>
+        <v>-0.07564014127823249</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.65129040278268</v>
+        <v>3.692782956397421</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.544979893845157</v>
+        <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.280785392219516</v>
+        <v>-4.51036171859382</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.832309312643603</v>
+        <v>1.919717131533205</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1539361850960722</v>
+        <v>-0.07564014127823249</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.637341604902801</v>
+        <v>3.678834158517541</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609748</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.556850382900571</v>
+        <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.533260546227241</v>
+        <v>-4.762836872601544</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.743189740095927</v>
+        <v>1.830597558985529</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1539361850960722</v>
+        <v>-0.07564014127823249</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.649212093958215</v>
+        <v>3.690704647572955</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973152</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.558060917419515</v>
+        <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.826156302706653</v>
+        <v>-5.055732629080956</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.627241972023106</v>
+        <v>1.714649790912708</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1539361850960722</v>
+        <v>-0.07564014127823249</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.650422628477159</v>
+        <v>3.691915182091899</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251941</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.562182659646836</v>
+        <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.983700374436094</v>
+        <v>-5.213276700810398</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.56834608555865</v>
+        <v>1.655753904448253</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08703437995579771</v>
+        <v>-0.142541946418507</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.614403287620315</v>
+        <v>3.655895841235056</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.557260512383026</v>
+        <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.261664770019368</v>
+        <v>-5.491241096393671</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.45223818006153</v>
+        <v>1.539645998951133</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.00258535432968654</v>
+        <v>-0.2321616807039912</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.555709299785214</v>
+        <v>3.597201853399955</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.71946456908207</v>
+        <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.378632462658259</v>
+        <v>-5.608208789032562</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.567655159705018</v>
+        <v>1.65506297859462</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.00258535432968654</v>
+        <v>-0.2321616807039912</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.717913356484258</v>
+        <v>3.759405910098999</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.714311207045884</v>
+        <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.463350404879212</v>
+        <v>-5.692926731253515</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.528614620780451</v>
+        <v>1.616022439670053</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.08770138325773291</v>
+        <v>-0.3172777096320376</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.661690377091245</v>
+        <v>3.703182930705985</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.724540624614375</v>
+        <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.545285223148095</v>
+        <v>-5.774861549522399</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.506070111041389</v>
+        <v>1.593477929930991</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.0976361288448131</v>
+        <v>-0.3272124552191178</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.665958947307487</v>
+        <v>3.707451500922228</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.733466263070278</v>
+        <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.647261345396503</v>
+        <v>-5.876837671770806</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.474205300597928</v>
+        <v>1.56161311948753</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1996122510932207</v>
+        <v>-0.4291885774675254</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.613698912414345</v>
+        <v>3.655191466029086</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.725619150314453</v>
+        <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.537255061919281</v>
+        <v>-5.766831388293585</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.510360701232992</v>
+        <v>1.597768520122595</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1764076791759455</v>
+        <v>-0.4059840055502502</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.619774542808886</v>
+        <v>3.661267096423626</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.729869161036427</v>
+        <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.394195486178356</v>
+        <v>-5.623771812552659</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.571834542251337</v>
+        <v>1.659242361140939</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1683942525859662</v>
+        <v>-0.3979705789602709</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.628832609484848</v>
+        <v>3.670325163099589</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051783</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.737130043918963</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.092748760706518</v>
+        <v>-5.322325087080822</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.699674115322608</v>
+        <v>1.78708193421221</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1330524728858711</v>
+        <v>-0.09652385348843362</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.816961527650486</v>
+        <v>3.858454081265227</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.738101221671674</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.117339004941702</v>
+        <v>-5.346915331316006</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.690809195381245</v>
+        <v>1.778217014270847</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1330524728858711</v>
+        <v>-0.09652385348843362</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.817932705403197</v>
+        <v>3.859425259017937</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.738944126051429</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.066300628935182</v>
+        <v>-5.295876955309486</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.712067450163608</v>
+        <v>1.79947526905321</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1330524728858711</v>
+        <v>-0.09652385348843362</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.818775609782952</v>
+        <v>3.860268163397692</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.757982224925575</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.025161334068551</v>
+        <v>-5.254737660442855</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.747561266984406</v>
+        <v>1.834969085874008</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1741917677525019</v>
+        <v>-0.0553845586218028</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.862497285577076</v>
+        <v>3.903989839191816</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.574166221049509</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.914555193988949</v>
+        <v>-5.144131520363253</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.607987719140182</v>
+        <v>1.695395538029783</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2847979078321039</v>
+        <v>0.05522158145779921</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.745044965748772</v>
+        <v>3.786537519363512</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.577668265123473</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.045135928519792</v>
+        <v>-5.274712254894095</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.559257469401809</v>
+        <v>1.64666528829141</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1542171733012614</v>
+        <v>-0.07535915307304331</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.67019856910423</v>
+        <v>3.71169112271897</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.562095084199556</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.88063959432883</v>
+        <v>-5.110215920703133</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.609482822154276</v>
+        <v>1.696890641043877</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.1542171733012614</v>
+        <v>-0.07535915307304331</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.654625388180313</v>
+        <v>3.696117941795053</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.561282794635986</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.908009527013262</v>
+        <v>-5.137585853387566</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.597722559516933</v>
+        <v>1.685130378406534</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.1542171733012614</v>
+        <v>-0.07535915307304331</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.653813098616743</v>
+        <v>3.695305652231482</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.571151573761058</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.918394721903152</v>
+        <v>-5.147971048277455</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.60343726068605</v>
+        <v>1.690845079575651</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1438319784113721</v>
+        <v>-0.08574434796293262</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.657450760807882</v>
+        <v>3.698943314422622</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735281</v>
+        <v>3.834415493735279</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.641988579537483</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.936982880625377</v>
+        <v>-5.16655920699968</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.666839002973585</v>
+        <v>1.754246821863186</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1252438196891467</v>
+        <v>-0.104332506685158</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.717134871350972</v>
+        <v>3.758627424965711</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.85512053549655</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.638857590355782</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.937281427321413</v>
+        <v>-5.166857753695716</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.663588595113469</v>
+        <v>1.75099641400307</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1252438196891467</v>
+        <v>-0.104332506685158</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.71400388216927</v>
+        <v>3.75549643578401</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.643388485295173</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.836458293630985</v>
+        <v>-5.066034620005288</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.708448743529031</v>
+        <v>1.795856562418633</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.1377080351735006</v>
+        <v>-0.09186829120080414</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.726013306399274</v>
+        <v>3.767505860014014</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.643517738773717</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.645676932878578</v>
+        <v>-4.875253259252881</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.784890541308537</v>
+        <v>1.872298360198139</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3284893959259079</v>
+        <v>0.09891306955160323</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.840611376329262</v>
+        <v>3.882103929944001</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.623354584511313</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.627160078836758</v>
+        <v>-4.856736405211061</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.772134128662862</v>
+        <v>1.859541947552463</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.3414195253511161</v>
+        <v>0.1118431989768114</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.828206299721983</v>
+        <v>3.869698853336723</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.658321521123372</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.601966894335439</v>
+        <v>-4.831543220709743</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.817178339075448</v>
+        <v>1.904586157965049</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.3666127098524345</v>
+        <v>0.1370363834781298</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.878289147034832</v>
+        <v>3.919781700649573</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.652008089024809</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.589912767422477</v>
+        <v>-4.81948909379678</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.815686557742071</v>
+        <v>1.903094376631672</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.3786668367653973</v>
+        <v>0.1490905103910926</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.879208191084048</v>
+        <v>3.920700744698788</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.653888719208945</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.596536014112835</v>
+        <v>-4.826112340487138</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.814917889250063</v>
+        <v>1.902325708139665</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.372043590075039</v>
+        <v>0.1424672637007343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.877114873253969</v>
+        <v>3.918607426868708</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.666739745086828</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.493655424584242</v>
+        <v>-4.723231750958545</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.868921150939383</v>
+        <v>1.956328969828984</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.2453478532293272</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.951694252849007</v>
+        <v>3.993186806463747</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.686942415260422</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.517097463764329</v>
+        <v>-4.746673790138632</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.879747005440942</v>
+        <v>1.967154824330543</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.2453478532293272</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.971896923022602</v>
+        <v>4.013389476637341</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781701</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.686942415260422</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.53516997205594</v>
+        <v>-4.764746298430244</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.872518002124298</v>
+        <v>1.959925821013899</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.2453478532293272</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.971896923022602</v>
+        <v>4.013389476637341</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.647194328853888</v>
+        <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.714906277451456</v>
+        <v>-4.944482603825759</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.760875393559558</v>
+        <v>1.848283212449159</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.2453478532293272</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.932148836616068</v>
+        <v>3.973641390230807</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.845806060592298</v>
+        <v>3.443869434763677</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.813673360061921</v>
+        <v>3.674212194684115</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.714906277451456</v>
+        <v>-4.944482603825759</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.760875393559558</v>
+        <v>1.848283212449159</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.2453478532293272</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.806737157048289</v>
+        <v>3.667275991670483</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240808.xlsx
+++ b/tame_output/ON/bt/strategyON_20240808.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>87.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>125.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>432.0%</t>
+          <t>435.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-656.0%</t>
+          <t>-629.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-191.4%</t>
+          <t>-180.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-71.0%</t>
+          <t>-153.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-199.5%</t>
+          <t>-176.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-47.9%</t>
         </is>
       </c>
     </row>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.846438384567879</v>
+        <v>-8.673916174092536</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3787574299077954</v>
+        <v>-0.3097485457176585</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.507638861707055</v>
+        <v>-1.335116651231713</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.255591031208871</v>
+        <v>2.359104357494076</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.021562801954422</v>
+        <v>-8.84904059147908</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4342519761148962</v>
+        <v>-0.3652430919247589</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.682763279093599</v>
+        <v>-1.510241068618257</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.165071601524462</v>
+        <v>2.268584927809667</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.256014895968912</v>
+        <v>-9.083492685493569</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5352519786222878</v>
+        <v>-0.466243094432151</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.682763279093599</v>
+        <v>-1.510241068618257</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.157852436622866</v>
+        <v>2.261365762908071</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.360389626995358</v>
+        <v>-9.187867416520016</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5836740618068426</v>
+        <v>-0.5146651776167057</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.787138010120045</v>
+        <v>-1.614615799644703</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.088555407233022</v>
+        <v>2.192068733518227</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.413175782595685</v>
+        <v>-9.240653572120342</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6036727342084172</v>
+        <v>-0.5346638500182799</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.882813496702442</v>
+        <v>-1.7102912862271</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.032265905122141</v>
+        <v>2.135779231407345</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.539212575963974</v>
+        <v>-9.366690365488632</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6513937229266182</v>
+        <v>-0.5823848387364809</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.8575618738927</v>
+        <v>-1.685039663417358</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0501106074371</v>
+        <v>2.153623933722305</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.482140804068043</v>
+        <v>-9.309618593592701</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6245746784818449</v>
+        <v>-0.5555657942917076</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.8575618738927</v>
+        <v>-1.685039663417358</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.054100943123501</v>
+        <v>2.157614269408707</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.623812645792164</v>
+        <v>-9.451290435316821</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6827186420702347</v>
+        <v>-0.6137097578800974</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.8575618738927</v>
+        <v>-1.685039663417358</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.052625716224759</v>
+        <v>2.156139042509965</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.574221801367329</v>
+        <v>-9.401699590891987</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6478288941354289</v>
+        <v>-0.5788200099452916</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.807971029467866</v>
+        <v>-1.635448818992524</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.097433633044532</v>
+        <v>2.200946959329737</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.425303466895473</v>
+        <v>-9.25278125642013</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6013126939933691</v>
+        <v>-0.5323038098032318</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.776721438732693</v>
+        <v>-1.604199228257351</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.103132253838953</v>
+        <v>2.206645580124158</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.199458314176061</v>
+        <v>-9.026936103700718</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5013955598693958</v>
+        <v>-0.4323866756792585</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.734794763145529</v>
+        <v>-1.562272552670187</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13786733222746</v>
+        <v>2.241380658512665</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.074879657838469</v>
+        <v>-8.902357447363126</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4504249527783002</v>
+        <v>-0.3814160685881629</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.734794763145529</v>
+        <v>-1.562272552670187</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.139006476783519</v>
+        <v>2.242519803068724</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.127774945882756</v>
+        <v>-8.955252735407413</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4689492938339068</v>
+        <v>-0.39994040964377</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.729839417057083</v>
+        <v>-1.557317206581741</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.144613458598694</v>
+        <v>2.248126784883899</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.055641770594875</v>
+        <v>-8.883119560119532</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4343623194801181</v>
+        <v>-0.3653534352899808</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.729839417057083</v>
+        <v>-1.557317206581741</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.15034716283733</v>
+        <v>2.253860489122536</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.984275377985227</v>
+        <v>-8.811753167509885</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4155530248301242</v>
+        <v>-0.3465441406399874</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.658473024447435</v>
+        <v>-1.485950813972093</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.183429736009254</v>
+        <v>2.286943062294459</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.890816344000003</v>
+        <v>-8.71829413352466</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3880528925489419</v>
+        <v>-0.3190440083588051</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.658473024447435</v>
+        <v>-1.485950813972093</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.173546254696347</v>
+        <v>2.277059580981552</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.880163162446571</v>
+        <v>-8.707640951971229</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3856261804269434</v>
+        <v>-0.3166172962368061</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.658473024447435</v>
+        <v>-1.485950813972093</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.171711694196973</v>
+        <v>2.275225020482178</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.782256123770081</v>
+        <v>-8.609733913294738</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3467636799298077</v>
+        <v>-0.2777547957396709</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.590487274586879</v>
+        <v>-1.417965064111537</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.212202829139846</v>
+        <v>2.315716155425051</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.758302582794123</v>
+        <v>-8.58578037231878</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3365137573939312</v>
+        <v>-0.2675048732037939</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.566533733610921</v>
+        <v>-1.394011523135579</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.227243459870914</v>
+        <v>2.330756786156119</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.494242644471326</v>
+        <v>-8.321720433995983</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2441500982265645</v>
+        <v>-0.1751412140364272</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.302473795288125</v>
+        <v>-1.129951584812783</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.372419106702839</v>
+        <v>2.475932432988045</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.787163020966488</v>
+        <v>-7.614640810491145</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.0358947175150699</v>
+        <v>0.1049036017052072</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.302473795288125</v>
+        <v>-1.129951584812783</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.369632073042538</v>
+        <v>2.473145399327744</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.746978722600297</v>
+        <v>-7.574456512124955</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.05231206074938743</v>
+        <v>0.1213209449395247</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.262289496921934</v>
+        <v>-1.089767286446592</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.394086275950094</v>
+        <v>2.4975996022353</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.583578851660935</v>
+        <v>-7.411056641185592</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1170388303458894</v>
+        <v>0.1860477145360266</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.098889625982571</v>
+        <v>-0.9263674155072295</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.491493019734469</v>
+        <v>2.595006346019674</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.350097629431336</v>
+        <v>-7.177575418955993</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2183557480755813</v>
+        <v>0.2873646322657182</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8654084037529728</v>
+        <v>-0.6928861932776309</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.639506181910081</v>
+        <v>2.743019508195286</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.200431238423821</v>
+        <v>-7.027909027948478</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.275330094165628</v>
+        <v>0.3443389783557653</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7725049125104368</v>
+        <v>-0.599982702035095</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.692356066342643</v>
+        <v>2.795869392627848</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.125209880691897</v>
+        <v>-6.895633554317592</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3007861240054246</v>
+        <v>0.3926166545551468</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6972835547785128</v>
+        <v>-0.4677072284042083</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.732856367728824</v>
+        <v>2.870602163553407</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.969471548132155</v>
+        <v>-6.73989522175785</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3658965177169584</v>
+        <v>0.4577270482666802</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5415452222187712</v>
+        <v>-0.3119688958444667</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.829114427952306</v>
+        <v>2.966860223776889</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.720471749448574</v>
+        <v>-6.490895423074269</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4784027784140492</v>
+        <v>0.5702333089637714</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2925454235351905</v>
+        <v>-0.06296909716088606</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.991420648386113</v>
+        <v>3.129166444210696</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.826061739221679</v>
+        <v>-6.596485412847374</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.308190852905589</v>
+        <v>0.4000213834553108</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3981354133082949</v>
+        <v>-0.1685590869339904</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.800090724923032</v>
+        <v>2.937836520747615</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.844796641340276</v>
+        <v>-6.615220314965971</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3492412339352367</v>
+        <v>0.4410717644849584</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4037314229684262</v>
+        <v>-0.1741550965941217</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.845277461004039</v>
+        <v>2.983023256828622</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.696856599932676</v>
+        <v>-6.467280273558371</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2885383278101088</v>
+        <v>0.3803688583598306</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3834105070598686</v>
+        <v>-0.1538341806855641</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.737591087861006</v>
+        <v>2.875336883685589</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.643887077678688</v>
+        <v>-6.414310751304383</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3010121504582259</v>
+        <v>0.3928426810079477</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3304409848058797</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.760658814959922</v>
+        <v>2.898404610784504</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.478098881718397</v>
+        <v>-6.248522555344092</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3603668167472489</v>
+        <v>0.4521973472969711</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3304409848058797</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.753698202864828</v>
+        <v>2.891443998689411</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.444735675239628</v>
+        <v>-6.215159348865323</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3881744537198997</v>
+        <v>0.4800049842696215</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3304409848058797</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.768160557245972</v>
+        <v>2.905906353070554</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.336476538117107</v>
+        <v>-6.106900211742802</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4260102290281034</v>
+        <v>0.5178407595778252</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3304409848058797</v>
+        <v>-0.1008646584315753</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.762692677705167</v>
+        <v>2.900438473529749</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.213185403299976</v>
+        <v>-5.983609076925671</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4728247769655325</v>
+        <v>0.5646553075152547</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2071498499887492</v>
+        <v>0.02242647638555523</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.834165452606022</v>
+        <v>2.971911248430605</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.192036204396532</v>
+        <v>-5.962459878022227</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4889854347642348</v>
+        <v>0.5808159653139571</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1860006510853059</v>
+        <v>0.04357567528899858</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.854555950185413</v>
+        <v>2.992301746009995</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.948270762413088</v>
+        <v>-5.718694436038783</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5822723199046633</v>
+        <v>0.6741028504543856</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1860006510853059</v>
+        <v>0.04357567528899858</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.850336658532464</v>
+        <v>2.988082454357046</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.846507942135793</v>
+        <v>-5.616931615761488</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6251017619355976</v>
+        <v>0.7169322924853194</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1727815826928772</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.860392413487937</v>
+        <v>2.998138209312519</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.596657548186719</v>
+        <v>-5.367081221812414</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7177839944989293</v>
+        <v>0.8096145250486515</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1727815826928772</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.853134488471639</v>
+        <v>2.990880284296221</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.420765455719286</v>
+        <v>-5.191189129344981</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7917399550065514</v>
+        <v>0.8835704855562736</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1727815826928772</v>
+        <v>0.05679474368142728</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.856733611992288</v>
+        <v>2.99447940781687</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.249318992696822</v>
+        <v>-5.019742666322517</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8736460462700903</v>
+        <v>0.9654765768198126</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.001335119670414053</v>
+        <v>0.2282412067038904</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.972928995860319</v>
+        <v>3.110674791684902</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.175029426958483</v>
+        <v>-4.945453100584178</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.902382350181723</v>
+        <v>0.9942128807314452</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.07295444606792523</v>
+        <v>0.3025307724422297</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.01652321291962</v>
+        <v>3.154269008744202</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.111393684724549</v>
+        <v>-4.881817358350244</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9325314481296143</v>
+        <v>1.024361978679336</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1365901883018598</v>
+        <v>0.3661665146761642</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.059399459314298</v>
+        <v>3.197145255138881</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.999966925398629</v>
+        <v>-4.770390599024323</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9582964106437779</v>
+        <v>1.0501269411935</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1365901883018598</v>
+        <v>0.3661665146761642</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.040593718098093</v>
+        <v>3.178339513922676</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.010469548463917</v>
+        <v>-4.780893222089612</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9558384380425395</v>
+        <v>1.047668968592262</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1260875652365709</v>
+        <v>0.3556638916108754</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.036035220883798</v>
+        <v>3.17378101670838</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.938226980292723</v>
+        <v>-4.708650653918418</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9886647791458376</v>
+        <v>1.08049530969556</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1260875652365709</v>
+        <v>0.3556638916108754</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.039964534718618</v>
+        <v>3.1777103305432</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.920513293414857</v>
+        <v>-4.690936967040552</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9964288378143238</v>
+        <v>1.088259368364046</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1292688941334877</v>
+        <v>0.3588452205077922</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.042551915974108</v>
+        <v>3.18029771179869</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.81170840793513</v>
+        <v>-4.582132081560825</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.036948863226208</v>
+        <v>1.12877939377593</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1292688941334877</v>
+        <v>0.3588452205077922</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.039549987194101</v>
+        <v>3.177295783018684</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.59168760989812</v>
+        <v>-4.362111283523815</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.126536219451626</v>
+        <v>1.218366750001349</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2704887392014679</v>
+        <v>0.5000650655757723</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.125860931245503</v>
+        <v>3.263606727070086</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.458819920834842</v>
+        <v>-4.229243594460537</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.195577477878761</v>
+        <v>1.287408008428483</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2704887392014679</v>
+        <v>0.5000650655757723</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.141755114047327</v>
+        <v>3.279500909871909</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.338646837470344</v>
+        <v>-4.109070511096038</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.244792555664862</v>
+        <v>1.336623086214584</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3906618225659669</v>
+        <v>0.6202381489402713</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.215004808506328</v>
+        <v>3.352750604330911</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.203393476140366</v>
+        <v>-3.973817149766061</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.308982002758293</v>
+        <v>1.400812533308015</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5259151838959439</v>
+        <v>0.7554915102702484</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.306244927865754</v>
+        <v>3.443990723690337</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.263268303498059</v>
+        <v>-4.033691977123754</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.271069563216642</v>
+        <v>1.362900093766364</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4660403565382518</v>
+        <v>0.6956166829125563</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.256357522852565</v>
+        <v>3.394103318677147</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.143448072587222</v>
+        <v>-3.913871746212916</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.334286824815185</v>
+        <v>1.426117355364907</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4660403565382518</v>
+        <v>0.6956166829125563</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.271646692086773</v>
+        <v>3.409392487911356</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.145917779049028</v>
+        <v>-3.916341452674722</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.240943141552904</v>
+        <v>1.332773672102626</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4635706500764457</v>
+        <v>0.6931469764507501</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.177809067532131</v>
+        <v>3.315554863356714</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.214287965373038</v>
+        <v>-3.984711638998732</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.132856928508602</v>
+        <v>1.224687459058324</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4728463491126606</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.102636348439161</v>
+        <v>3.240382144263744</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.228076018220085</v>
+        <v>-3.998499691845779</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.117778416001674</v>
+        <v>1.209608946551397</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4728463491126606</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.093073057071053</v>
+        <v>3.230818852895635</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.283596094112674</v>
+        <v>-4.054019767738368</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.232601222336841</v>
+        <v>1.324431752886563</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4728463491126606</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.230103893763255</v>
+        <v>3.367849689587838</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.108121834320205</v>
+        <v>-3.878545507945899</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.307358158245616</v>
+        <v>1.399188688795339</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4728463491126606</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.234671125755043</v>
+        <v>3.372416921579625</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.219058086961454</v>
+        <v>-3.989481760587148</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.238725685950324</v>
+        <v>1.330556216500046</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4728463491126606</v>
+        <v>0.702422675486965</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.21041315451625</v>
+        <v>3.348158950340832</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.185394541489171</v>
+        <v>-3.955818215114866</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.180729417540687</v>
+        <v>1.272559948090409</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5065098945849424</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.159149595201069</v>
+        <v>3.296895391025652</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.125541922285448</v>
+        <v>-3.895965595911143</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.214842851654308</v>
+        <v>1.30667338220403</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5065098945849424</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.169321981633201</v>
+        <v>3.307067777457784</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.03929845925907</v>
+        <v>-3.809722132884765</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.24428650743872</v>
+        <v>1.336117037988442</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5065098945849424</v>
+        <v>0.7360862209592469</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.164268252207061</v>
+        <v>3.302014048031644</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.08460527865805</v>
+        <v>-3.855028952283745</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.217939555123653</v>
+        <v>1.309770085673375</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4656997315757117</v>
+        <v>0.6952760579500161</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.131557929846049</v>
+        <v>3.269303725670631</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.113638383360351</v>
+        <v>-3.849752511721149</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.206878186275834</v>
+        <v>1.312432534931515</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4656997315757117</v>
+        <v>0.6952760579500161</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.13210980287915</v>
+        <v>3.269855598703733</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.020827901909492</v>
+        <v>-3.756942030270289</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.173275070747544</v>
+        <v>1.278829419403225</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.558510213026571</v>
+        <v>0.7880865394008755</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.117068783641031</v>
+        <v>3.254814579465614</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.065217371238919</v>
+        <v>-3.801331499599717</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.157392758940374</v>
+        <v>1.262947107596055</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5141207436971433</v>
+        <v>0.7436970700714478</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.092308577967976</v>
+        <v>3.230054373792558</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.181758976344262</v>
+        <v>-3.91787310470506</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.10585182540996</v>
+        <v>1.21140617406564</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.3975791385918006</v>
+        <v>0.6271554649661051</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.017459323416493</v>
+        <v>3.155205119241076</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.069381975161589</v>
+        <v>-3.805496103522387</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.156293921713696</v>
+        <v>1.261848270369377</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.3975791385918006</v>
+        <v>0.6271554649661051</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.02295061924716</v>
+        <v>3.160696415071743</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.097162373062941</v>
+        <v>-3.83327650142374</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.156678964321694</v>
+        <v>1.262233312977374</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3697987406904475</v>
+        <v>0.599375067064752</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.017779582274887</v>
+        <v>3.15552537809947</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.21554304579308</v>
+        <v>-3.951657174153879</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9476824152302921</v>
+        <v>1.053236763885972</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3025808885394713</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.815804590984955</v>
+        <v>2.953550386809538</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.324157124236411</v>
+        <v>-4.06027125259721</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.024386444572165</v>
+        <v>1.129940793227846</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3025808885394713</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.935954251704161</v>
+        <v>3.073700047528743</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.288748085988268</v>
+        <v>-4.024862214349067</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.053063085973745</v>
+        <v>1.158617434629426</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3025808885394713</v>
+        <v>0.5321572149137758</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.950467277806484</v>
+        <v>3.088213073631066</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.250364423430117</v>
+        <v>-3.986478551790916</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.065835992339375</v>
+        <v>1.171390340995055</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3409645510976225</v>
+        <v>0.5705408774719269</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.970916916683743</v>
+        <v>3.108662712508325</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.073248093394951</v>
+        <v>-3.80936222175575</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.133411553198743</v>
+        <v>1.238965901854423</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3409645510976225</v>
+        <v>0.5705408774719269</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.967645945529045</v>
+        <v>3.105391741353627</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.118340338228497</v>
+        <v>-3.854454466589296</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.116058047027238</v>
+        <v>1.221612395682918</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2790685079282327</v>
+        <v>0.5086448343025372</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.931191711389324</v>
+        <v>3.068937507213907</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.938964916989729</v>
+        <v>-3.675079045350528</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.181595190829159</v>
+        <v>1.287149539484839</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4358452660989514</v>
+        <v>0.6654215924732558</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.01904474159817</v>
+        <v>3.156790537422753</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.983979130510335</v>
+        <v>-3.720093258871134</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.144396960752506</v>
+        <v>1.249951309408187</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4054963707843467</v>
+        <v>0.6350726971586512</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.981642859740997</v>
+        <v>3.119388655565579</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.250983640782771</v>
+        <v>-3.98709776914357</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.043286718982478</v>
+        <v>1.148841067638158</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2111333327413982</v>
+        <v>0.4407096591157026</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.870716599254173</v>
+        <v>3.008462395078756</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.352181422219943</v>
+        <v>-4.088295550580742</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.00201152830411</v>
+        <v>1.107565876959791</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.142724519196079</v>
+        <v>0.3723008455703835</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.828875233023483</v>
+        <v>2.966621028848066</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.345670455605631</v>
+        <v>-4.08178458396643</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.002215876504152</v>
+        <v>1.107770225159832</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.142724519196079</v>
+        <v>0.3723008455703835</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.8264751945778</v>
+        <v>2.964220990402382</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.326632327898333</v>
+        <v>-4.062746456259132</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.006355846795316</v>
+        <v>1.111910195450996</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.08454090786488444</v>
+        <v>0.3141172342391889</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.788089746987328</v>
+        <v>2.925835542811911</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.357758959048952</v>
+        <v>-4.093873087409751</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.113199595969259</v>
+        <v>1.218753944624939</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.08454090786488444</v>
+        <v>0.3141172342391889</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.907384148621519</v>
+        <v>3.045129944446101</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.37162572038287</v>
+        <v>-4.107739848743669</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.108486220421825</v>
+        <v>1.214040569077506</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.0466829911310615</v>
+        <v>0.276259317505366</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.885502727567358</v>
+        <v>3.023248523391941</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.32682154884294</v>
+        <v>-4.062935677203739</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.132416419434723</v>
+        <v>1.237970768090404</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.0466829911310615</v>
+        <v>0.276259317505366</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.891511257964284</v>
+        <v>3.029257053788867</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.179078578607937</v>
+        <v>-3.915192706968737</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.089463828805924</v>
+        <v>1.195018177461604</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2144903483659447</v>
+        <v>0.4440666747402491</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.890145893582413</v>
+        <v>3.027891689406996</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.262899799882636</v>
+        <v>-3.999013928243435</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.058728961827525</v>
+        <v>1.164283310483206</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2144903483659447</v>
+        <v>0.4440666747402491</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.892939515113894</v>
+        <v>3.030685310938477</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.256747093829851</v>
+        <v>-3.99286122219065</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.061852392640297</v>
+        <v>1.167406741295978</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2206430544187289</v>
+        <v>0.4502193807930334</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.897293487137223</v>
+        <v>3.035039282961806</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.273556391980353</v>
+        <v>-4.009670520341152</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.054209150120207</v>
+        <v>1.159763498775887</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2038337562682273</v>
+        <v>0.4334100826425318</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.886288384987033</v>
+        <v>3.024034180811615</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.211258393204231</v>
+        <v>-3.94737252156503</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.145463903427477</v>
+        <v>1.251018252083157</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2038337562682273</v>
+        <v>0.4334100826425318</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.952623938783854</v>
+        <v>3.090369734608436</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.009468195539073</v>
+        <v>-3.745582323899872</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.028471984207667</v>
+        <v>1.134026332863347</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4018519484373817</v>
+        <v>0.6314282748116862</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.873726855799474</v>
+        <v>3.011472651624056</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.060354908225268</v>
+        <v>-3.796469036586067</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.078407531455364</v>
+        <v>1.183961880111045</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.3509652357511872</v>
+        <v>0.5805415621254917</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.913485060509932</v>
+        <v>3.051230856334515</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.97374416557546</v>
+        <v>-3.70985829393626</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.127679564631331</v>
+        <v>1.233233913287011</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4295909669563454</v>
+        <v>0.6591672933306499</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.97528823534907</v>
+        <v>3.113034031173653</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.033953463580745</v>
+        <v>-3.770067591941544</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.102131826253889</v>
+        <v>1.207686174909569</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3693816689510609</v>
+        <v>0.5989579953253654</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.937698637370572</v>
+        <v>3.075444433195154</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.957531417148818</v>
+        <v>-3.693645545509618</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.131192262866588</v>
+        <v>1.236746611522268</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3693816689510609</v>
+        <v>0.5989579953253654</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.9361902554105</v>
+        <v>3.073936051235083</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.913158285510249</v>
+        <v>-3.649272413871049</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.148804382957452</v>
+        <v>1.254358731613132</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4137548005896295</v>
+        <v>0.643331126963934</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.962677001829077</v>
+        <v>3.10042279765366</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.935638636369134</v>
+        <v>-3.671752764729934</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.134206036752488</v>
+        <v>1.239760385408168</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4137548005896295</v>
+        <v>0.643331126963934</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.957070795967668</v>
+        <v>3.094816591792251</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.887982905808078</v>
+        <v>-3.624097034168878</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.159650086004715</v>
+        <v>1.265204434660395</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4614105311506851</v>
+        <v>0.6909868575249897</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.992045991332106</v>
+        <v>3.129791787156689</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.787464747309324</v>
+        <v>-3.523578875670124</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.204749722778942</v>
+        <v>1.310304071434622</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5619286896494398</v>
+        <v>0.7915050160237442</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.057249259806083</v>
+        <v>3.194995055630666</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.848131337711713</v>
+        <v>-3.584245466072513</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.167237759093859</v>
+        <v>1.272792107749539</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4802303729309061</v>
+        <v>0.7098066993052106</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.994984942250835</v>
+        <v>3.132730738075418</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.803292936103315</v>
+        <v>-3.539407064464115</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.189270822347846</v>
+        <v>1.294825171003526</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4847738058757756</v>
+        <v>0.71435013225008</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.001808704628386</v>
+        <v>3.139554500452968</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.822791392345323</v>
+        <v>-3.558905520706123</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.185632379482121</v>
+        <v>1.291186728137801</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4366891645958713</v>
+        <v>0.6662654909701757</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.977118859491521</v>
+        <v>3.114864655316104</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.778588555259422</v>
+        <v>-3.514702683620222</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.209193116844318</v>
+        <v>1.314747465499998</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4808920016817717</v>
+        <v>0.7104683280560762</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.009520164270898</v>
+        <v>3.147265960095481</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.815567582922866</v>
+        <v>-3.551681711283666</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.192811506248189</v>
+        <v>1.298365854903869</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5178659034731022</v>
+        <v>0.7474422298474067</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.030114505814944</v>
+        <v>3.167860301639527</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.657276165383593</v>
+        <v>-3.393390293744393</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.307375838446937</v>
+        <v>1.412930187102617</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5178659034731022</v>
+        <v>0.7474422298474067</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.081362270997984</v>
+        <v>3.219108066822567</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.449634161749117</v>
+        <v>-3.185748290109917</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.388873344494981</v>
+        <v>1.494427693150661</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7255079071075784</v>
+        <v>0.9550842334818829</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.204388177772923</v>
+        <v>3.342133973597505</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.398602069026589</v>
+        <v>-3.134716197387389</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.404234409822262</v>
+        <v>1.509788758477942</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7765399998301064</v>
+        <v>1.006116326204411</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.22995566164471</v>
+        <v>3.367701457469293</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.333377887899384</v>
+        <v>-3.069492016260184</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.447511486365849</v>
+        <v>1.553065835021529</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.841764180957312</v>
+        <v>1.071340507331616</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.286277574413738</v>
+        <v>3.42402337023832</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.29595086782825</v>
+        <v>-3.03206499618905</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.458443266693583</v>
+        <v>1.563997615349263</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8470157189864936</v>
+        <v>1.076592045360798</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.285389469530527</v>
+        <v>3.42313526535511</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.316062523862958</v>
+        <v>-3.052176652223758</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.45165539661094</v>
+        <v>1.55720974526662</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8580430639839128</v>
+        <v>1.087619390358217</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.293262668860219</v>
+        <v>3.431008464684802</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.262317709435754</v>
+        <v>-2.998431837796554</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.633711093403033</v>
+        <v>1.739265442058713</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8681063734243748</v>
+        <v>1.097682699798679</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.459858425545707</v>
+        <v>3.59760422137029</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.187535448410741</v>
+        <v>-2.923649576771541</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.783736907030855</v>
+        <v>1.889291255686535</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9428886344493874</v>
+        <v>1.172464960823692</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.624840691378532</v>
+        <v>3.762586487203115</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.161451364146933</v>
+        <v>-2.897565492507733</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.785878516750237</v>
+        <v>1.891432865405917</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9428886344493874</v>
+        <v>1.172464960823692</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.616548667392391</v>
+        <v>3.754294463216973</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.073573451037813</v>
+        <v>-2.809687579398612</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.819222877577665</v>
+        <v>1.924777226233345</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.058814276872738</v>
+        <v>1.288390603247043</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.684297248430181</v>
+        <v>3.822043044254764</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.064680989644529</v>
+        <v>-2.800795118005329</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.840334267861769</v>
+        <v>1.94588861651745</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.058814276872738</v>
+        <v>1.288390603247043</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.701851654156972</v>
+        <v>3.839597449981555</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.233157106614407</v>
+        <v>-2.969271234975207</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.764798868478402</v>
+        <v>1.870353217134082</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.030866441156158</v>
+        <v>1.260442767530462</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.676938000131608</v>
+        <v>3.814683795956191</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782704</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.535357577752824</v>
+        <v>-2.271471706113624</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.025188377210897</v>
+        <v>2.130742725866577</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.960518381785747</v>
+        <v>1.190094708160052</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.615998861697223</v>
+        <v>3.753744657521806</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.512636474069671</v>
+        <v>-2.248750602430471</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.024940841181063</v>
+        <v>2.130495189836743</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.960518381785747</v>
+        <v>1.190094708160052</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.606662884194128</v>
+        <v>3.744408680018711</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.641838287363714</v>
+        <v>-2.377952415724514</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.132166241714615</v>
+        <v>2.237720590370295</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8313165684917048</v>
+        <v>1.060892894866009</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.688047922068872</v>
+        <v>3.825793717893454</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.796619294141969</v>
+        <v>-2.532733422502769</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.107331661496959</v>
+        <v>2.212886010152639</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7979488944372286</v>
+        <v>1.027525220811533</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.705105140129832</v>
+        <v>3.842850935954415</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.789564603926796</v>
+        <v>-2.525678732287596</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.106828893572574</v>
+        <v>2.212383242228254</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8050035846524024</v>
+        <v>1.034579911026707</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.706013310248482</v>
+        <v>3.843759106073064</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.762613379600308</v>
+        <v>-2.498727507961108</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.127615536947911</v>
+        <v>2.233169885603591</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8198839306801216</v>
+        <v>1.049460257054426</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.724947671509855</v>
+        <v>3.862693467334438</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784104</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.898566387656624</v>
+        <v>-2.634680516017424</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.257337465870344</v>
+        <v>2.362891814526024</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8198839306801216</v>
+        <v>1.049460257054426</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.909050803654814</v>
+        <v>4.046796599479397</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.920974505461496</v>
+        <v>-2.657088633822296</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.240490913651388</v>
+        <v>2.346045262307068</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8198839306801216</v>
+        <v>1.049460257054426</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.901167498557808</v>
+        <v>4.03891329438239</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.949198741039096</v>
+        <v>-2.685312869399896</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.231255218969985</v>
+        <v>2.336809567625665</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8378606831314301</v>
+        <v>1.067437009505735</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.91400754957823</v>
+        <v>4.051753345402813</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.958639666927626</v>
+        <v>-2.694753795288426</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.283732566336421</v>
+        <v>2.389286914992101</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9602878006748216</v>
+        <v>1.189864127049126</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.043717537826113</v>
+        <v>4.181463333650695</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.010913274263268</v>
+        <v>-2.747027402624068</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.265714217947465</v>
+        <v>2.371268566603145</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9080141933391803</v>
+        <v>1.137590519713485</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.015244467970028</v>
+        <v>4.152990263794611</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.087243251864173</v>
+        <v>-2.823357380224973</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.233294039800878</v>
+        <v>2.338848388456558</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9080141933391803</v>
+        <v>1.137590519713485</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.013356280863803</v>
+        <v>4.151102076688386</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.289496972188527</v>
+        <v>-3.025611100549327</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.147212781273999</v>
+        <v>2.252767129929679</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7057604730148268</v>
+        <v>0.9353367993891315</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.886824278272054</v>
+        <v>4.024570074096637</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.451065397715782</v>
+        <v>-3.187179526076582</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.081019421273249</v>
+        <v>2.186573769928929</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5789775492169474</v>
+        <v>0.8085538755912521</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.809188534203479</v>
+        <v>3.946934330028061</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.583366689813335</v>
+        <v>-3.319480818174135</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.041172311300146</v>
+        <v>2.146726659955826</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5789775492169474</v>
+        <v>0.8085538755912521</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.822261941069397</v>
+        <v>3.96000773689398</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.769235000652565</v>
+        <v>-3.505349129013365</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.958830183747394</v>
+        <v>2.064384532403074</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4204119558969998</v>
+        <v>0.6499882822713045</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.719127781860368</v>
+        <v>3.856873577684951</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.797135787762038</v>
+        <v>-3.533249916122838</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.946193910030607</v>
+        <v>2.051748258686287</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.385815031754065</v>
+        <v>0.6153913581283696</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.69689366850161</v>
+        <v>3.834639464326192</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787381</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.919661890464932</v>
+        <v>-3.655776018825732</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.893947912926648</v>
+        <v>1.999502261582328</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2632889290511711</v>
+        <v>0.4928652554254758</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.620142450857072</v>
+        <v>3.757888246681655</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.150176386650521</v>
+        <v>-3.886290515011321</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.868448074042917</v>
+        <v>1.974002422698597</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.03277443286558235</v>
+        <v>0.262350759239887</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.548539712736222</v>
+        <v>3.686285508560805</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.64075008781466</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.406897204645345</v>
+        <v>-4.143011333006145</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.906071465846834</v>
+        <v>2.011625814502514</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.07564014127823249</v>
+        <v>0.1539361850960722</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.623802687251781</v>
+        <v>3.761548483076364</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.66828900423709</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.560883622421485</v>
+        <v>-4.296997750782285</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.913457167882018</v>
+        <v>2.019011516537698</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.07564014127823249</v>
+        <v>0.1539361850960722</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.692782956397421</v>
+        <v>3.830528752222004</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423383</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.51036171859382</v>
+        <v>-4.24647584695462</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.919717131533205</v>
+        <v>2.025271480188885</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.07564014127823249</v>
+        <v>0.1539361850960722</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.678834158517541</v>
+        <v>3.816579954342124</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609748</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.762836872601544</v>
+        <v>-4.498951000962344</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.830597558985529</v>
+        <v>1.936151907641209</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.07564014127823249</v>
+        <v>0.1539361850960722</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.690704647572955</v>
+        <v>3.828450443397538</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973152</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.055732629080956</v>
+        <v>-4.791846757441756</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.714649790912708</v>
+        <v>1.820204139568388</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.07564014127823249</v>
+        <v>0.1539361850960722</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.691915182091899</v>
+        <v>3.829660977916482</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251941</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.213276700810398</v>
+        <v>-4.949390829171198</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.655753904448253</v>
+        <v>1.761308253103933</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.142541946418507</v>
+        <v>0.08703437995579771</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.655895841235056</v>
+        <v>3.793641637059638</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.491241096393671</v>
+        <v>-5.227355224754471</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.539645998951133</v>
+        <v>1.645200347606813</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2321616807039912</v>
+        <v>-0.00258535432968654</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.597201853399955</v>
+        <v>3.734947649224537</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.608208789032562</v>
+        <v>-5.344322917393362</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.65506297859462</v>
+        <v>1.760617327250301</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2321616807039912</v>
+        <v>-0.00258535432968654</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.759405910098999</v>
+        <v>3.897151705923582</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.692926731253515</v>
+        <v>-5.429040859614315</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.616022439670053</v>
+        <v>1.721576788325733</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3172777096320376</v>
+        <v>-0.08770138325773291</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.703182930705985</v>
+        <v>3.840928726530568</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.774861549522399</v>
+        <v>-5.510975677883199</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.593477929930991</v>
+        <v>1.699032278586671</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3272124552191178</v>
+        <v>-0.0976361288448131</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.707451500922228</v>
+        <v>3.845197296746811</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.876837671770806</v>
+        <v>-5.612951800131606</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.56161311948753</v>
+        <v>1.66716746814321</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4291885774675254</v>
+        <v>-0.1996122510932207</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.655191466029086</v>
+        <v>3.792937261853669</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.766831388293585</v>
+        <v>-5.502945516654385</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.597768520122595</v>
+        <v>1.703322868778275</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4059840055502502</v>
+        <v>-0.1764076791759455</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.661267096423626</v>
+        <v>3.799012892248209</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.623771812552659</v>
+        <v>-5.359885940913459</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.659242361140939</v>
+        <v>1.764796709796619</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3979705789602709</v>
+        <v>-0.1683942525859662</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.670325163099589</v>
+        <v>3.808070958924171</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051783</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.322325087080822</v>
+        <v>-5.058439215441622</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.78708193421221</v>
+        <v>1.89263628286789</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.09652385348843362</v>
+        <v>0.1330524728858711</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.858454081265227</v>
+        <v>3.99619987708981</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.346915331316006</v>
+        <v>-5.083029459676806</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.778217014270847</v>
+        <v>1.883771362926527</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.09652385348843362</v>
+        <v>0.1330524728858711</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.859425259017937</v>
+        <v>3.997171054842521</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.295876955309486</v>
+        <v>-5.031991083670285</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.79947526905321</v>
+        <v>1.90502961770889</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.09652385348843362</v>
+        <v>0.1330524728858711</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.860268163397692</v>
+        <v>3.998013959222275</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969539</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.254737660442855</v>
+        <v>-4.990851788803655</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.834969085874008</v>
+        <v>1.940523434529688</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.0553845586218028</v>
+        <v>0.1741917677525019</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.903989839191816</v>
+        <v>4.0417356350164</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.144131520363253</v>
+        <v>-4.880245648724053</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.695395538029783</v>
+        <v>1.800949886685463</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.05522158145779921</v>
+        <v>0.2847979078321039</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.786537519363512</v>
+        <v>3.924283315188095</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.274712254894095</v>
+        <v>-5.010826383254895</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.64666528829141</v>
+        <v>1.75221963694709</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.07535915307304331</v>
+        <v>0.1542171733012614</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.71169112271897</v>
+        <v>3.849436918543553</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.110215920703133</v>
+        <v>-4.846330049063933</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.696890641043877</v>
+        <v>1.802444989699557</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.07535915307304331</v>
+        <v>0.1542171733012614</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.696117941795053</v>
+        <v>3.833863737619636</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077624</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.137585853387566</v>
+        <v>-4.873699981748365</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.685130378406534</v>
+        <v>1.790684727062214</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.07535915307304331</v>
+        <v>0.1542171733012614</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.695305652231482</v>
+        <v>3.833051448056065</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.147971048277455</v>
+        <v>-4.884085176638255</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.690845079575651</v>
+        <v>1.796399428231331</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.08574434796293262</v>
+        <v>0.1438319784113721</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.698943314422622</v>
+        <v>3.836689110247204</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735279</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.16655920699968</v>
+        <v>-4.90267333536048</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.754246821863186</v>
+        <v>1.859801170518866</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.104332506685158</v>
+        <v>0.1252438196891467</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.758627424965711</v>
+        <v>3.896373220790294</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.85512053549655</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.166857753695716</v>
+        <v>-4.902971882056516</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.75099641400307</v>
+        <v>1.85655076265875</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.104332506685158</v>
+        <v>0.1252438196891467</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.75549643578401</v>
+        <v>3.893242231608593</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.066034620005288</v>
+        <v>-4.802148748366088</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.795856562418633</v>
+        <v>1.901410911074313</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.09186829120080414</v>
+        <v>0.1377080351735006</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.767505860014014</v>
+        <v>3.905251655838597</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.875253259252881</v>
+        <v>-4.611367387613681</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.872298360198139</v>
+        <v>1.977852708853819</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.09891306955160323</v>
+        <v>0.3284893959259079</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.882103929944001</v>
+        <v>4.019849725768585</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.856736405211061</v>
+        <v>-4.592850533571861</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.859541947552463</v>
+        <v>1.965096296208143</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.1118431989768114</v>
+        <v>0.3414195253511161</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.869698853336723</v>
+        <v>4.007444649161306</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.831543220709743</v>
+        <v>-4.567657349070543</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.904586157965049</v>
+        <v>2.010140506620729</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.1370363834781298</v>
+        <v>0.3666127098524345</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.919781700649573</v>
+        <v>4.057527496474155</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.81948909379678</v>
+        <v>-4.55560322215758</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.903094376631672</v>
+        <v>2.008648725287352</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.1490905103910926</v>
+        <v>0.3786668367653973</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.920700744698788</v>
+        <v>4.05844654052337</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.826112340487138</v>
+        <v>-4.562226468847938</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.902325708139665</v>
+        <v>2.007880056795345</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.1424672637007343</v>
+        <v>0.372043590075039</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.918607426868708</v>
+        <v>4.056353222693291</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.723231750958545</v>
+        <v>-4.459345879319345</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.956328969828984</v>
+        <v>2.061883318484664</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.2453478532293272</v>
+        <v>0.4749241796036319</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.993186806463747</v>
+        <v>4.13093260228833</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760311</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.746673790138632</v>
+        <v>-4.482787918499432</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.967154824330543</v>
+        <v>2.072709172986223</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.2453478532293272</v>
+        <v>0.4749241796036319</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.013389476637341</v>
+        <v>4.151135272461924</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781701</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.764746298430244</v>
+        <v>-4.500860426791044</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.959925821013899</v>
+        <v>2.065480169669579</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.2453478532293272</v>
+        <v>0.4749241796036319</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.013389476637341</v>
+        <v>4.151135272461924</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.944482603825759</v>
+        <v>-4.680596732186559</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.848283212449159</v>
+        <v>1.95383756110484</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.2453478532293272</v>
+        <v>0.4749241796036319</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.973641390230807</v>
+        <v>4.11138718605539</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.443869434763677</v>
+        <v>3.868994597472571</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.674212194684115</v>
+        <v>3.987962901173263</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.944482603825759</v>
+        <v>-4.680596732186559</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.848283212449159</v>
+        <v>1.95383756110484</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.2453478532293272</v>
+        <v>0.4749241796036319</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.667275991670483</v>
+        <v>3.981026698159631</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240808.xlsx
+++ b/tame_output/ON/bt/strategyON_20240808.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>50.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>74.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.4%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>435.0%</t>
+          <t>434.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-629.6%</t>
+          <t>-651.7%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-180.8%</t>
+          <t>-197.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-39.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.9%</t>
+          <t>-263.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-176.5%</t>
+          <t>-168.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-60.5%</t>
         </is>
       </c>
     </row>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003597</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.849752511721149</v>
+        <v>-3.884062056986047</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.312432534931515</v>
+        <v>1.298708716825556</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6952760579500161</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.756942030270289</v>
+        <v>-3.791251575535187</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.278829419403225</v>
+        <v>1.265105601297265</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7880865394008755</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.801331499599717</v>
+        <v>-3.835641044864615</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.262947107596055</v>
+        <v>1.249223289490095</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7436970700714478</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.91787310470506</v>
+        <v>-3.952182649969958</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.21140617406564</v>
+        <v>1.197682355959681</v>
       </c>
       <c r="F1948" t="n">
         <v>0.6271554649661051</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.805496103522387</v>
+        <v>-3.839805648787285</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.261848270369377</v>
+        <v>1.248124452263417</v>
       </c>
       <c r="F1949" t="n">
         <v>0.6271554649661051</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.83327650142374</v>
+        <v>-3.867586046688638</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.262233312977374</v>
+        <v>1.248509494871415</v>
       </c>
       <c r="F1950" t="n">
         <v>0.599375067064752</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.951657174153879</v>
+        <v>-3.985966719418777</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.053236763885972</v>
+        <v>1.039512945780013</v>
       </c>
       <c r="F1951" t="n">
         <v>0.5321572149137758</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.06027125259721</v>
+        <v>-4.094580797862108</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.129940793227846</v>
+        <v>1.116216975121886</v>
       </c>
       <c r="F1952" t="n">
         <v>0.5321572149137758</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.024862214349067</v>
+        <v>-4.059171759613965</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.158617434629426</v>
+        <v>1.144893616523467</v>
       </c>
       <c r="F1953" t="n">
         <v>0.5321572149137758</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.986478551790916</v>
+        <v>-4.020788097055814</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.171390340995055</v>
+        <v>1.157666522889096</v>
       </c>
       <c r="F1954" t="n">
         <v>0.5705408774719269</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.80936222175575</v>
+        <v>-3.843671767020648</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.238965901854423</v>
+        <v>1.225242083748464</v>
       </c>
       <c r="F1955" t="n">
         <v>0.5705408774719269</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.854454466589296</v>
+        <v>-3.888764011854193</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.221612395682918</v>
+        <v>1.207888577576959</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5086448343025372</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.675079045350528</v>
+        <v>-3.709388590615426</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.287149539484839</v>
+        <v>1.27342572137888</v>
       </c>
       <c r="F1957" t="n">
         <v>0.6654215924732558</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.720093258871134</v>
+        <v>-3.754402804136032</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.249951309408187</v>
+        <v>1.236227491302228</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6350726971586512</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.98709776914357</v>
+        <v>-4.021407314408467</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.148841067638158</v>
+        <v>1.135117249532199</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4407096591157026</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.088295550580742</v>
+        <v>-4.12260509584564</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.107565876959791</v>
+        <v>1.093842058853832</v>
       </c>
       <c r="F1960" t="n">
         <v>0.3723008455703835</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.08178458396643</v>
+        <v>-4.116094129231327</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.107770225159832</v>
+        <v>1.094046407053873</v>
       </c>
       <c r="F1961" t="n">
         <v>0.3723008455703835</v>
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.062746456259132</v>
+        <v>-4.09705600152403</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.111910195450996</v>
+        <v>1.098186377345037</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.4495225846088753</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.925835542811911</v>
+        <v>3.007078753033722</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.093873087409751</v>
+        <v>-4.128182632674648</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.218753944624939</v>
+        <v>1.20503012651898</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3141172342391889</v>
+        <v>0.4495225846088753</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.045129944446101</v>
+        <v>3.126373154667913</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.107739848743669</v>
+        <v>-4.142049394008566</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.214040569077506</v>
+        <v>1.200316750971547</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.276259317505366</v>
+        <v>0.4116646678750523</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.023248523391941</v>
+        <v>3.104491733613753</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.062935677203739</v>
+        <v>-4.097245222468636</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.237970768090404</v>
+        <v>1.224246949984444</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.276259317505366</v>
+        <v>0.4116646678750523</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.029257053788867</v>
+        <v>3.110500264010679</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.915192706968737</v>
+        <v>-3.949502252233634</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.195018177461604</v>
+        <v>1.181294359355645</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.5794720251099355</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.027891689406996</v>
+        <v>3.109134899628808</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.999013928243435</v>
+        <v>-4.033323473508332</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.164283310483206</v>
+        <v>1.150559492377247</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4440666747402491</v>
+        <v>0.5794720251099355</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.030685310938477</v>
+        <v>3.111928521160289</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.99286122219065</v>
+        <v>-4.027170767455548</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.167406741295978</v>
+        <v>1.153682923190019</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4502193807930334</v>
+        <v>0.5856247311627197</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.035039282961806</v>
+        <v>3.116282493183618</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.009670520341152</v>
+        <v>-4.04398006560605</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.159763498775887</v>
+        <v>1.146039680669928</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.5688154330122182</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.024034180811615</v>
+        <v>3.105277391033427</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.94737252156503</v>
+        <v>-3.981682066829928</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.251018252083157</v>
+        <v>1.237294433977198</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4334100826425318</v>
+        <v>0.5688154330122182</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.090369734608436</v>
+        <v>3.171612944830248</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.745582323899872</v>
+        <v>-3.77989186916477</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.134026332863347</v>
+        <v>1.120302514757388</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6314282748116862</v>
+        <v>0.7668336251813725</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.011472651624056</v>
+        <v>3.092715861845868</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.796469036586067</v>
+        <v>-3.830778581850965</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.183961880111045</v>
+        <v>1.170238062005085</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5805415621254917</v>
+        <v>0.7159469124951781</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.051230856334515</v>
+        <v>3.132474066556326</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.70985829393626</v>
+        <v>-3.744167839201157</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.233233913287011</v>
+        <v>1.219510095181052</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6591672933306499</v>
+        <v>0.7945726437003363</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.113034031173653</v>
+        <v>3.194277241395465</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.770067591941544</v>
+        <v>-3.804377137206442</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.207686174909569</v>
+        <v>1.19396235680361</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.7343633456950518</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.075444433195154</v>
+        <v>3.156687643416966</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.693645545509618</v>
+        <v>-3.727955090774515</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.236746611522268</v>
+        <v>1.223022793416309</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5989579953253654</v>
+        <v>0.7343633456950518</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.073936051235083</v>
+        <v>3.155179261456894</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.649272413871049</v>
+        <v>-3.683581959135946</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.254358731613132</v>
+        <v>1.240634913507173</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.643331126963934</v>
+        <v>0.7787364773336204</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.10042279765366</v>
+        <v>3.181666007875472</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.671752764729934</v>
+        <v>-3.706062309994831</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.239760385408168</v>
+        <v>1.226036567302209</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.643331126963934</v>
+        <v>0.7787364773336204</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.094816591792251</v>
+        <v>3.176059802014062</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.624097034168878</v>
+        <v>-3.658406579433776</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.265204434660395</v>
+        <v>1.251480616554436</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6909868575249897</v>
+        <v>0.826392207894676</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.129791787156689</v>
+        <v>3.2110349973785</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.523578875670124</v>
+        <v>-3.643322467058094</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.310304071434622</v>
+        <v>1.262406634879434</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7915050160237442</v>
+        <v>0.8414763202703581</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.194995055630666</v>
+        <v>3.224977838178634</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.584245466072513</v>
+        <v>-3.703989057460483</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.272792107749539</v>
+        <v>1.22489467119435</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7098066993052106</v>
+        <v>0.7597780035518245</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.132730738075418</v>
+        <v>3.162713520623386</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.539407064464115</v>
+        <v>-3.659150655852085</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.294825171003526</v>
+        <v>1.246927734448338</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.71435013225008</v>
+        <v>0.7643214364966939</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.139554500452968</v>
+        <v>3.169537283000937</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.558905520706123</v>
+        <v>-3.678649112094093</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.291186728137801</v>
+        <v>1.243289291582613</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6662654909701757</v>
+        <v>0.7162367952167896</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.114864655316104</v>
+        <v>3.144847437864072</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.514702683620222</v>
+        <v>-3.634446275008193</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.314747465499998</v>
+        <v>1.26685002894481</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7104683280560762</v>
+        <v>0.7604396323026901</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.147265960095481</v>
+        <v>3.177248742643449</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.551681711283666</v>
+        <v>-3.671425302671636</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.298365854903869</v>
+        <v>1.25046841834868</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7474422298474067</v>
+        <v>0.7974135340940206</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.167860301639527</v>
+        <v>3.197843084187495</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.393390293744393</v>
+        <v>-3.513133885132364</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.412930187102617</v>
+        <v>1.365032750547429</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7474422298474067</v>
+        <v>0.7974135340940206</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.219108066822567</v>
+        <v>3.249090849370535</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.185748290109917</v>
+        <v>-3.305491881497888</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.494427693150661</v>
+        <v>1.446530256595473</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9550842334818829</v>
+        <v>1.005055537728497</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.342133973597505</v>
+        <v>3.372116756145474</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475134</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.134716197387389</v>
+        <v>-3.254459788775359</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.509788758477942</v>
+        <v>1.461891321922754</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.006116326204411</v>
+        <v>1.056087630451025</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.367701457469293</v>
+        <v>3.397684240017261</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.069492016260184</v>
+        <v>-3.189235607648154</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.553065835021529</v>
+        <v>1.505168398466341</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.071340507331616</v>
+        <v>1.121311811578231</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.42402337023832</v>
+        <v>3.454006152786289</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.03206499618905</v>
+        <v>-3.15180858757702</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.563997615349263</v>
+        <v>1.516100178794075</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.076592045360798</v>
+        <v>1.126563349607412</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.42313526535511</v>
+        <v>3.453118047903079</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.052176652223758</v>
+        <v>-3.171920243611729</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.55720974526662</v>
+        <v>1.509312308711432</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.087619390358217</v>
+        <v>1.137590694604832</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.431008464684802</v>
+        <v>3.46099124723277</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.998431837796554</v>
+        <v>-3.118175429184524</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.739265442058713</v>
+        <v>1.691368005503525</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.097682699798679</v>
+        <v>1.147654004045294</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.59760422137029</v>
+        <v>3.627587003918258</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.923649576771541</v>
+        <v>-3.043393168159511</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.889291255686535</v>
+        <v>1.841393819131347</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.172464960823692</v>
+        <v>1.222436265070306</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.762586487203115</v>
+        <v>3.792569269751083</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.897565492507733</v>
+        <v>-3.017309083895703</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.891432865405917</v>
+        <v>1.843535428850729</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.172464960823692</v>
+        <v>1.222436265070306</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.754294463216973</v>
+        <v>3.784277245764942</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.809687579398612</v>
+        <v>-2.929431170786583</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.924777226233345</v>
+        <v>1.876879789678157</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.288390603247043</v>
+        <v>1.338361907493657</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.822043044254764</v>
+        <v>3.852025826802732</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.800795118005329</v>
+        <v>-2.920538709393299</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.94588861651745</v>
+        <v>1.897991179962261</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.288390603247043</v>
+        <v>1.338361907493657</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.839597449981555</v>
+        <v>3.869580232529524</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.969271234975207</v>
+        <v>-3.089014826363177</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.870353217134082</v>
+        <v>1.822455780578894</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.260442767530462</v>
+        <v>1.310414071777077</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.814683795956191</v>
+        <v>3.844666578504159</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.271471706113624</v>
+        <v>-2.391215297501594</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.130742725866577</v>
+        <v>2.082845289311389</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.190094708160052</v>
+        <v>1.240066012406666</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.753744657521806</v>
+        <v>3.783727440069775</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.248750602430471</v>
+        <v>-2.368494193818441</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.130495189836743</v>
+        <v>2.082597753281555</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.190094708160052</v>
+        <v>1.240066012406666</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.744408680018711</v>
+        <v>3.774391462566679</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.377952415724514</v>
+        <v>-2.497696007112484</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.237720590370295</v>
+        <v>2.189823153815107</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.060892894866009</v>
+        <v>1.110864199112624</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.825793717893454</v>
+        <v>3.855776500441423</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.532733422502769</v>
+        <v>-2.652477013890739</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.212886010152639</v>
+        <v>2.164988573597451</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.027525220811533</v>
+        <v>1.077496525058148</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.842850935954415</v>
+        <v>3.872833718502384</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.525678732287596</v>
+        <v>-2.645422323675566</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.212383242228254</v>
+        <v>2.164485805673066</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.034579911026707</v>
+        <v>1.084551215273321</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.843759106073064</v>
+        <v>3.873741888621033</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331111</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.498727507961108</v>
+        <v>-2.618471099349078</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.233169885603591</v>
+        <v>2.185272449048402</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.049460257054426</v>
+        <v>1.099431561301041</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.862693467334438</v>
+        <v>3.892676249882406</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.634680516017424</v>
+        <v>-2.754424107405394</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.362891814526024</v>
+        <v>2.314994377970836</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.049460257054426</v>
+        <v>1.099431561301041</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.046796599479397</v>
+        <v>4.076779382027366</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.657088633822296</v>
+        <v>-2.776832225210266</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.346045262307068</v>
+        <v>2.29814782575188</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.049460257054426</v>
+        <v>1.099431561301041</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.03891329438239</v>
+        <v>4.068896076930359</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.685312869399896</v>
+        <v>-2.906029770043186</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.336809567625665</v>
+        <v>2.248522807368349</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.067437009505735</v>
+        <v>1.14962246615839</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.051753345402813</v>
+        <v>4.101064619394407</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.694753795288426</v>
+        <v>-2.915470695931716</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.389286914992101</v>
+        <v>2.301000154734785</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.189864127049126</v>
+        <v>1.272049583701782</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.181463333650695</v>
+        <v>4.230774607642289</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.747027402624068</v>
+        <v>-2.967744303267357</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.371268566603145</v>
+        <v>2.282981806345829</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.137590519713485</v>
+        <v>1.219775976366141</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.152990263794611</v>
+        <v>4.202301537786204</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347699</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.823357380224973</v>
+        <v>-3.044074280868263</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.338848388456558</v>
+        <v>2.250561628199242</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.137590519713485</v>
+        <v>1.219775976366141</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.151102076688386</v>
+        <v>4.200413350679979</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.025611100549327</v>
+        <v>-3.246328001192616</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.252767129929679</v>
+        <v>2.164480369672363</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9353367993891315</v>
+        <v>1.017522256041787</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.024570074096637</v>
+        <v>4.07388134808823</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.187179526076582</v>
+        <v>-3.407896426719871</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.186573769928929</v>
+        <v>2.098287009671613</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8085538755912521</v>
+        <v>0.8907393322439078</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.946934330028061</v>
+        <v>3.996245604019655</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.319480818174135</v>
+        <v>-3.540197718817425</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.146726659955826</v>
+        <v>2.05843989969851</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8085538755912521</v>
+        <v>0.8907393322439078</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.96000773689398</v>
+        <v>4.009319010885573</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.505349129013365</v>
+        <v>-3.726066029656655</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.064384532403074</v>
+        <v>1.976097772145758</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6499882822713045</v>
+        <v>0.7321737389239601</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.856873577684951</v>
+        <v>3.906184851676545</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.71581989500697</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.533249916122838</v>
+        <v>-3.753966816766128</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.051748258686287</v>
+        <v>1.963461498428972</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6153913581283696</v>
+        <v>0.6975768147810253</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.834639464326192</v>
+        <v>3.883950738317786</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787381</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.655776018825732</v>
+        <v>-3.876492919469022</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.999502261582328</v>
+        <v>1.911215501325013</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4928652554254758</v>
+        <v>0.5750507120781314</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.757888246681655</v>
+        <v>3.807199520673248</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585932</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.886290515011321</v>
+        <v>-4.107007415654611</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.974002422698597</v>
+        <v>1.885715662441281</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.262350759239887</v>
+        <v>0.3445362158925427</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.686285508560805</v>
+        <v>3.735596782552399</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814659</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.143011333006145</v>
+        <v>-4.363728233649434</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.011625814502514</v>
+        <v>1.923339054245198</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1539361850960722</v>
+        <v>0.2361216417487279</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.761548483076364</v>
+        <v>3.810859757067957</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237089</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.296997750782285</v>
+        <v>-4.517714651425575</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.019011516537698</v>
+        <v>1.930724756280382</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1539361850960722</v>
+        <v>0.2361216417487279</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.830528752222004</v>
+        <v>3.879840026213597</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423382</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.24647584695462</v>
+        <v>-4.467192747597909</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.025271480188885</v>
+        <v>1.936984719931569</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1539361850960722</v>
+        <v>0.2361216417487279</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.816579954342124</v>
+        <v>3.865891228333718</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609747</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.498951000962344</v>
+        <v>-4.719667901605633</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.936151907641209</v>
+        <v>1.847865147383893</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1539361850960722</v>
+        <v>0.2361216417487279</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.828450443397538</v>
+        <v>3.877761717389132</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973151</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.791846757441756</v>
+        <v>-5.012563658085045</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.820204139568388</v>
+        <v>1.731917379311072</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1539361850960722</v>
+        <v>0.2361216417487279</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.829660977916482</v>
+        <v>3.878972251908075</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.66350945725194</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.949390829171198</v>
+        <v>-5.170107729814487</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.761308253103933</v>
+        <v>1.673021492846617</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08703437995579771</v>
+        <v>0.1692198366084534</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.793641637059638</v>
+        <v>3.842952911051232</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.227355224754471</v>
+        <v>-5.44807212539776</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.645200347606813</v>
+        <v>1.556913587349497</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.00258535432968654</v>
+        <v>0.0796001023229691</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.734947649224537</v>
+        <v>3.784258923216131</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830323</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.344322917393362</v>
+        <v>-5.565039818036651</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.760617327250301</v>
+        <v>1.672330566992985</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.00258535432968654</v>
+        <v>0.0796001023229691</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.897151705923582</v>
+        <v>3.946462979915175</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.429040859614315</v>
+        <v>-5.649757760257605</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.721576788325733</v>
+        <v>1.633290028068417</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.08770138325773291</v>
+        <v>-0.00551592660507727</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.840928726530568</v>
+        <v>3.890240000522161</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.510975677883199</v>
+        <v>-5.731692578526488</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.699032278586671</v>
+        <v>1.610745518329356</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.0976361288448131</v>
+        <v>-0.01545067219215746</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.845197296746811</v>
+        <v>3.894508570738404</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.612951800131606</v>
+        <v>-5.833668700774895</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.66716746814321</v>
+        <v>1.578880707885895</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1996122510932207</v>
+        <v>-0.117426794440565</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.792937261853669</v>
+        <v>3.842248535845262</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.502945516654385</v>
+        <v>-5.723662417297674</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.703322868778275</v>
+        <v>1.615036108520959</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1764076791759455</v>
+        <v>-0.09422222252328982</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.799012892248209</v>
+        <v>3.848324166239803</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818517</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.359885940913459</v>
+        <v>-5.580602841556749</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.764796709796619</v>
+        <v>1.676509949539303</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1683942525859662</v>
+        <v>-0.08620879593331054</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.808070958924171</v>
+        <v>3.857382232915765</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.838576733364665</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.058439215441622</v>
+        <v>-5.279156116084911</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.89263628286789</v>
+        <v>1.726557862616952</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1330524728858711</v>
+        <v>0.2152379295385267</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.99619987708981</v>
+        <v>3.967719491087781</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.839547911117375</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.083029459676806</v>
+        <v>-5.303746360320095</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.883771362926527</v>
+        <v>1.71769294267559</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1330524728858711</v>
+        <v>0.2152379295385267</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.997171054842521</v>
+        <v>3.968690668840492</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474154</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.840390815497131</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.031991083670285</v>
+        <v>-5.252707984313575</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.90502961770889</v>
+        <v>1.738951197457953</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1330524728858711</v>
+        <v>0.2152379295385267</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.998013959222275</v>
+        <v>3.969533573220247</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969537</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.859428914371276</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.990851788803655</v>
+        <v>-5.211568689446944</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.940523434529688</v>
+        <v>1.774445014278751</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1741917677525019</v>
+        <v>0.2563772244051575</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.0417356350164</v>
+        <v>4.013255249014371</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700473</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.675612910495211</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.880245648724053</v>
+        <v>-5.100962549367342</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.800949886685463</v>
+        <v>1.634871466434526</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2847979078321039</v>
+        <v>0.3669833644847595</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.924283315188095</v>
+        <v>3.895802929186067</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077635</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.679114954569175</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.010826383254895</v>
+        <v>-5.231543283898184</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.75221963694709</v>
+        <v>1.586141216696153</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1542171733012614</v>
+        <v>0.236402629953917</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.849436918543553</v>
+        <v>3.820956532541525</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.663541773645258</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.846330049063933</v>
+        <v>-5.067046949707223</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.802444989699557</v>
+        <v>1.63636656944862</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.1542171733012614</v>
+        <v>0.236402629953917</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.833863737619636</v>
+        <v>3.805383351617608</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077622</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.662729484081687</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.873699981748365</v>
+        <v>-5.094416882391655</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.790684727062214</v>
+        <v>1.624606306811277</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.1542171733012614</v>
+        <v>0.236402629953917</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.833051448056065</v>
+        <v>3.804571062054038</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.67259826320676</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.884085176638255</v>
+        <v>-5.104802077281544</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.796399428231331</v>
+        <v>1.630321007980394</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1438319784113721</v>
+        <v>0.2260174350640277</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.836689110247204</v>
+        <v>3.808208724245177</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735281</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.743435268983185</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.90267333536048</v>
+        <v>-5.123390236003769</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.859801170518866</v>
+        <v>1.693722750267929</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1252438196891467</v>
+        <v>0.2074292763418024</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.896373220790294</v>
+        <v>3.867892834788266</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496548</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.740304279801483</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.902971882056516</v>
+        <v>-5.123688782699805</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.85655076265875</v>
+        <v>1.690472342407813</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1252438196891467</v>
+        <v>0.2074292763418024</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.893242231608593</v>
+        <v>3.864761845606565</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108852</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.744835174740875</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.802148748366088</v>
+        <v>-5.022865649009377</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.901410911074313</v>
+        <v>1.735332490823376</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.1377080351735006</v>
+        <v>0.2198934918261562</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.905251655838597</v>
+        <v>3.876771269836569</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121461</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.744964428219418</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.611367387613681</v>
+        <v>-4.83208428825697</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.977852708853819</v>
+        <v>1.811774288602882</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3284893959259079</v>
+        <v>0.4106748525785636</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.019849725768585</v>
+        <v>3.991369339766557</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.724801273957015</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.592850533571861</v>
+        <v>-4.81356743421515</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.965096296208143</v>
+        <v>1.799017875957207</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.3414195253511161</v>
+        <v>0.4236049820037718</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.007444649161306</v>
+        <v>3.978964263159278</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.759768210569073</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.567657349070543</v>
+        <v>-4.788374249713832</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.010140506620729</v>
+        <v>1.844062086369792</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.3666127098524345</v>
+        <v>0.4487981665050901</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.057527496474155</v>
+        <v>4.029047110472128</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.753454778470511</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.55560322215758</v>
+        <v>-4.776320122800869</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.008648725287352</v>
+        <v>1.842570305036415</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.3786668367653973</v>
+        <v>0.4608522934180529</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.05844654052337</v>
+        <v>4.029966154521343</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.755335408654647</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.562226468847938</v>
+        <v>-4.782943369491227</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.007880056795345</v>
+        <v>1.841801636544408</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.372043590075039</v>
+        <v>0.4542290467276946</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.056353222693291</v>
+        <v>4.027872836691263</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.768186434532529</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.459345879319345</v>
+        <v>-4.680062779962634</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.061883318484664</v>
+        <v>1.895804898233727</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.5571096362562875</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.13093260228833</v>
+        <v>4.102452216286302</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760309</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.788389104706123</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.482787918499432</v>
+        <v>-4.703504819142721</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.072709172986223</v>
+        <v>1.906630752735287</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.5571096362562875</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.151135272461924</v>
+        <v>4.122654886459896</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781699</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.788389104706123</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.500860426791044</v>
+        <v>-4.721577327434333</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.065480169669579</v>
+        <v>1.899401749418642</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.5571096362562875</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.151135272461924</v>
+        <v>4.122654886459896</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.67006888808283</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.74864101829959</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.680596732186559</v>
+        <v>-4.901313632829848</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.95383756110484</v>
+        <v>1.787759140853903</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.5571096362562875</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.11138718605539</v>
+        <v>4.082906800053363</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.868994597472571</v>
+        <v>3.783483427745939</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.987962901173263</v>
+        <v>3.861896847630099</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.680596732186559</v>
+        <v>-4.901313632829848</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.95383756110484</v>
+        <v>1.787759140853903</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.4749241796036319</v>
+        <v>0.5571096362562875</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.981026698159631</v>
+        <v>3.854960644616467</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240808.xlsx
+++ b/tame_output/ON/bt/strategyON_20240808.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>58.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>125.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>434.8%</t>
+          <t>433.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-651.7%</t>
+          <t>-637.1%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-197.4%</t>
+          <t>-196.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-39.5%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-263.9%</t>
+          <t>-165.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-168.3%</t>
+          <t>-189.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-60.5%</t>
+          <t>-54.6%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.791251575535187</v>
+        <v>-3.908483026444977</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.265105601297265</v>
+        <v>1.21821302093335</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7880865394008755</v>
+        <v>0.6708550884910853</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.254814579465614</v>
+        <v>3.18447570891974</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.835641044864615</v>
+        <v>-3.952872495774405</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.249223289490095</v>
+        <v>1.202330709126179</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7436970700714478</v>
+        <v>0.6264656191616577</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.230054373792558</v>
+        <v>3.159715503246684</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.952182649969958</v>
+        <v>-4.069414100879747</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.197682355959681</v>
+        <v>1.150789775595765</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.5099240140563148</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.155205119241076</v>
+        <v>3.084866248695202</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.839805648787285</v>
+        <v>-3.957037099697075</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.248124452263417</v>
+        <v>1.201231871899502</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6271554649661051</v>
+        <v>0.5099240140563148</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.160696415071743</v>
+        <v>3.090357544525869</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.867586046688638</v>
+        <v>-3.984817497598428</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.248509494871415</v>
+        <v>1.2016169145075</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.599375067064752</v>
+        <v>0.4821436161549618</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.15552537809947</v>
+        <v>3.085186507553596</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.985966719418777</v>
+        <v>-4.103198170328566</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.039512945780013</v>
+        <v>0.9926203654160974</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.4149257640039856</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.953550386809538</v>
+        <v>2.883211516263664</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.094580797862108</v>
+        <v>-4.211812248771897</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.116216975121886</v>
+        <v>1.069324394757971</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.4149257640039856</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.073700047528743</v>
+        <v>3.003361176982869</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.059171759613965</v>
+        <v>-4.176403210523755</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.144893616523467</v>
+        <v>1.098001036159551</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5321572149137758</v>
+        <v>0.4149257640039856</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.088213073631066</v>
+        <v>3.017874203085192</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.020788097055814</v>
+        <v>-4.138019547965603</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.157666522889096</v>
+        <v>1.11077394252518</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.4533094265621367</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.108662712508325</v>
+        <v>3.038323841962451</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.843671767020648</v>
+        <v>-3.960903217930437</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.225242083748464</v>
+        <v>1.178349503384548</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5705408774719269</v>
+        <v>0.4533094265621367</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.105391741353627</v>
+        <v>3.035052870807753</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.888764011854193</v>
+        <v>-4.005995462763983</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.207888577576959</v>
+        <v>1.160995997213043</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5086448343025372</v>
+        <v>0.3914133833927469</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.068937507213907</v>
+        <v>2.998598636668033</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.709388590615426</v>
+        <v>-3.826620041525215</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.27342572137888</v>
+        <v>1.226533141014964</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6654215924732558</v>
+        <v>0.5481901415634656</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.156790537422753</v>
+        <v>3.086451666876878</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.754402804136032</v>
+        <v>-3.871634255045822</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.236227491302228</v>
+        <v>1.189334910938312</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6350726971586512</v>
+        <v>0.517841246248861</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.119388655565579</v>
+        <v>3.049049785019705</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.021407314408467</v>
+        <v>-4.138638765318257</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.135117249532199</v>
+        <v>1.088224669168283</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4407096591157026</v>
+        <v>0.3234782082059124</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.008462395078756</v>
+        <v>2.938123524532882</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.12260509584564</v>
+        <v>-4.23983654675543</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.093842058853832</v>
+        <v>1.046949478489916</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.2550693946605932</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.966621028848066</v>
+        <v>2.896282158302192</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.116094129231327</v>
+        <v>-4.233325580141117</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.094046407053873</v>
+        <v>1.047153826689957</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3723008455703835</v>
+        <v>0.2550693946605932</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.964220990402382</v>
+        <v>2.893882119856508</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.09705600152403</v>
+        <v>-4.21428745243382</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.098186377345037</v>
+        <v>1.051293796981121</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4495225846088753</v>
+        <v>0.1968857833293987</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.007078753033722</v>
+        <v>2.855496672266037</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.128182632674648</v>
+        <v>-4.245414083584438</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.20503012651898</v>
+        <v>1.158137546155064</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4495225846088753</v>
+        <v>0.1968857833293987</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.126373154667913</v>
+        <v>2.974791073900227</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.142049394008566</v>
+        <v>-4.259280844918356</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.200316750971547</v>
+        <v>1.153424170607631</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4116646678750523</v>
+        <v>0.1590278665955757</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.104491733613753</v>
+        <v>2.952909652846067</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.097245222468636</v>
+        <v>-4.214476673378426</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.224246949984444</v>
+        <v>1.177354369620529</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4116646678750523</v>
+        <v>0.1590278665955757</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.110500264010679</v>
+        <v>2.958918183242993</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.949502252233634</v>
+        <v>-4.066733703143424</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.181294359355645</v>
+        <v>1.134401778991729</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5794720251099355</v>
+        <v>0.3268352238304589</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.109134899628808</v>
+        <v>2.957552818861122</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.033323473508332</v>
+        <v>-4.150554924418122</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.150559492377247</v>
+        <v>1.103666912013331</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5794720251099355</v>
+        <v>0.3268352238304589</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.111928521160289</v>
+        <v>2.960346440392603</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.027170767455548</v>
+        <v>-4.144402218365338</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.153682923190019</v>
+        <v>1.106790342826103</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5856247311627197</v>
+        <v>0.3329879298832432</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.116282493183618</v>
+        <v>2.964700412415932</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.04398006560605</v>
+        <v>-4.16121151651584</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.146039680669928</v>
+        <v>1.099147100306012</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5688154330122182</v>
+        <v>0.3161786317327415</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.105277391033427</v>
+        <v>2.953695310265741</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.981682066829928</v>
+        <v>-4.098913517739717</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.237294433977198</v>
+        <v>1.190401853613282</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5688154330122182</v>
+        <v>0.3161786317327415</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.171612944830248</v>
+        <v>3.020030864062562</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.77989186916477</v>
+        <v>-3.897123320074559</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.120302514757388</v>
+        <v>1.073409934393472</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7668336251813725</v>
+        <v>0.5141968239018959</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.092715861845868</v>
+        <v>2.941133781078182</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.830778581850965</v>
+        <v>-3.948010032760754</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.170238062005085</v>
+        <v>1.12334548164117</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7159469124951781</v>
+        <v>0.4633101112157014</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.132474066556326</v>
+        <v>2.98089198578864</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.744167839201157</v>
+        <v>-3.861399290110947</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.219510095181052</v>
+        <v>1.172617514817136</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7945726437003363</v>
+        <v>0.5419358424208596</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.194277241395465</v>
+        <v>3.042695160627779</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.804377137206442</v>
+        <v>-3.921608588116231</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.19396235680361</v>
+        <v>1.147069776439694</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7343633456950518</v>
+        <v>0.4817265444155751</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.156687643416966</v>
+        <v>3.00510556264928</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.727955090774515</v>
+        <v>-3.845186541684305</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.223022793416309</v>
+        <v>1.176130213052393</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7343633456950518</v>
+        <v>0.4817265444155751</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.155179261456894</v>
+        <v>3.003597180689209</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.683581959135946</v>
+        <v>-3.800813410045736</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.240634913507173</v>
+        <v>1.193742333143257</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7787364773336204</v>
+        <v>0.5260996760541437</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.181666007875472</v>
+        <v>3.030083927107786</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.706062309994831</v>
+        <v>-3.823293760904621</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.226036567302209</v>
+        <v>1.179143986938294</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7787364773336204</v>
+        <v>0.5260996760541437</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.176059802014062</v>
+        <v>3.024477721246376</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.658406579433776</v>
+        <v>-3.775638030343565</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.251480616554436</v>
+        <v>1.204588036190521</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.826392207894676</v>
+        <v>0.5737554066151993</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.2110349973785</v>
+        <v>3.059452916610814</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.643322467058094</v>
+        <v>-3.67511987184481</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.262406634879434</v>
+        <v>1.249687672964747</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8414763202703581</v>
+        <v>0.6742735651139539</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.224977838178634</v>
+        <v>3.124656185084792</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.703989057460483</v>
+        <v>-3.735786462247199</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.22489467119435</v>
+        <v>1.212175709279664</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7597780035518245</v>
+        <v>0.5925752483954202</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.162713520623386</v>
+        <v>3.062391867529544</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.659150655852085</v>
+        <v>-3.690948060638801</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.246927734448338</v>
+        <v>1.234208772533652</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7643214364966939</v>
+        <v>0.5971186813402897</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.169537283000937</v>
+        <v>3.069215629907094</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.678649112094093</v>
+        <v>-3.710446516880809</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.243289291582613</v>
+        <v>1.230570329667926</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7162367952167896</v>
+        <v>0.5490340400603854</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.144847437864072</v>
+        <v>3.044525784770229</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.634446275008193</v>
+        <v>-3.666243679794909</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.26685002894481</v>
+        <v>1.254131067030124</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7604396323026901</v>
+        <v>0.5932368771462858</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.177248742643449</v>
+        <v>3.076927089549607</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.671425302671636</v>
+        <v>-3.703222707458352</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.25046841834868</v>
+        <v>1.237749456433994</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7974135340940206</v>
+        <v>0.6302107789376163</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.197843084187495</v>
+        <v>3.097521431093653</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.513133885132364</v>
+        <v>-3.54493128991908</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.365032750547429</v>
+        <v>1.352313788632743</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7974135340940206</v>
+        <v>0.6302107789376163</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.249090849370535</v>
+        <v>3.148769196276692</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321018</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.305491881497888</v>
+        <v>-3.337289286284604</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.446530256595473</v>
+        <v>1.433811294680786</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.005055537728497</v>
+        <v>0.8378527825720925</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.372116756145474</v>
+        <v>3.271795103051631</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475134</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.254459788775359</v>
+        <v>-3.286257193562076</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.461891321922754</v>
+        <v>1.449172360008067</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.056087630451025</v>
+        <v>0.8888848752946205</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.397684240017261</v>
+        <v>3.297362586923418</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.189235607648154</v>
+        <v>-3.22103301243487</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.505168398466341</v>
+        <v>1.492449436551655</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.121311811578231</v>
+        <v>0.9541090564218261</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.454006152786289</v>
+        <v>3.353684499692446</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.15180858757702</v>
+        <v>-3.183605992363737</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.516100178794075</v>
+        <v>1.503381216879388</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.126563349607412</v>
+        <v>0.9593605944510077</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.453118047903079</v>
+        <v>3.352796394809236</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.171920243611729</v>
+        <v>-3.203717648398445</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.509312308711432</v>
+        <v>1.496593346796745</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.137590694604832</v>
+        <v>0.9703879394484269</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.46099124723277</v>
+        <v>3.360669594138928</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.118175429184524</v>
+        <v>-3.14997283397124</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.691368005503525</v>
+        <v>1.678649043588838</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.147654004045294</v>
+        <v>0.9804512488888889</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.627587003918258</v>
+        <v>3.527265350824416</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.043393168159511</v>
+        <v>-3.075190572946227</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.841393819131347</v>
+        <v>1.82867485721666</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.222436265070306</v>
+        <v>1.055233509913902</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.792569269751083</v>
+        <v>3.69224761665724</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.017309083895703</v>
+        <v>-3.04910648868242</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.843535428850729</v>
+        <v>1.830816466936042</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.222436265070306</v>
+        <v>1.055233509913902</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.784277245764942</v>
+        <v>3.683955592671099</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.929431170786583</v>
+        <v>-2.961228575573299</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.876879789678157</v>
+        <v>1.86416082776347</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.338361907493657</v>
+        <v>1.171159152337253</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.852025826802732</v>
+        <v>3.75170417370889</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.920538709393299</v>
+        <v>-2.952336114180016</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.897991179962261</v>
+        <v>1.885272218047575</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.338361907493657</v>
+        <v>1.171159152337253</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.869580232529524</v>
+        <v>3.769258579435681</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.089014826363177</v>
+        <v>-3.120812231149893</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.822455780578894</v>
+        <v>1.809736818664208</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.310414071777077</v>
+        <v>1.143211316620672</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.844666578504159</v>
+        <v>3.744344925410316</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782704</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.391215297501594</v>
+        <v>-2.42301270228831</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.082845289311389</v>
+        <v>2.070126327396703</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.240066012406666</v>
+        <v>1.072863257250261</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.783727440069775</v>
+        <v>3.683405786975932</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.368494193818441</v>
+        <v>-2.400291598605158</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.082597753281555</v>
+        <v>2.069878791366868</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.240066012406666</v>
+        <v>1.072863257250261</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.774391462566679</v>
+        <v>3.674069809472837</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.497696007112484</v>
+        <v>-2.5294934118992</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.189823153815107</v>
+        <v>2.17710419190042</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.110864199112624</v>
+        <v>0.9436614439562192</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.855776500441423</v>
+        <v>3.75545484734758</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.652477013890739</v>
+        <v>-2.684274418677456</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.164988573597451</v>
+        <v>2.152269611682764</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.077496525058148</v>
+        <v>0.910293769901743</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.872833718502384</v>
+        <v>3.772512065408541</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.645422323675566</v>
+        <v>-2.677219728462282</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.164485805673066</v>
+        <v>2.151766843758379</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.084551215273321</v>
+        <v>0.9173484601169168</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.873741888621033</v>
+        <v>3.77342023552719</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331111</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.618471099349078</v>
+        <v>-2.650268504135794</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.185272449048402</v>
+        <v>2.172553487133716</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.099431561301041</v>
+        <v>0.932228806144636</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.892676249882406</v>
+        <v>3.792354596788563</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784104</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.754424107405394</v>
+        <v>-2.78622151219211</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.314994377970836</v>
+        <v>2.302275416056149</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.099431561301041</v>
+        <v>0.932228806144636</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.076779382027366</v>
+        <v>3.976457728933523</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.776832225210266</v>
+        <v>-2.808629629996982</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.29814782575188</v>
+        <v>2.285428863837193</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.099431561301041</v>
+        <v>0.932228806144636</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.068896076930359</v>
+        <v>3.968574423836516</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.906029770043186</v>
+        <v>-2.836853865574583</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.248522807368349</v>
+        <v>2.276193169155791</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.14962246615839</v>
+        <v>0.9502055585959446</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.101064619394407</v>
+        <v>3.981414474856939</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.915470695931716</v>
+        <v>-2.846294791463113</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.301000154734785</v>
+        <v>2.328670516522226</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.272049583701782</v>
+        <v>1.072632676139336</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.230774607642289</v>
+        <v>4.111124463104821</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.967744303267357</v>
+        <v>-2.898568398798754</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.282981806345829</v>
+        <v>2.31065216813327</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.219775976366141</v>
+        <v>1.020359068803695</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.202301537786204</v>
+        <v>4.082651393248737</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347699</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.044074280868263</v>
+        <v>-2.97489837639966</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.250561628199242</v>
+        <v>2.278231989986683</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.219775976366141</v>
+        <v>1.020359068803695</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.200413350679979</v>
+        <v>4.080763206142512</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.246328001192616</v>
+        <v>-3.177152096724013</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.164480369672363</v>
+        <v>2.192150731459804</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.017522256041787</v>
+        <v>0.8181053484793412</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.07388134808823</v>
+        <v>3.954231203550762</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.407896426719871</v>
+        <v>-3.338720522251268</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.098287009671613</v>
+        <v>2.125957371459054</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8907393322439078</v>
+        <v>0.6913224246814619</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.996245604019655</v>
+        <v>3.876595459482187</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.540197718817425</v>
+        <v>-3.471021814348822</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.05843989969851</v>
+        <v>2.086110261485952</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8907393322439078</v>
+        <v>0.6913224246814619</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.009319010885573</v>
+        <v>3.889668866348106</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.726066029656655</v>
+        <v>-3.656890125188052</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.976097772145758</v>
+        <v>2.0037681339332</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7321737389239601</v>
+        <v>0.5327568313615142</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.906184851676545</v>
+        <v>3.786534707139077</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.753966816766128</v>
+        <v>-3.684790912297525</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.963461498428972</v>
+        <v>1.991131860216413</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6975768147810253</v>
+        <v>0.4981599072185794</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.883950738317786</v>
+        <v>3.764300593780318</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.876492919469022</v>
+        <v>-3.762159968958917</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.911215501325013</v>
+        <v>1.956948681529054</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5750507120781314</v>
+        <v>0.4207908505571871</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.807199520673248</v>
+        <v>3.714643603760682</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.107007415654611</v>
+        <v>-3.992674465144506</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.885715662441281</v>
+        <v>1.931448842645322</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3445362158925427</v>
+        <v>0.1902763543715984</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.735596782552399</v>
+        <v>3.643040865639832</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.363728233649434</v>
+        <v>-4.24939528313933</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.923339054245198</v>
+        <v>1.96907223444924</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2361216417487279</v>
+        <v>0.08186178022778356</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.810859757067957</v>
+        <v>3.71830384015539</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.517714651425575</v>
+        <v>-4.403381700915471</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.930724756280382</v>
+        <v>1.976457936484423</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2361216417487279</v>
+        <v>0.08186178022778356</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.879840026213597</v>
+        <v>3.78728410930103</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.467192747597909</v>
+        <v>-4.352859797087805</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.936984719931569</v>
+        <v>1.982717900135611</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2361216417487279</v>
+        <v>0.08186178022778356</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.865891228333718</v>
+        <v>3.773335311421151</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.719667901605633</v>
+        <v>-4.605334951095529</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.847865147383893</v>
+        <v>1.893598327587935</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2361216417487279</v>
+        <v>0.08186178022778356</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.877761717389132</v>
+        <v>3.785205800476565</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.012563658085045</v>
+        <v>-4.898230707574942</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.731917379311072</v>
+        <v>1.777650559515114</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2361216417487279</v>
+        <v>0.08186178022778356</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.878972251908075</v>
+        <v>3.786416334995509</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.170107729814487</v>
+        <v>-5.055774779304383</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.673021492846617</v>
+        <v>1.718754673050658</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1692198366084534</v>
+        <v>0.01495997508750907</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.842952911051232</v>
+        <v>3.750396994138665</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.44807212539776</v>
+        <v>-5.333739174887657</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.556913587349497</v>
+        <v>1.602646767553539</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.0796001023229691</v>
+        <v>-0.07465975919797518</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.784258923216131</v>
+        <v>3.691703006303564</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.565039818036651</v>
+        <v>-5.450706867526548</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.672330566992985</v>
+        <v>1.718063747197026</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.0796001023229691</v>
+        <v>-0.07465975919797518</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.946462979915175</v>
+        <v>3.853907063002608</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.649757760257605</v>
+        <v>-5.535424809747501</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.633290028068417</v>
+        <v>1.679023208272459</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.00551592660507727</v>
+        <v>-0.1597757881260216</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.890240000522161</v>
+        <v>3.797684083609595</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.731692578526488</v>
+        <v>-5.617359628016384</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.610745518329356</v>
+        <v>1.656478698533397</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.01545067219215746</v>
+        <v>-0.1697105337131017</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.894508570738404</v>
+        <v>3.801952653825838</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.833668700774895</v>
+        <v>-5.719335750264792</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.578880707885895</v>
+        <v>1.624613888089936</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.117426794440565</v>
+        <v>-0.2716866559615093</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.842248535845262</v>
+        <v>3.749692618932696</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.723662417297674</v>
+        <v>-5.60932946678757</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.615036108520959</v>
+        <v>1.660769288725001</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.09422222252328982</v>
+        <v>-0.2484820840442341</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.848324166239803</v>
+        <v>3.755768249327236</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.580602841556749</v>
+        <v>-5.466269891046645</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.676509949539303</v>
+        <v>1.722243129743345</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.08620879593331054</v>
+        <v>-0.2404686574542548</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.857382232915765</v>
+        <v>3.764826316003198</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.838576733364665</v>
+        <v>3.787934895229653</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.279156116084911</v>
+        <v>-5.245960535272319</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.726557862616952</v>
+        <v>1.689194256806978</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2152379295385267</v>
+        <v>-0.02015930167992852</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.967719491087781</v>
+        <v>3.775839314221696</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.839547911117375</v>
+        <v>3.788906072982364</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.303746360320095</v>
+        <v>-5.270550779507503</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.71769294267559</v>
+        <v>1.680329336865614</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2152379295385267</v>
+        <v>-0.02015930167992852</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.968690668840492</v>
+        <v>3.776810491974407</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474154</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.840390815497131</v>
+        <v>3.789748977362119</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.252707984313575</v>
+        <v>-5.219512403500983</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.738951197457953</v>
+        <v>1.701587591647978</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2152379295385267</v>
+        <v>-0.02015930167992852</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.969533573220247</v>
+        <v>3.777653396354162</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969537</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.859428914371276</v>
+        <v>3.808787076236265</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.211568689446944</v>
+        <v>-5.178373108634352</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.774445014278751</v>
+        <v>1.737081408468776</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2563772244051575</v>
+        <v>0.02097999318670229</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.013255249014371</v>
+        <v>3.821375072148286</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700473</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.675612910495211</v>
+        <v>3.624971072360199</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.100962549367342</v>
+        <v>-5.06776696855475</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.634871466434526</v>
+        <v>1.597507860624551</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3669833644847595</v>
+        <v>0.1315861332663043</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.895802929186067</v>
+        <v>3.703922752319982</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077635</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.679114954569175</v>
+        <v>3.628473116434163</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.231543283898184</v>
+        <v>-5.198347703085592</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.586141216696153</v>
+        <v>1.548777610886178</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.236402629953917</v>
+        <v>0.001005398735461793</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.820956532541525</v>
+        <v>3.629076355675441</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.663541773645258</v>
+        <v>3.612899935510246</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.067046949707223</v>
+        <v>-5.033851368894631</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.63636656944862</v>
+        <v>1.599002963638645</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.236402629953917</v>
+        <v>0.001005398735461793</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.805383351617608</v>
+        <v>3.613503174751523</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077622</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.662729484081687</v>
+        <v>3.612087645946676</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.094416882391655</v>
+        <v>-5.061221301579063</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.624606306811277</v>
+        <v>1.587242701001303</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.236402629953917</v>
+        <v>0.001005398735461793</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.804571062054038</v>
+        <v>3.612690885187953</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.67259826320676</v>
+        <v>3.621956425071748</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.104802077281544</v>
+        <v>-5.071606496468952</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.630321007980394</v>
+        <v>1.592957402170419</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2260174350640277</v>
+        <v>-0.009379796154427522</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.808208724245177</v>
+        <v>3.616328547379092</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.743435268983185</v>
+        <v>3.692793430848173</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.123390236003769</v>
+        <v>-5.090194655191177</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.693722750267929</v>
+        <v>1.656359144457954</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2074292763418024</v>
+        <v>-0.02796795487665288</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.867892834788266</v>
+        <v>3.676012657922182</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496548</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.740304279801483</v>
+        <v>3.689662441666472</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.123688782699805</v>
+        <v>-5.090493201887213</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.690472342407813</v>
+        <v>1.653108736597838</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2074292763418024</v>
+        <v>-0.02796795487665288</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.864761845606565</v>
+        <v>3.67288166874048</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108852</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.744835174740875</v>
+        <v>3.694193336605863</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.022865649009377</v>
+        <v>-4.989670068196785</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.735332490823376</v>
+        <v>1.697968885013401</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2198934918261562</v>
+        <v>-0.01550373939229904</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.876771269836569</v>
+        <v>3.684891092970484</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121461</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.744964428219418</v>
+        <v>3.694322590084406</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.83208428825697</v>
+        <v>-4.798888707444378</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.811774288602882</v>
+        <v>1.774410682792907</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4106748525785636</v>
+        <v>0.1752776213601083</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.991369339766557</v>
+        <v>3.799489162900472</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.724801273957015</v>
+        <v>3.674159435822003</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.81356743421515</v>
+        <v>-4.780371853402558</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.799017875957207</v>
+        <v>1.761654270147232</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4236049820037718</v>
+        <v>0.1882077507853165</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.978964263159278</v>
+        <v>3.787084086293193</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.759768210569073</v>
+        <v>3.709126372434061</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.788374249713832</v>
+        <v>-4.75517866890124</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.844062086369792</v>
+        <v>1.806698480559817</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4487981665050901</v>
+        <v>0.2134009352866349</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.029047110472128</v>
+        <v>3.837166933606043</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.753454778470511</v>
+        <v>3.702812940335499</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.776320122800869</v>
+        <v>-4.743124541988277</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.842570305036415</v>
+        <v>1.80520669922644</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4608522934180529</v>
+        <v>0.2254550621995977</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.029966154521343</v>
+        <v>3.838085977655258</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.755335408654647</v>
+        <v>3.704693570519635</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.782943369491227</v>
+        <v>-4.749747788678635</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.841801636544408</v>
+        <v>1.804438030734433</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4542290467276946</v>
+        <v>0.2188318155092394</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.027872836691263</v>
+        <v>3.835992659825179</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.768186434532529</v>
+        <v>3.717544596397517</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.680062779962634</v>
+        <v>-4.646867199150043</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.895804898233727</v>
+        <v>1.858441292423752</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5571096362562875</v>
+        <v>0.3217124050378323</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.102452216286302</v>
+        <v>3.910572039420217</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760309</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.788389104706123</v>
+        <v>3.737747266571112</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.703504819142721</v>
+        <v>-4.670309238330129</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.906630752735287</v>
+        <v>1.869267146925312</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5571096362562875</v>
+        <v>0.3217124050378323</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.122654886459896</v>
+        <v>3.930774709593811</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781699</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.788389104706123</v>
+        <v>3.737747266571112</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.721577327434333</v>
+        <v>-4.688381746621741</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.899401749418642</v>
+        <v>1.862038143608667</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5571096362562875</v>
+        <v>0.3217124050378323</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.122654886459896</v>
+        <v>3.930774709593811</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.67006888808283</v>
+        <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.74864101829959</v>
+        <v>3.697999180164578</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.901313632829848</v>
+        <v>-4.897365611207698</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.787759140853903</v>
+        <v>1.738696511367751</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5571096362562875</v>
+        <v>0.3217124050378323</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.082906800053363</v>
+        <v>3.891026623187278</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.783483427745939</v>
+        <v>3.49305318213921</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.861896847630099</v>
+        <v>3.705021799161518</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.901313632829848</v>
+        <v>-4.755730450592816</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.787759140853903</v>
+        <v>1.802373194610644</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.5571096362562875</v>
+        <v>0.3481921558166484</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.854960644616467</v>
+        <v>3.913937092651508</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240808.xlsx
+++ b/tame_output/ON/bt/strategyON_20240808.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.4%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-622.4%</t>
+          <t>-629.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>433.1%</t>
+          <t>440.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-637.1%</t>
+          <t>-641.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,27 +1135,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-249.4%</t>
+          <t>-252.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-196.0%</t>
+          <t>-198.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-245.3%</t>
+          <t>-252.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>439.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-165.3%</t>
+          <t>1996.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-189.2%</t>
+          <t>-192.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-147.6%</t>
+          <t>-151.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-54.6%</t>
+          <t>-56.8%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.3634908492490375</v>
+        <v>0.2951176996706588</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.26761008749881</v>
+        <v>3.240260827667459</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.70757260984084</v>
+        <v>1.639199460262462</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.147113738017447</v>
+        <v>4.10608984827042</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1263593573992424</v>
+        <v>0.05798620782086372</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.207698575256434</v>
+        <v>3.180349315425083</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.70757260984084</v>
+        <v>1.639199460262462</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.182054822514989</v>
+        <v>4.141030932767961</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.1313969481268289</v>
+        <v>0.06302379854845025</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.208291051732806</v>
+        <v>3.180941791901455</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.763217066107158</v>
+        <v>1.694843916528779</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.214018936460117</v>
+        <v>4.17299504671309</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1257970865812278</v>
+        <v>-0.1941702361596065</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.084159819473321</v>
+        <v>3.05681055964197</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.506023031399101</v>
+        <v>1.437649881820722</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.03844889725902</v>
+        <v>3.997425007511993</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.1915644766306399</v>
+        <v>-0.2599376262090186</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.058870472584026</v>
+        <v>3.031521212752675</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.506023031399101</v>
+        <v>1.437649881820722</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.03946650638949</v>
+        <v>3.998442616642463</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3968091536878844</v>
+        <v>-0.4651823032662631</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.967400633748884</v>
+        <v>2.940051373917533</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.506023031399101</v>
+        <v>1.437649881820722</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.030094538377246</v>
+        <v>3.989070648630219</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4785810541156361</v>
+        <v>-0.5469542036940148</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.924774599533022</v>
+        <v>2.89742533970167</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.533058604805237</v>
+        <v>1.464685455226859</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.036398608376166</v>
+        <v>3.995374718629139</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5457901619875138</v>
+        <v>-0.6141633115658924</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.902656273217973</v>
+        <v>2.875307013386621</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.533058604805237</v>
+        <v>1.464685455226859</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.041163925209869</v>
+        <v>4.000140035462842</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.5344009253327124</v>
+        <v>-0.602774074911091</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.905036763999134</v>
+        <v>2.877687504167783</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.544447841460039</v>
+        <v>1.47607469188166</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.045822263321989</v>
+        <v>4.004798373574962</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.9521549488795494</v>
+        <v>-1.020528098457928</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.735862046085463</v>
+        <v>2.708512786254111</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.126693817913202</v>
+        <v>1.058320668334823</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.793096740698951</v>
+        <v>3.752072850951924</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.242286615484981</v>
+        <v>-1.310659765063359</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.619675596042212</v>
+        <v>2.59232633621086</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.150775612653382</v>
+        <v>1.082402463075003</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.807412034141981</v>
+        <v>3.766388144394953</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.450290673838058</v>
+        <v>-1.518663823416437</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.541366117254906</v>
+        <v>2.514016857423554</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.150775612653382</v>
+        <v>1.082402463075003</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.812304178695906</v>
+        <v>3.771280288948879</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.512469084999028</v>
+        <v>-1.580842234577407</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.511576209128506</v>
+        <v>2.484226949297155</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.088597201492412</v>
+        <v>1.020224051914033</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.770078588337312</v>
+        <v>3.729054698590284</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.878537812143681</v>
+        <v>-1.946910961722059</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.358233017577094</v>
+        <v>2.330883757745743</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.722528474347759</v>
+        <v>0.6541553247693802</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.543521651356969</v>
+        <v>3.502497761609942</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.087028593595365</v>
+        <v>-2.155401743173744</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.295174994735189</v>
+        <v>2.267825734903837</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.5140376928960746</v>
+        <v>0.4456645433176958</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.438765472224727</v>
+        <v>3.3977415824777</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.334229778360587</v>
+        <v>-2.402602927938966</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.204393271237668</v>
+        <v>2.177044011406317</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.534191046394887</v>
+        <v>0.4658178968165082</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.458956234732583</v>
+        <v>3.417932344985556</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.826614806384684</v>
+        <v>-2.894987955963062</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.008545652071762</v>
+        <v>1.981196392240411</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.04180601837079029</v>
+        <v>-0.02656713120758852</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.164631609961857</v>
+        <v>3.12360772021483</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.211795197314756</v>
+        <v>-3.280168346893135</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.853016034512596</v>
+        <v>1.825666774681245</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.04180601837079029</v>
+        <v>-0.02656713120758852</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.16317414877472</v>
+        <v>3.122150259027693</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.461665877329338</v>
+        <v>-3.530039026907716</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.75483688596138</v>
+        <v>1.727487626130028</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.07806873820125354</v>
+        <v>0.009695588622874729</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.186700904127615</v>
+        <v>3.145677014380587</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.668177654216359</v>
+        <v>-3.736550803794738</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.668338233862829</v>
+        <v>1.640988974031478</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.128443038685768</v>
+        <v>-0.1968161882641468</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.058899896651659</v>
+        <v>3.017876006904632</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.98752172929686</v>
+        <v>-4.05589487887524</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.542373530530888</v>
+        <v>1.515024270699536</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.128443038685768</v>
+        <v>-0.1968161882641468</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.060672823351919</v>
+        <v>3.019648933604892</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.373731560572635</v>
+        <v>-4.442104710151015</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.374222485487982</v>
+        <v>1.346873225656631</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.2192159784032113</v>
+        <v>-0.2875891279815901</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.992541946988857</v>
+        <v>2.95151805724183</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.608425554705187</v>
+        <v>-4.676798704283567</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.268629662837052</v>
+        <v>1.2412804030057</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.2128797111739561</v>
+        <v>-0.2812528607523349</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.984628482328501</v>
+        <v>2.943604592581474</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.94408820193564</v>
+        <v>-5.01246135151402</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.132945195600836</v>
+        <v>1.105595935769485</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.2808106966628609</v>
+        <v>-0.3491838462412397</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.942450482691124</v>
+        <v>2.901426592944096</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.020532532138511</v>
+        <v>-5.088905681716891</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.108855023753929</v>
+        <v>1.081505763922578</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.200365187569199</v>
+        <v>-0.2687383371475778</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.997205348381562</v>
+        <v>2.956181458634535</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.385659914777258</v>
+        <v>-5.454033064355638</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9620585857042618</v>
+        <v>0.9347093258729102</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.4966759718682116</v>
+        <v>-0.5650491214465904</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.818673392807986</v>
+        <v>2.777649503060958</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.794248691957937</v>
+        <v>-5.862621841536317</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7973846188467495</v>
+        <v>0.7700353590153974</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.90526474904889</v>
+        <v>-0.9736378986272688</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.572281670514338</v>
+        <v>2.53125778076731</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.908009103980802</v>
+        <v>-5.976382253559182</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.747065886509064</v>
+        <v>0.7197166266777124</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.90526474904889</v>
+        <v>-0.9736378986272688</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.567467102985799</v>
+        <v>2.526443213238771</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.324400978267799</v>
+        <v>-6.392774127846179</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5785031874031423</v>
+        <v>0.5511539275717907</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.90526474904889</v>
+        <v>-0.9736378986272688</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.565461153594676</v>
+        <v>2.524437263847648</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.685574608084787</v>
+        <v>-6.753947757663167</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4442924261450263</v>
+        <v>0.4169431663136747</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.90526474904889</v>
+        <v>-0.9736378986272688</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.575719844263355</v>
+        <v>2.534695954516327</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.028833127727806</v>
+        <v>-7.097206277306186</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3030885834335137</v>
+        <v>0.2757393236021621</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.90526474904889</v>
+        <v>-0.9736378986272688</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.57181940940905</v>
+        <v>2.530795519662023</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.07703594497015</v>
+        <v>-7.14540909454853</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2822123765915774</v>
+        <v>0.2548631167602253</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.90526474904889</v>
+        <v>-0.9736378986272688</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.570224329464051</v>
+        <v>2.529200439717024</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.373697286780347</v>
+        <v>-7.442070436358727</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1673268157967063</v>
+        <v>0.1399775559653547</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.9740078847827686</v>
+        <v>-1.042381034361147</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.532757423952932</v>
+        <v>2.491733534205905</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.56041699508965</v>
+        <v>-7.62879014466803</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.08861262793858238</v>
+        <v>0.06126336810723032</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.9740078847827686</v>
+        <v>-1.042381034361147</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.528731119418529</v>
+        <v>2.487707229671502</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.943418383832281</v>
+        <v>-8.01179153341066</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.06469002888005448</v>
+        <v>-0.09203928871140565</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.9740078847827686</v>
+        <v>-1.042381034361147</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.528629018096945</v>
+        <v>2.487605128349918</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.94790482903367</v>
+        <v>-8.016277978612049</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.06391309098917963</v>
+        <v>-0.0912623508205308</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.9784943299841573</v>
+        <v>-1.046867479562536</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.528508666947542</v>
+        <v>2.487484777200514</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.307435151537671</v>
+        <v>-8.37580830111605</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2023749166927304</v>
+        <v>-0.2297241765240816</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.9784943299841573</v>
+        <v>-1.046867479562536</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.533858970245592</v>
+        <v>2.492835080498565</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.357784214991893</v>
+        <v>-8.426157364570273</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.214598522117242</v>
+        <v>-0.2419477819485927</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.028843393438379</v>
+        <v>-1.097216543016758</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.511565552130236</v>
+        <v>2.470541662383209</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.455403492413289</v>
+        <v>-8.523776641991669</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2506044824640314</v>
+        <v>-0.2779537422953822</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.126462670859776</v>
+        <v>-1.194835820438155</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.456035736299167</v>
+        <v>2.41501184655214</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.509474991921648</v>
+        <v>-8.577848141500027</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2693395259458025</v>
+        <v>-0.2966887857771536</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.180534170368135</v>
+        <v>-1.248907319946514</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.426486392915724</v>
+        <v>2.385462503168696</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.713733167251512</v>
+        <v>-8.782106316829891</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3455295989591058</v>
+        <v>-0.3728788587904566</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.308173114982124</v>
+        <v>-1.376546264560503</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.355416223265973</v>
+        <v>2.314392333518946</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.747386005759985</v>
+        <v>-8.815759155338364</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3545081798780592</v>
+        <v>-0.3818574397094099</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.408586482899162</v>
+        <v>-1.47695963247754</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.299650757000186</v>
+        <v>2.258626867253159</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.673916174092536</v>
+        <v>-8.742289323670915</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3097485457176585</v>
+        <v>-0.3370978055490093</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.335116651231713</v>
+        <v>-1.403489800810092</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.359104357494076</v>
+        <v>2.318080467747049</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.84904059147908</v>
+        <v>-8.917413741057459</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3652430919247589</v>
+        <v>-0.3925923517561101</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.510241068618257</v>
+        <v>-1.578614218196636</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.268584927809667</v>
+        <v>2.22756103806264</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.083492685493569</v>
+        <v>-9.151865835071948</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.466243094432151</v>
+        <v>-0.4935923542635017</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.510241068618257</v>
+        <v>-1.578614218196636</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.261365762908071</v>
+        <v>2.220341873161044</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.187867416520016</v>
+        <v>-9.256240566098395</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5146651776167057</v>
+        <v>-0.5420144374480564</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.614615799644703</v>
+        <v>-1.682988949223082</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.192068733518227</v>
+        <v>2.1510448437712</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.240653572120342</v>
+        <v>-9.309026721698721</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5346638500182799</v>
+        <v>-0.562013109849631</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.7102912862271</v>
+        <v>-1.778664435805479</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.135779231407345</v>
+        <v>2.094755341660318</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.366690365488632</v>
+        <v>-9.435063515067011</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5823848387364809</v>
+        <v>-0.6097340985678321</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.753412812995736</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.153623933722305</v>
+        <v>2.112600043975278</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.309618593592701</v>
+        <v>-9.37799174317108</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5555657942917076</v>
+        <v>-0.5829150541230588</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.753412812995736</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.157614269408707</v>
+        <v>2.116590379661679</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.451290435316821</v>
+        <v>-9.5196635848952</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6137097578800974</v>
+        <v>-0.6410590177114486</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.685039663417358</v>
+        <v>-1.753412812995736</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.156139042509965</v>
+        <v>2.115115152762937</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.401699590891987</v>
+        <v>-9.470072740470366</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5788200099452916</v>
+        <v>-0.6061692697766428</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.635448818992524</v>
+        <v>-1.703821968570903</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.200946959329737</v>
+        <v>2.15992306958271</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.25278125642013</v>
+        <v>-9.321154405998509</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5323038098032318</v>
+        <v>-0.5596530696345829</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.604199228257351</v>
+        <v>-1.67257237783573</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.206645580124158</v>
+        <v>2.165621690377131</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.026936103700718</v>
+        <v>-9.095309253279098</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4323866756792585</v>
+        <v>-0.4597359355106097</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.562272552670187</v>
+        <v>-1.630645702248566</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.241380658512665</v>
+        <v>2.200356768765638</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.902357447363126</v>
+        <v>-8.970730596941506</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3814160685881629</v>
+        <v>-0.4087653284195141</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.562272552670187</v>
+        <v>-1.630645702248566</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.242519803068724</v>
+        <v>2.201495913321696</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.955252735407413</v>
+        <v>-9.023625884985792</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.39994040964377</v>
+        <v>-0.4272896694751207</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.557317206581741</v>
+        <v>-1.62569035616012</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.248126784883899</v>
+        <v>2.207102895136872</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.883119560119532</v>
+        <v>-8.951492709697911</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3653534352899808</v>
+        <v>-0.3927026951213319</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.557317206581741</v>
+        <v>-1.62569035616012</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.253860489122536</v>
+        <v>2.212836599375509</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.811753167509885</v>
+        <v>-8.880126317088264</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3465441406399874</v>
+        <v>-0.3738934004713381</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.554323963550472</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.286943062294459</v>
+        <v>2.245919172547432</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.71829413352466</v>
+        <v>-8.786667283103039</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3190440083588051</v>
+        <v>-0.3463932681901558</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.554323963550472</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.277059580981552</v>
+        <v>2.236035691234524</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.707640951971229</v>
+        <v>-8.776014101549608</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3166172962368061</v>
+        <v>-0.3439665560681573</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.485950813972093</v>
+        <v>-1.554323963550472</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.275225020482178</v>
+        <v>2.23420113073515</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.609733913294738</v>
+        <v>-8.678107062873117</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2777547957396709</v>
+        <v>-0.3051040555710216</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.417965064111537</v>
+        <v>-1.486338213689915</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.315716155425051</v>
+        <v>2.274692265678024</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.58578037231878</v>
+        <v>-8.654153521897159</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2675048732037939</v>
+        <v>-0.2948541330351451</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.394011523135579</v>
+        <v>-1.462384672713958</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.330756786156119</v>
+        <v>2.289732896409092</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.321720433995983</v>
+        <v>-8.390093583574362</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1751412140364272</v>
+        <v>-0.2024904738677784</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.129951584812783</v>
+        <v>-1.198324734391162</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.475932432988045</v>
+        <v>2.434908543241018</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.614640810491145</v>
+        <v>-7.683013960069524</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1049036017052072</v>
+        <v>0.07755434187385601</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.129951584812783</v>
+        <v>-1.198324734391162</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.473145399327744</v>
+        <v>2.432121509580717</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.574456512124955</v>
+        <v>-7.642829661703334</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1213209449395247</v>
+        <v>0.09397168510817355</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.089767286446592</v>
+        <v>-1.158140436024971</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.4975996022353</v>
+        <v>2.456575712488272</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.411056641185592</v>
+        <v>-7.479429790763971</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1860477145360266</v>
+        <v>0.1586984547046755</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9263674155072295</v>
+        <v>-0.9947405650856083</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.595006346019674</v>
+        <v>2.553982456272647</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.177575418955993</v>
+        <v>-7.245948568534373</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2873646322657182</v>
+        <v>0.2600153724343675</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6928861932776309</v>
+        <v>-0.7612593428560097</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.743019508195286</v>
+        <v>2.701995618448258</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.027909027948478</v>
+        <v>-7.096282177526858</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3443389783557653</v>
+        <v>0.3169897185244142</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.599982702035095</v>
+        <v>-0.6683558516134738</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.795869392627848</v>
+        <v>2.754845502880821</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.895633554317592</v>
+        <v>-6.964006703895971</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3926166545551468</v>
+        <v>0.3652673947237957</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4677072284042083</v>
+        <v>-0.5360803779825871</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.870602163553407</v>
+        <v>2.829578273806379</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.73989522175785</v>
+        <v>-6.808268371336229</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4577270482666802</v>
+        <v>0.4303777884353295</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3119688958444667</v>
+        <v>-0.3803420454228456</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.966860223776889</v>
+        <v>2.925836334029861</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.490895423074269</v>
+        <v>-6.559268572652648</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5702333089637714</v>
+        <v>0.5428840491324203</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06296909716088606</v>
+        <v>-0.1313422467392649</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.129166444210696</v>
+        <v>3.088142554463668</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.596485412847374</v>
+        <v>-6.664858562425753</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4000213834553108</v>
+        <v>0.3726721236239601</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1685590869339904</v>
+        <v>-0.2369322365123692</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937836520747615</v>
+        <v>2.896812631000587</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.615220314965971</v>
+        <v>-6.68359346454435</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4410717644849584</v>
+        <v>0.4137225046536077</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1741550965941217</v>
+        <v>-0.2425282461725005</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.983023256828622</v>
+        <v>2.941999367081595</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.467280273558371</v>
+        <v>-6.53565342313675</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3803688583598306</v>
+        <v>0.3530195985284799</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1538341806855641</v>
+        <v>-0.222207330263943</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.875336883685589</v>
+        <v>2.834312993938562</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.414310751304383</v>
+        <v>-6.482683900882762</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3928426810079477</v>
+        <v>0.365493421176597</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1692378080099541</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.898404610784504</v>
+        <v>2.857380721037477</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.248522555344092</v>
+        <v>-6.316895704922471</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4521973472969711</v>
+        <v>0.42484808746562</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1692378080099541</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.891443998689411</v>
+        <v>2.850420108942384</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.215159348865323</v>
+        <v>-6.283532498443702</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4800049842696215</v>
+        <v>0.4526557244382707</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1692378080099541</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.905906353070554</v>
+        <v>2.864882463323527</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.106900211742802</v>
+        <v>-6.175273361321181</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5178407595778252</v>
+        <v>0.4904914997464744</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1008646584315753</v>
+        <v>-0.1692378080099541</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.900438473529749</v>
+        <v>2.859414583782722</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.983609076925671</v>
+        <v>-6.05198222650405</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5646553075152547</v>
+        <v>0.5373060476839036</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.02242647638555523</v>
+        <v>-0.04594667319282358</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.971911248430605</v>
+        <v>2.930887358683577</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.962459878022227</v>
+        <v>-6.030833027600607</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5808159653139571</v>
+        <v>0.5534667054826059</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.02479747428938023</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.992301746009995</v>
+        <v>2.951277856262968</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.718694436038783</v>
+        <v>-5.787067585617162</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6741028504543856</v>
+        <v>0.6467535906230344</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.04357567528899858</v>
+        <v>-0.02479747428938023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.988082454357046</v>
+        <v>2.947058564610019</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.616931615761488</v>
+        <v>-5.685304765339867</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7169322924853194</v>
+        <v>0.6895830326539687</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.01157840589695153</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.998138209312519</v>
+        <v>2.957114319565492</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.367081221812414</v>
+        <v>-5.435454371390793</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8096145250486515</v>
+        <v>0.7822652652173003</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.01157840589695153</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.990880284296221</v>
+        <v>2.949856394549194</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.191189129344981</v>
+        <v>-5.25956227892336</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8835704855562736</v>
+        <v>0.8562212257249224</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.05679474368142728</v>
+        <v>-0.01157840589695153</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.99447940781687</v>
+        <v>2.953455518069843</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.019742666322517</v>
+        <v>-5.088115815900896</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9654765768198126</v>
+        <v>0.9381273169884614</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2282412067038904</v>
+        <v>0.1598680571255116</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.110674791684902</v>
+        <v>3.069650901937874</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.945453100584178</v>
+        <v>-5.013826250162557</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9942128807314452</v>
+        <v>0.966863620900094</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3025307724422297</v>
+        <v>0.2341576228638509</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.154269008744202</v>
+        <v>3.113245118997175</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.881817358350244</v>
+        <v>-4.950190507928623</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.024361978679336</v>
+        <v>0.9970127188479851</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.2977933650977854</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.197145255138881</v>
+        <v>3.156121365391853</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.770390599024323</v>
+        <v>-4.838763748602703</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.0501269411935</v>
+        <v>1.022777681362149</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3661665146761642</v>
+        <v>0.2977933650977854</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.178339513922676</v>
+        <v>3.137315624175649</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.780893222089612</v>
+        <v>-4.849266371667992</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.047668968592262</v>
+        <v>1.020319708760911</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.2872907420324965</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.17378101670838</v>
+        <v>3.132757126961353</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.708650653918418</v>
+        <v>-4.777023803496797</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.08049530969556</v>
+        <v>1.053146049864209</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3556638916108754</v>
+        <v>0.2872907420324965</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.1777103305432</v>
+        <v>3.136686440796173</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.690936967040552</v>
+        <v>-4.759310116618932</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.088259368364046</v>
+        <v>1.060910108532695</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.2904720709294134</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.18029771179869</v>
+        <v>3.139273822051663</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.582132081560825</v>
+        <v>-4.650505231139205</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.12877939377593</v>
+        <v>1.101430133944579</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3588452205077922</v>
+        <v>0.2904720709294134</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.177295783018684</v>
+        <v>3.136271893271656</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.362111283523815</v>
+        <v>-4.430484433102194</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.218366750001349</v>
+        <v>1.191017490169997</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.4316919159973936</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.263606727070086</v>
+        <v>3.222582837323059</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.229243594460537</v>
+        <v>-4.297616744038916</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.287408008428483</v>
+        <v>1.260058748597132</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5000650655757723</v>
+        <v>0.4316919159973936</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.279500909871909</v>
+        <v>3.238477020124882</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.109070511096038</v>
+        <v>-4.177443660674418</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.336623086214584</v>
+        <v>1.309273826383233</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6202381489402713</v>
+        <v>0.5518649993618925</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.352750604330911</v>
+        <v>3.311726714583883</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.973817149766061</v>
+        <v>-4.042190299344441</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.400812533308015</v>
+        <v>1.373463273476664</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7554915102702484</v>
+        <v>0.6871183606918696</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.443990723690337</v>
+        <v>3.40296683394331</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.033691977123754</v>
+        <v>-4.102065126702133</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.362900093766364</v>
+        <v>1.335550833935013</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.6272435333341775</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.394103318677147</v>
+        <v>3.35307942893012</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.913871746212916</v>
+        <v>-3.982244895791295</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.426117355364907</v>
+        <v>1.398768095533556</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6956166829125563</v>
+        <v>0.6272435333341775</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.409392487911356</v>
+        <v>3.368368598164329</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.916341452674722</v>
+        <v>-3.984714602253101</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.332773672102626</v>
+        <v>1.305424412271275</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6931469764507501</v>
+        <v>0.6247738268723713</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.315554863356714</v>
+        <v>3.274530973609687</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.984711638998732</v>
+        <v>-4.053084788577111</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.224687459058324</v>
+        <v>1.197338199226973</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6340495259085862</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.240382144263744</v>
+        <v>3.199358254516717</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.998499691845779</v>
+        <v>-4.066872841424158</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.209608946551397</v>
+        <v>1.182259686720046</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6340495259085862</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.230818852895635</v>
+        <v>3.189794963148608</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.054019767738368</v>
+        <v>-4.122392917316748</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.324431752886563</v>
+        <v>1.297082493055212</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6340495259085862</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.367849689587838</v>
+        <v>3.32682579984081</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.878545507945899</v>
+        <v>-3.946918657524278</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.399188688795339</v>
+        <v>1.371839428963988</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6340495259085862</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.372416921579625</v>
+        <v>3.331393031832598</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.989481760587148</v>
+        <v>-4.057854910165527</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.330556216500046</v>
+        <v>1.303206956668695</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.702422675486965</v>
+        <v>0.6340495259085862</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.348158950340832</v>
+        <v>3.307135060593805</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.955818215114866</v>
+        <v>-4.024191364693245</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.272559948090409</v>
+        <v>1.245210688259058</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6677130713808681</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.296895391025652</v>
+        <v>3.255871501278624</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.895965595911143</v>
+        <v>-3.964338745489521</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.30667338220403</v>
+        <v>1.27932412237268</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6677130713808681</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.307067777457784</v>
+        <v>3.266043887710757</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.809722132884765</v>
+        <v>-3.878095282463144</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.336117037988442</v>
+        <v>1.308767778157091</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7360862209592469</v>
+        <v>0.6677130713808681</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.302014048031644</v>
+        <v>3.260990158284617</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.855028952283745</v>
+        <v>-3.923402101862123</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.309770085673375</v>
+        <v>1.282420825842025</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.6269029083716373</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.269303725670631</v>
+        <v>3.228279835923604</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.884062056986047</v>
+        <v>-3.952435206564425</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.298708716825556</v>
+        <v>1.271359456994205</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6952760579500161</v>
+        <v>0.6269029083716373</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.269855598703733</v>
+        <v>3.228831708956705</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.908483026444977</v>
+        <v>-3.946080600951339</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.21821302093335</v>
+        <v>1.203173991130805</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6708550884910853</v>
+        <v>0.6332575139847233</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.18447570891974</v>
+        <v>3.161917164215923</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.952872495774405</v>
+        <v>-3.990470070280767</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.202330709126179</v>
+        <v>1.187291679323635</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6264656191616577</v>
+        <v>0.5888680446552956</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.159715503246684</v>
+        <v>3.137156958542867</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.069414100879747</v>
+        <v>-4.10701167538611</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.150789775595765</v>
+        <v>1.135750745793221</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5099240140563148</v>
+        <v>0.4723264395499528</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.084866248695202</v>
+        <v>3.062307703991384</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.957037099697075</v>
+        <v>-3.994634674203437</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.201231871899502</v>
+        <v>1.186192842096957</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5099240140563148</v>
+        <v>0.4723264395499528</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.090357544525869</v>
+        <v>3.067798999822052</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.984817497598428</v>
+        <v>-4.02241507210479</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.2016169145075</v>
+        <v>1.186577884704955</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4821436161549618</v>
+        <v>0.4445460416485998</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.085186507553596</v>
+        <v>3.062627962849779</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.103198170328566</v>
+        <v>-4.140795744834929</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9926203654160974</v>
+        <v>0.9775813356135532</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4149257640039856</v>
+        <v>0.3773281894976236</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.883211516263664</v>
+        <v>2.860652971559846</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.211812248771897</v>
+        <v>-4.24940982327826</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.069324394757971</v>
+        <v>1.054285364955426</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4149257640039856</v>
+        <v>0.3773281894976236</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.003361176982869</v>
+        <v>2.980802632279052</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.176403210523755</v>
+        <v>-4.214000785030117</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.098001036159551</v>
+        <v>1.082962006357006</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4149257640039856</v>
+        <v>0.3773281894976236</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.017874203085192</v>
+        <v>2.995315658381375</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.138019547965603</v>
+        <v>-4.175617122471966</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.11077394252518</v>
+        <v>1.095734912722636</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4533094265621367</v>
+        <v>0.4157118520557748</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.038323841962451</v>
+        <v>3.015765297258634</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.960903217930437</v>
+        <v>-3.9985007924368</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.178349503384548</v>
+        <v>1.163310473582004</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4533094265621367</v>
+        <v>0.4157118520557748</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.035052870807753</v>
+        <v>3.012494326103936</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.005995462763983</v>
+        <v>-4.043593037270345</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.160995997213043</v>
+        <v>1.145956967410499</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3914133833927469</v>
+        <v>0.353815808886385</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.998598636668033</v>
+        <v>2.976040091964216</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.826620041525215</v>
+        <v>-3.864217616031578</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.226533141014964</v>
+        <v>1.21149411121242</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5481901415634656</v>
+        <v>0.5105925670571037</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.086451666876878</v>
+        <v>3.063893122173061</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.871634255045822</v>
+        <v>-3.909231829552184</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.189334910938312</v>
+        <v>1.174295881135768</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.517841246248861</v>
+        <v>0.480243671742499</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.049049785019705</v>
+        <v>3.026491240315888</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.138638765318257</v>
+        <v>-4.176236339824619</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.088224669168283</v>
+        <v>1.073185639365739</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3234782082059124</v>
+        <v>0.2858806336995505</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.938123524532882</v>
+        <v>2.915564979829065</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.23983654675543</v>
+        <v>-4.277434121261792</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.046949478489916</v>
+        <v>1.031910448687371</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2550693946605932</v>
+        <v>0.2174718201542313</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.896282158302192</v>
+        <v>2.873723613598374</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.233325580141117</v>
+        <v>-4.27092315464748</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.047153826689957</v>
+        <v>1.032114796887413</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2550693946605932</v>
+        <v>0.2174718201542313</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.893882119856508</v>
+        <v>2.871323575152691</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.21428745243382</v>
+        <v>-4.251885026940182</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.051293796981121</v>
+        <v>1.036254767178577</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1968857833293987</v>
+        <v>0.1592882088230367</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.855496672266037</v>
+        <v>2.832938127562219</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.245414083584438</v>
+        <v>-4.283011658090801</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.158137546155064</v>
+        <v>1.14309851635252</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1968857833293987</v>
+        <v>0.1592882088230367</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.974791073900227</v>
+        <v>2.95223252919641</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.259280844918356</v>
+        <v>-4.296878419424718</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.153424170607631</v>
+        <v>1.138385140805086</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1590278665955757</v>
+        <v>0.1214302920892138</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.952909652846067</v>
+        <v>2.93035110814225</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.214476673378426</v>
+        <v>-4.252074247884789</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.177354369620529</v>
+        <v>1.162315339817984</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1590278665955757</v>
+        <v>0.1214302920892138</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.958918183242993</v>
+        <v>2.936359638539176</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.066733703143424</v>
+        <v>-4.104331277649786</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.134401778991729</v>
+        <v>1.119362749189185</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3268352238304589</v>
+        <v>0.289237649324097</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.957552818861122</v>
+        <v>2.934994274157305</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.150554924418122</v>
+        <v>-4.188152498924484</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.103666912013331</v>
+        <v>1.088627882210786</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3268352238304589</v>
+        <v>0.289237649324097</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.960346440392603</v>
+        <v>2.937787895688786</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.144402218365338</v>
+        <v>-4.1819997928717</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.106790342826103</v>
+        <v>1.091751313023559</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3329879298832432</v>
+        <v>0.2953903553768812</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.964700412415932</v>
+        <v>2.942141867712115</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.16121151651584</v>
+        <v>-4.198809091022202</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.099147100306012</v>
+        <v>1.084108070503468</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3161786317327415</v>
+        <v>0.2785810572263796</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.953695310265741</v>
+        <v>2.931136765561924</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.098913517739717</v>
+        <v>-4.13651109224608</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.190401853613282</v>
+        <v>1.175362823810738</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3161786317327415</v>
+        <v>0.2785810572263796</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.020030864062562</v>
+        <v>2.997472319358745</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.897123320074559</v>
+        <v>-3.934720894580922</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.073409934393472</v>
+        <v>1.058370904590928</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5141968239018959</v>
+        <v>0.476599249395534</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.941133781078182</v>
+        <v>2.918575236374365</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.948010032760754</v>
+        <v>-3.985607607267116</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.12334548164117</v>
+        <v>1.108306451838625</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4633101112157014</v>
+        <v>0.4257125367093395</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.98089198578864</v>
+        <v>2.958333441084823</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.861399290110947</v>
+        <v>-3.898996864617309</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.172617514817136</v>
+        <v>1.157578485014592</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5419358424208596</v>
+        <v>0.5043382679144977</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.042695160627779</v>
+        <v>3.020136615923962</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.921608588116231</v>
+        <v>-3.959206162622594</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.147069776439694</v>
+        <v>1.13203074663715</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4817265444155751</v>
+        <v>0.4441289699092131</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.00510556264928</v>
+        <v>2.982547017945463</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.845186541684305</v>
+        <v>-3.882784116190667</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.176130213052393</v>
+        <v>1.161091183249849</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4817265444155751</v>
+        <v>0.4441289699092131</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.003597180689209</v>
+        <v>2.981038635985391</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.800813410045736</v>
+        <v>-3.838410984552098</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.193742333143257</v>
+        <v>1.178703303340713</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5260996760541437</v>
+        <v>0.4885021015477817</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.030083927107786</v>
+        <v>3.007525382403969</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.823293760904621</v>
+        <v>-3.860891335410983</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.179143986938294</v>
+        <v>1.164104957135749</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5260996760541437</v>
+        <v>0.4885021015477817</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.024477721246376</v>
+        <v>3.001919176542559</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.775638030343565</v>
+        <v>-3.813235604849927</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.204588036190521</v>
+        <v>1.189549006387976</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5737554066151993</v>
+        <v>0.5361578321088374</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.059452916610814</v>
+        <v>3.036894371906997</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.67511987184481</v>
+        <v>-3.712717446351173</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.249687672964747</v>
+        <v>1.234648643162203</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6742735651139539</v>
+        <v>0.6366759906075919</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.124656185084792</v>
+        <v>3.102097640380975</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.735786462247199</v>
+        <v>-3.773384036753562</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.212175709279664</v>
+        <v>1.19713667947712</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5925752483954202</v>
+        <v>0.5549776738890583</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.062391867529544</v>
+        <v>3.039833322825727</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.690948060638801</v>
+        <v>-3.728545635145164</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.234208772533652</v>
+        <v>1.219169742731107</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5971186813402897</v>
+        <v>0.5595211068339278</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.069215629907094</v>
+        <v>3.046657085203277</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.710446516880809</v>
+        <v>-3.748044091387172</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.230570329667926</v>
+        <v>1.215531299865382</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5490340400603854</v>
+        <v>0.5114364655540234</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.044525784770229</v>
+        <v>3.021967240066413</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.666243679794909</v>
+        <v>-3.703841254301271</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.254131067030124</v>
+        <v>1.23909203722758</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5932368771462858</v>
+        <v>0.5556393026399239</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.076927089549607</v>
+        <v>3.05436854484579</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.703222707458352</v>
+        <v>-3.740820281964714</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.237749456433994</v>
+        <v>1.22271042663145</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6302107789376163</v>
+        <v>0.5926132044312544</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.097521431093653</v>
+        <v>3.074962886389836</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.54493128991908</v>
+        <v>-3.582528864425442</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.352313788632743</v>
+        <v>1.337274758830198</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6302107789376163</v>
+        <v>0.5926132044312544</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.148769196276692</v>
+        <v>3.126210651572875</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.337289286284604</v>
+        <v>-3.374886860790966</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.433811294680786</v>
+        <v>1.418772264878242</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8378527825720925</v>
+        <v>0.8002552080657306</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.271795103051631</v>
+        <v>3.249236558347814</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.286257193562076</v>
+        <v>-3.323854768068438</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.449172360008067</v>
+        <v>1.434133330205523</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8888848752946205</v>
+        <v>0.8512873007882585</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.297362586923418</v>
+        <v>3.274804042219601</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.22103301243487</v>
+        <v>-3.258630586941233</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.492449436551655</v>
+        <v>1.47741040674911</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9541090564218261</v>
+        <v>0.9165114819154642</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.353684499692446</v>
+        <v>3.331125954988629</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.183605992363737</v>
+        <v>-3.221203566870099</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.503381216879388</v>
+        <v>1.488342187076844</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9593605944510077</v>
+        <v>0.9217630199446458</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.352796394809236</v>
+        <v>3.330237850105418</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.203717648398445</v>
+        <v>-3.241315222904807</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.496593346796745</v>
+        <v>1.481554316994201</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9703879394484269</v>
+        <v>0.932790364942065</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.360669594138928</v>
+        <v>3.338111049435111</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.14997283397124</v>
+        <v>-3.187570408477602</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.678649043588838</v>
+        <v>1.663610013786294</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9804512488888889</v>
+        <v>0.942853674382527</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.527265350824416</v>
+        <v>3.504706806120598</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.075190572946227</v>
+        <v>-3.11278814745259</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.82867485721666</v>
+        <v>1.813635827414116</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.055233509913902</v>
+        <v>1.01763593540754</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.69224761665724</v>
+        <v>3.669689071953423</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.04910648868242</v>
+        <v>-3.086704063188782</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.830816466936042</v>
+        <v>1.815777437133498</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.055233509913902</v>
+        <v>1.01763593540754</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.683955592671099</v>
+        <v>3.661397047967282</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.961228575573299</v>
+        <v>-2.998826150079661</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.86416082776347</v>
+        <v>1.849121797960926</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.171159152337253</v>
+        <v>1.133561577830891</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.75170417370889</v>
+        <v>3.729145629005072</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.952336114180016</v>
+        <v>-2.989933688686378</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.885272218047575</v>
+        <v>1.870233188245031</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.171159152337253</v>
+        <v>1.133561577830891</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.769258579435681</v>
+        <v>3.746700034731864</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.120812231149893</v>
+        <v>-3.158409805656256</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.809736818664208</v>
+        <v>1.794697788861663</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.143211316620672</v>
+        <v>1.10561374211431</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.744344925410316</v>
+        <v>3.721786380706499</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782704</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.42301270228831</v>
+        <v>-2.460610276794672</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.070126327396703</v>
+        <v>2.055087297594159</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.072863257250261</v>
+        <v>1.0352656827439</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.683405786975932</v>
+        <v>3.660847242272115</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.400291598605158</v>
+        <v>-2.43788917311152</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.069878791366868</v>
+        <v>2.054839761564324</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.072863257250261</v>
+        <v>1.0352656827439</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.674069809472837</v>
+        <v>3.651511264769019</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.5294934118992</v>
+        <v>-2.567090986405562</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.17710419190042</v>
+        <v>2.162065162097876</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9436614439562192</v>
+        <v>0.9060638694498573</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.75545484734758</v>
+        <v>3.732896302643763</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.684274418677456</v>
+        <v>-2.721871993183818</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.152269611682764</v>
+        <v>2.13723058188022</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.910293769901743</v>
+        <v>0.8726961953953811</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.772512065408541</v>
+        <v>3.749953520704724</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.677219728462282</v>
+        <v>-2.714817302968644</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.151766843758379</v>
+        <v>2.136727813955835</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9173484601169168</v>
+        <v>0.8797508856105549</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.77342023552719</v>
+        <v>3.750861690823373</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.650268504135794</v>
+        <v>-2.687866078642156</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.172553487133716</v>
+        <v>2.157514457331172</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.932228806144636</v>
+        <v>0.8946312316382741</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.792354596788563</v>
+        <v>3.769796052084746</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784104</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.78622151219211</v>
+        <v>-2.823819086698473</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.302275416056149</v>
+        <v>2.287236386253605</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.932228806144636</v>
+        <v>0.8946312316382741</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.976457728933523</v>
+        <v>3.953899184229706</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.808629629996982</v>
+        <v>-2.846227204503345</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.285428863837193</v>
+        <v>2.270389834034649</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.932228806144636</v>
+        <v>0.8946312316382741</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.968574423836516</v>
+        <v>3.946015879132699</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.836853865574583</v>
+        <v>-2.874451440080945</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.276193169155791</v>
+        <v>2.261154139353247</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9502055585959446</v>
+        <v>0.9126079840895827</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.981414474856939</v>
+        <v>3.958855930153121</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.846294791463113</v>
+        <v>-2.883892365969475</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.328670516522226</v>
+        <v>2.313631486719682</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.072632676139336</v>
+        <v>1.035035101632974</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.111124463104821</v>
+        <v>4.088565918401004</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.898568398798754</v>
+        <v>-2.936165973305116</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.31065216813327</v>
+        <v>2.295613138330726</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.020359068803695</v>
+        <v>0.9827614942973329</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.082651393248737</v>
+        <v>4.06009284854492</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.97489837639966</v>
+        <v>-3.012495950906022</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.278231989986683</v>
+        <v>2.263192960184139</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.020359068803695</v>
+        <v>0.9827614942973329</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.080763206142512</v>
+        <v>4.058204661438695</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.177152096724013</v>
+        <v>-3.214749671230376</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.192150731459804</v>
+        <v>2.17711170165726</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8181053484793412</v>
+        <v>0.7805077739729795</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.954231203550762</v>
+        <v>3.931672658846946</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.338720522251268</v>
+        <v>-3.376318096757631</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.125957371459054</v>
+        <v>2.11091834165651</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6913224246814619</v>
+        <v>0.6537248501751002</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.876595459482187</v>
+        <v>3.85403691477837</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.471021814348822</v>
+        <v>-3.508619388855184</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.086110261485952</v>
+        <v>2.071071231683407</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6913224246814619</v>
+        <v>0.6537248501751002</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.889668866348106</v>
+        <v>3.867110321644289</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.656890125188052</v>
+        <v>-3.694487699694414</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.0037681339332</v>
+        <v>1.988729104130655</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5327568313615142</v>
+        <v>0.4951592568551525</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.786534707139077</v>
+        <v>3.76397616243526</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.71581989500697</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.684790912297525</v>
+        <v>-3.722388486803887</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.991131860216413</v>
+        <v>1.976092830413868</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4981599072185794</v>
+        <v>0.4605623327122177</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.764300593780318</v>
+        <v>3.741742049076501</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787381</v>
+        <v>3.684895778787383</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.762159968958917</v>
+        <v>-3.844914589506781</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.956948681529054</v>
+        <v>1.923846833309909</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4207908505571871</v>
+        <v>0.3380362300093238</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.714643603760682</v>
+        <v>3.664990831431964</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585932</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.992674465144506</v>
+        <v>-4.075429085692369</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.931448842645322</v>
+        <v>1.898346994426178</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1902763543715984</v>
+        <v>0.1075217338237351</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.643040865639832</v>
+        <v>3.593388093311114</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814659</v>
+        <v>3.640750087814661</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.24939528313933</v>
+        <v>-4.332149903687194</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.96907223444924</v>
+        <v>1.935970386230095</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.08186178022778356</v>
+        <v>-0.0008928403200797463</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.71830384015539</v>
+        <v>3.668651067826672</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237089</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.403381700915471</v>
+        <v>-4.486136321463334</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.976457936484423</v>
+        <v>1.943356088265279</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.08186178022778356</v>
+        <v>-0.0008928403200797463</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.78728410930103</v>
+        <v>3.737631336972312</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423382</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.352859797087805</v>
+        <v>-4.435614417635668</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.982717900135611</v>
+        <v>1.949616051916466</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.08186178022778356</v>
+        <v>-0.0008928403200797463</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.773335311421151</v>
+        <v>3.723682539092433</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609747</v>
+        <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.605334951095529</v>
+        <v>-4.688089571643393</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.893598327587935</v>
+        <v>1.86049647936879</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.08186178022778356</v>
+        <v>-0.0008928403200797463</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.785205800476565</v>
+        <v>3.735553028147847</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973151</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.898230707574942</v>
+        <v>-4.980985328122805</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.777650559515114</v>
+        <v>1.744548711295969</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.08186178022778356</v>
+        <v>-0.0008928403200797463</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.786416334995509</v>
+        <v>3.736763562666791</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725194</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.055774779304383</v>
+        <v>-5.138529399852247</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.718754673050658</v>
+        <v>1.685652824831514</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.01495997508750907</v>
+        <v>-0.06779464546035424</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.750396994138665</v>
+        <v>3.700744221809948</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.333739174887657</v>
+        <v>-5.41649379543552</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.602646767553539</v>
+        <v>1.569544919334394</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.07465975919797518</v>
+        <v>-0.1574143797458385</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.691703006303564</v>
+        <v>3.642050233974846</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830323</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.450706867526548</v>
+        <v>-5.533461488074411</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.718063747197026</v>
+        <v>1.684961898977881</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.07465975919797518</v>
+        <v>-0.1574143797458385</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.853907063002608</v>
+        <v>3.804254290673891</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.535424809747501</v>
+        <v>-5.618179430295364</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.679023208272459</v>
+        <v>1.645921360053314</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1597757881260216</v>
+        <v>-0.2425304086738849</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.797684083609595</v>
+        <v>3.748031311280877</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.617359628016384</v>
+        <v>-5.700114248564248</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.656478698533397</v>
+        <v>1.623376850314252</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1697105337131017</v>
+        <v>-0.2524651542609651</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.801952653825838</v>
+        <v>3.75229988149712</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.719335750264792</v>
+        <v>-5.802090370812655</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.624613888089936</v>
+        <v>1.591512039870792</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2716866559615093</v>
+        <v>-0.3544412765093726</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.749692618932696</v>
+        <v>3.700039846603978</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.60932946678757</v>
+        <v>-5.692084087335433</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.660769288725001</v>
+        <v>1.627667440505856</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2484820840442341</v>
+        <v>-0.3312367045920974</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.755768249327236</v>
+        <v>3.706115476998518</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818517</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.466269891046645</v>
+        <v>-5.549024511594508</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.722243129743345</v>
+        <v>1.6891412815242</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2404686574542548</v>
+        <v>-0.3232232780021181</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.764826316003198</v>
+        <v>3.71517354367448</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051782</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.787934895229653</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.245960535272319</v>
+        <v>-5.247577786122671</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.689194256806978</v>
+        <v>1.816980854595471</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.02015930167992852</v>
+        <v>-0.02177655253028088</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.775839314221696</v>
+        <v>3.903302461840118</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.788906072982364</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.270550779507503</v>
+        <v>-5.272168030357855</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.680329336865614</v>
+        <v>1.808115934654108</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.02015930167992852</v>
+        <v>-0.02177655253028088</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.776810491974407</v>
+        <v>3.904273639592829</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474154</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.789748977362119</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.219512403500983</v>
+        <v>-5.221129654351334</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.701587591647978</v>
+        <v>1.829374189436471</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.02015930167992852</v>
+        <v>-0.02177655253028088</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.777653396354162</v>
+        <v>3.905116543972584</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969537</v>
+        <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.808787076236265</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.178373108634352</v>
+        <v>-5.179990359484703</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.737081408468776</v>
+        <v>1.864868006257269</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.02097999318670229</v>
+        <v>0.01936274233634994</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.821375072148286</v>
+        <v>3.948838219766708</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700473</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.624971072360199</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.06776696855475</v>
+        <v>-5.069384219405102</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.597507860624551</v>
+        <v>1.725294458413044</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1315861332663043</v>
+        <v>0.1299688824159519</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.703922752319982</v>
+        <v>3.831385899938404</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077635</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.628473116434163</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.198347703085592</v>
+        <v>-5.199964953935944</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.548777610886178</v>
+        <v>1.676564208674671</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.001005398735461793</v>
+        <v>-0.0006118521148905653</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.629076355675441</v>
+        <v>3.756539503293862</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.612899935510246</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.033851368894631</v>
+        <v>-5.035468619744982</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.599002963638645</v>
+        <v>1.726789561427138</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.001005398735461793</v>
+        <v>-0.0006118521148905653</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.613503174751523</v>
+        <v>3.740966322369944</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077622</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.612087645946676</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.061221301579063</v>
+        <v>-5.062838552429414</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.587242701001303</v>
+        <v>1.715029298789795</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.001005398735461793</v>
+        <v>-0.0006118521148905653</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.612690885187953</v>
+        <v>3.740154032806374</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147903</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.621956425071748</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.071606496468952</v>
+        <v>-5.073223747319304</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.592957402170419</v>
+        <v>1.720743999958912</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.009379796154427522</v>
+        <v>-0.01099704700477988</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.616328547379092</v>
+        <v>3.743791694997513</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735279</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.692793430848173</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.090194655191177</v>
+        <v>-5.091811906041529</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.656359144457954</v>
+        <v>1.784145742246447</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.02796795487665288</v>
+        <v>-0.02958520572700524</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.676012657922182</v>
+        <v>3.803475805540603</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496548</v>
+        <v>3.85512053549655</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.689662441666472</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.090493201887213</v>
+        <v>-5.092110452737565</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.653108736597838</v>
+        <v>1.780895334386331</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.02796795487665288</v>
+        <v>-0.02958520572700524</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.67288166874048</v>
+        <v>3.800344816358902</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108852</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.694193336605863</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.989670068196785</v>
+        <v>-4.991287319047137</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.697968885013401</v>
+        <v>1.825755482801894</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.01550373939229904</v>
+        <v>-0.0171209902426514</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.684891092970484</v>
+        <v>3.812354240588905</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121461</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.694322590084406</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.798888707444378</v>
+        <v>-4.80050595829473</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.774410682792907</v>
+        <v>1.9021972805814</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.1752776213601083</v>
+        <v>0.173660370509756</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.799489162900472</v>
+        <v>3.926952310518893</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.674159435822003</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.780371853402558</v>
+        <v>-4.78198910425291</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.761654270147232</v>
+        <v>1.889440867935725</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.1882077507853165</v>
+        <v>0.1865904999349642</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.787084086293193</v>
+        <v>3.914547233911614</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912979</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.709126372434061</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.75517866890124</v>
+        <v>-4.756795919751592</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.806698480559817</v>
+        <v>1.93448507834831</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.2134009352866349</v>
+        <v>0.2117836844362825</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.837166933606043</v>
+        <v>3.964630081224464</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539888</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.702812940335499</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.743124541988277</v>
+        <v>-4.744741792838629</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.80520669922644</v>
+        <v>1.932993297014933</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.2254550621995977</v>
+        <v>0.2238378113492454</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.838085977655258</v>
+        <v>3.96554912527368</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811003</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.704693570519635</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.749747788678635</v>
+        <v>-4.751365039528987</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.804438030734433</v>
+        <v>1.932224628522926</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.2188318155092394</v>
+        <v>0.217214564658887</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.835992659825179</v>
+        <v>3.9634558074436</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.717544596397517</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.646867199150043</v>
+        <v>-4.648484450000394</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.858441292423752</v>
+        <v>1.986227890212245</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.3217124050378323</v>
+        <v>0.3200951541874799</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.910572039420217</v>
+        <v>4.038035187038639</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760309</v>
+        <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.737747266571112</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.670309238330129</v>
+        <v>-4.671926489180481</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.869267146925312</v>
+        <v>1.997053744713805</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.3217124050378323</v>
+        <v>0.3200951541874799</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.930774709593811</v>
+        <v>4.058237857212233</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781699</v>
+        <v>3.666767386781701</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.737747266571112</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.688381746621741</v>
+        <v>-4.689998997472093</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.862038143608667</v>
+        <v>1.98982474139716</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.3217124050378323</v>
+        <v>0.3200951541874799</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.930774709593811</v>
+        <v>4.058237857212233</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082831</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.697999180164578</v>
+        <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.897365611207698</v>
+        <v>-4.869735302867608</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.738696511367751</v>
+        <v>1.878182132832421</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.3217124050378323</v>
+        <v>0.3200951541874799</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.891026623187278</v>
+        <v>4.018489770805699</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.49305318213921</v>
+        <v>3.807146638130423</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.705021799161518</v>
+        <v>3.69994498536121</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.755730450592816</v>
+        <v>-4.803296271251182</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.802373194610644</v>
+        <v>1.77827005254699</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.3481921558166484</v>
+        <v>0.3200951541874799</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.913937092651508</v>
+        <v>3.892002077873698</v>
       </c>
     </row>
   </sheetData>
